--- a/public/datos/puntos_entrega_rows validado.xlsx
+++ b/public/datos/puntos_entrega_rows validado.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29902"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29911"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\SRL CONCHOS\CICLO 2025-2026\Proyectos\MONITOREO\SICA 005\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\peper\Downloads\Antigravity\SICA 005\conchos-digital\public\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C46DBB5-8762-4427-91AA-A4B9C6E3A1CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9E5D858-6439-4C7D-9F1F-56A876F14ABE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-34510" yWindow="-110" windowWidth="34620" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-17290" yWindow="0" windowWidth="17380" windowHeight="13770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="puntos_entrega_rows" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
     <author>tc={68D79ADE-2227-4F97-AF7F-FD7D8C7C0BD9}</author>
   </authors>
   <commentList>
-    <comment ref="C6" authorId="0" shapeId="0" xr:uid="{68D79ADE-2227-4F97-AF7F-FD7D8C7C0BD9}">
+    <comment ref="C15" authorId="0" shapeId="0" xr:uid="{B160D996-08EB-4B64-BC68-969651B009FF}">
       <text>
         <r>
           <rPr>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="852" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="904" uniqueCount="416">
   <si>
     <t>id</t>
   </si>
@@ -100,9 +100,6 @@
     <t>lateral</t>
   </si>
   <si>
-    <t>Zona # 1</t>
-  </si>
-  <si>
     <t>1 Y 2</t>
   </si>
   <si>
@@ -184,21 +181,6 @@
     <t>Directa K 22+210</t>
   </si>
   <si>
-    <t>PE-014</t>
-  </si>
-  <si>
-    <t>Represa y Des.K 23+070</t>
-  </si>
-  <si>
-    <t>PE-015</t>
-  </si>
-  <si>
-    <t>Desfogue K-23+058</t>
-  </si>
-  <si>
-    <t>desfogue</t>
-  </si>
-  <si>
     <t>PE-017</t>
   </si>
   <si>
@@ -232,18 +214,12 @@
     <t>Lateral 33+340</t>
   </si>
   <si>
-    <t>Desfogue k-33+400</t>
-  </si>
-  <si>
     <t>Directa K 34+020</t>
   </si>
   <si>
     <t>Lateral k-34+952</t>
   </si>
   <si>
-    <t>Directa K-34+960</t>
-  </si>
-  <si>
     <t>Directa K-36+600</t>
   </si>
   <si>
@@ -325,9 +301,6 @@
     <t>Toma k-48+420</t>
   </si>
   <si>
-    <t>Tomak-49+872</t>
-  </si>
-  <si>
     <t>Toma k-55+370</t>
   </si>
   <si>
@@ -379,12 +352,6 @@
     <t>Toma K-55+360</t>
   </si>
   <si>
-    <t>Desfogue K-55+370</t>
-  </si>
-  <si>
-    <t>Desfogue</t>
-  </si>
-  <si>
     <t>Lateral k-56+360</t>
   </si>
   <si>
@@ -406,18 +373,12 @@
     <t>Directa K-58+761</t>
   </si>
   <si>
-    <t>DESF. AUT K-59+780</t>
-  </si>
-  <si>
     <t>Directa K-60+303</t>
   </si>
   <si>
     <t>Lateral K-61+030</t>
   </si>
   <si>
-    <t>Desfogue K-62+160</t>
-  </si>
-  <si>
     <t>Directa K-62+630</t>
   </si>
   <si>
@@ -463,9 +424,6 @@
     <t>Lateral k-75+580</t>
   </si>
   <si>
-    <t>Desfogue K-75+780</t>
-  </si>
-  <si>
     <t>Lateral K-75+811</t>
   </si>
   <si>
@@ -505,12 +463,6 @@
     <t>ZONA #2</t>
   </si>
   <si>
-    <t>TOTAL SECCION 20</t>
-  </si>
-  <si>
-    <t>118 SUB LAT K-0+186(M-12)</t>
-  </si>
-  <si>
     <t xml:space="preserve"> DIRECTA K-67+615</t>
   </si>
   <si>
@@ -550,9 +502,6 @@
     <t>Directa K-90+136</t>
   </si>
   <si>
-    <t>Desfogue K-90+428</t>
-  </si>
-  <si>
     <t>Directa K-90+729</t>
   </si>
   <si>
@@ -571,9 +520,6 @@
     <t>Directa K-93+190</t>
   </si>
   <si>
-    <t>Desfogue K-93+570</t>
-  </si>
-  <si>
     <t>Directa K-93+622</t>
   </si>
   <si>
@@ -592,9 +538,6 @@
     <t>Directa K-94+967</t>
   </si>
   <si>
-    <t>Directa K-94+617</t>
-  </si>
-  <si>
     <t>Directa K-96+824</t>
   </si>
   <si>
@@ -607,9 +550,6 @@
     <t>Directa k-97+790</t>
   </si>
   <si>
-    <t>Desfogue K-97+814</t>
-  </si>
-  <si>
     <t>Directa K-97+845</t>
   </si>
   <si>
@@ -700,9 +640,6 @@
     <t>PE-024</t>
   </si>
   <si>
-    <t>PE-025</t>
-  </si>
-  <si>
     <t>PE-027</t>
   </si>
   <si>
@@ -844,9 +781,6 @@
     <t>PE-077</t>
   </si>
   <si>
-    <t>PE-078</t>
-  </si>
-  <si>
     <t>PE-080</t>
   </si>
   <si>
@@ -868,18 +802,12 @@
     <t>PE-086</t>
   </si>
   <si>
-    <t>PE-087</t>
-  </si>
-  <si>
     <t>PE-088</t>
   </si>
   <si>
     <t>PE-089</t>
   </si>
   <si>
-    <t>PE-090</t>
-  </si>
-  <si>
     <t>PE-091</t>
   </si>
   <si>
@@ -970,15 +898,9 @@
     <t>PE-130</t>
   </si>
   <si>
-    <t>PE-131</t>
-  </si>
-  <si>
     <t>PE-132</t>
   </si>
   <si>
-    <t>PE-133</t>
-  </si>
-  <si>
     <t>PE-134</t>
   </si>
   <si>
@@ -1048,9 +970,6 @@
     <t>PE-158</t>
   </si>
   <si>
-    <t>PE-159</t>
-  </si>
-  <si>
     <t>PE-160</t>
   </si>
   <si>
@@ -1069,9 +988,6 @@
     <t>PE-165</t>
   </si>
   <si>
-    <t>PE-166</t>
-  </si>
-  <si>
     <t>PE-167</t>
   </si>
   <si>
@@ -1105,9 +1021,6 @@
     <t>PE-178</t>
   </si>
   <si>
-    <t>PE-179</t>
-  </si>
-  <si>
     <t>PE-180</t>
   </si>
   <si>
@@ -1133,13 +1046,265 @@
   </si>
   <si>
     <t>MOD-002</t>
+  </si>
+  <si>
+    <t>ZONA #1</t>
+  </si>
+  <si>
+    <t>PE-026</t>
+  </si>
+  <si>
+    <t>Lateral K-34+950</t>
+  </si>
+  <si>
+    <t>Directa K-34+980</t>
+  </si>
+  <si>
+    <t>105°15'45.01"O</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 27°57'7.58"N</t>
+  </si>
+  <si>
+    <t>105°15'55.72"O</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 27°57'6.53"N</t>
+  </si>
+  <si>
+    <t>105°16'10.65"O</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 27°57'20.07"N</t>
+  </si>
+  <si>
+    <t>105°16'17.17"O</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 27°57'26.28"N</t>
+  </si>
+  <si>
+    <t>105°16'19.71"O</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 27°57'28.64"N</t>
+  </si>
+  <si>
+    <t>105°16'25.63"O</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 27°57'34.32"N</t>
+  </si>
+  <si>
+    <t>105°16'32.98"O</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 27°57'41.35"N</t>
+  </si>
+  <si>
+    <t>105°16'40.01"O</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 27°57'48.00"N</t>
+  </si>
+  <si>
+    <t>105°17'46.79"O</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 27°59'9.58"N</t>
+  </si>
+  <si>
+    <t>PE-053</t>
+  </si>
+  <si>
+    <t>Directa k-44+800</t>
+  </si>
+  <si>
+    <t>105°19'3.42"O</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 28° 0'33.25"N</t>
+  </si>
+  <si>
+    <t>MOD-012</t>
+  </si>
+  <si>
+    <t>Toma K-49+872</t>
+  </si>
+  <si>
+    <t>105°19'34.02"O</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 28° 1'24.54"N</t>
+  </si>
+  <si>
+    <t>105°21'39.55"O</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 28° 4'2.56"N</t>
+  </si>
+  <si>
+    <t>105°19'29.56"O</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 28° 1'17.87"N</t>
+  </si>
+  <si>
+    <t>105°21'48.34"O</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 28° 4'5.42"N</t>
+  </si>
+  <si>
+    <t>PE-092</t>
+  </si>
+  <si>
+    <t>Repr. Y Pte K-62+800</t>
+  </si>
+  <si>
+    <t>105°23'48.20"O</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 28° 5'39.55"N</t>
+  </si>
+  <si>
+    <t>105°23'46.94"O</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 28° 5'59.46"N</t>
+  </si>
+  <si>
+    <t>105°23'56.42"O</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 28° 7'8.20"N</t>
+  </si>
+  <si>
+    <t>MOD-003</t>
+  </si>
+  <si>
+    <t>MOD-004</t>
+  </si>
+  <si>
+    <t>PE-115</t>
+  </si>
+  <si>
+    <t>SUBLATERAL K-2+286</t>
+  </si>
+  <si>
+    <t>105°23'56.26"O</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 28° 7'58.55"N</t>
+  </si>
+  <si>
+    <t>105°24'44.35"O</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 28° 7'53.67"N</t>
+  </si>
+  <si>
+    <t>105°25'13.84"O</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 28° 7'52.30"N</t>
+  </si>
+  <si>
+    <t>SUB LAT K-0+186(M-12)</t>
+  </si>
+  <si>
+    <t>PE-128</t>
+  </si>
+  <si>
+    <t>Represa K-73+296</t>
+  </si>
+  <si>
+    <t>105°28'51.36"O</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 28° 5'56.93"N</t>
+  </si>
+  <si>
+    <t>105°28'51.33"O</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 28° 5'56.83"N</t>
+  </si>
+  <si>
+    <t>PE-138</t>
+  </si>
+  <si>
+    <t>Represa K-79+025</t>
+  </si>
+  <si>
+    <t>105°28'51.37"O</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 28° 5'56.51"N</t>
+  </si>
+  <si>
+    <t>105°31'31.72"O</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 28° 5'34.71"N</t>
+  </si>
+  <si>
+    <t>PE-152</t>
+  </si>
+  <si>
+    <t>Represa K-87+549</t>
+  </si>
+  <si>
+    <t>PE-172</t>
+  </si>
+  <si>
+    <t>Represa K-94+057</t>
+  </si>
+  <si>
+    <t>Directa K-95+617</t>
+  </si>
+  <si>
+    <t>105°36'19.29"O</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 28° 8'43.42"N</t>
+  </si>
+  <si>
+    <t>105°36'27.76"O</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 28° 8'53.48"N</t>
+  </si>
+  <si>
+    <t>105°36'47.28"O</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 28° 9'23.41"N</t>
+  </si>
+  <si>
+    <t>105°36'46.86"O</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 28° 9'22.87"N</t>
+  </si>
+  <si>
+    <t>105°37'10.40"O</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 28° 9'35.09"N</t>
+  </si>
+  <si>
+    <t>105°37'10.85"O</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 28° 9'35.28"N</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1294,12 +1459,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <sz val="10"/>
       <name val="Comic Sans MS"/>
@@ -1326,7 +1485,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1506,8 +1665,20 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="12">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -1622,34 +1793,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1695,48 +1838,66 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2161,726 +2322,730 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="1" t="s">
+    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>386</v>
+      </c>
+      <c r="D2" s="19">
+        <v>0.186</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="20">
+        <v>400</v>
+      </c>
+      <c r="G2" s="9">
+        <v>-105.209819</v>
+      </c>
+      <c r="H2" s="9">
+        <v>27.669433000000001</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="J2" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="D3" s="16">
+        <v>0.53</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>187</v>
+      </c>
+      <c r="F3" s="14">
+        <v>400</v>
+      </c>
+      <c r="G3" s="9">
+        <v>-105.20787199999999</v>
+      </c>
+      <c r="H3" s="9">
+        <v>27.671658000000001</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="J3" s="8">
         <v>14</v>
       </c>
-      <c r="D2" s="1">
-        <v>6.8</v>
-      </c>
-      <c r="E2" s="1" t="s">
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>186</v>
+      </c>
+      <c r="D4" s="16">
+        <v>0.54</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="14">
+        <v>400</v>
+      </c>
+      <c r="G4" s="9">
+        <v>-105.207808</v>
+      </c>
+      <c r="H4" s="9">
+        <v>27.671703000000001</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="J4" s="8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="D5" s="16">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="E5" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="1">
-        <v>200</v>
-      </c>
-      <c r="G2" s="2">
-        <v>-105.1942667</v>
-      </c>
-      <c r="H2" s="2">
-        <v>27.7253583</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="1" t="s">
+      <c r="F5" s="14">
+        <v>400</v>
+      </c>
+      <c r="G5" s="9">
+        <v>-105.20411900000001</v>
+      </c>
+      <c r="H5" s="9">
+        <v>27.675628</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="J5" s="8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="D6" s="16">
+        <v>1.36</v>
+      </c>
+      <c r="E6" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="1">
-        <v>7.61</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" s="1">
-        <v>200</v>
-      </c>
-      <c r="G3" s="2">
-        <v>-105.193725</v>
-      </c>
-      <c r="H3" s="2">
-        <v>27.73255</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="1">
-        <v>8.1639999999999997</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" s="1">
-        <v>200</v>
-      </c>
-      <c r="G4" s="3">
-        <v>-105.19242103000001</v>
-      </c>
-      <c r="H4" s="3">
-        <v>27.737176049999999</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="1">
-        <v>10.53</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" s="1">
-        <v>200</v>
-      </c>
-      <c r="G5" s="3">
-        <v>-105.18438539</v>
-      </c>
-      <c r="H5" s="3">
-        <v>27.755246669999998</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="1">
-        <v>11.21</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" s="1">
-        <v>300</v>
-      </c>
-      <c r="G6" s="3">
-        <v>-105.18461035999999</v>
-      </c>
-      <c r="H6" s="3">
-        <v>27.761106130000002</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>17</v>
+      <c r="F6" s="14">
+        <v>400</v>
+      </c>
+      <c r="G6" s="9">
+        <v>-105.203367</v>
+      </c>
+      <c r="H6" s="9">
+        <v>27.677778</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="J6" s="8">
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" s="1">
-        <v>14.5</v>
-      </c>
-      <c r="E7" s="1" t="s">
+      <c r="A7" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="D7" s="16">
+        <v>1.36</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" s="14">
+        <v>400</v>
+      </c>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="J7" s="8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>175</v>
+      </c>
+      <c r="D8" s="16">
+        <v>1.37</v>
+      </c>
+      <c r="E8" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="1">
-        <v>200</v>
-      </c>
-      <c r="G7" s="3">
-        <v>-105.18494722</v>
-      </c>
-      <c r="H7" s="3">
-        <v>27.792011460000001</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" s="1">
-        <v>15.7</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F8" s="1">
-        <v>150</v>
-      </c>
-      <c r="G8" s="3">
-        <v>-105.18779438999999</v>
-      </c>
-      <c r="H8" s="3">
-        <v>27.801911499999999</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>29</v>
+      <c r="F8" s="14">
+        <v>400</v>
+      </c>
+      <c r="G8" s="9">
+        <v>-105.20357799999999</v>
+      </c>
+      <c r="H8" s="9">
+        <v>27.677810999999998</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="J8" s="18" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" s="1">
-        <v>16.41</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F9" s="1">
-        <v>150</v>
-      </c>
-      <c r="G9" s="3">
-        <v>-105.18806952</v>
-      </c>
-      <c r="H9" s="3">
-        <v>27.80784976</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="A9" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="D9" s="16">
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" s="14">
+        <v>400</v>
+      </c>
+      <c r="G9" s="9">
+        <v>-105.201308</v>
+      </c>
+      <c r="H9" s="9">
+        <v>27.685775</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="J9" s="8">
+        <v>14</v>
+      </c>
+      <c r="K9" s="7"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" s="1">
-        <v>17.32</v>
-      </c>
-      <c r="E10" s="1" t="s">
+      <c r="A10" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>379</v>
+      </c>
+      <c r="D10" s="16">
+        <v>2.286</v>
+      </c>
+      <c r="E10" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="1">
-        <v>300</v>
-      </c>
-      <c r="G10" s="3">
-        <v>-105.18725971000001</v>
-      </c>
-      <c r="H10" s="3">
-        <v>27.813766860000001</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>29</v>
+      <c r="F10" s="14">
+        <v>400</v>
+      </c>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="D11" s="1">
-        <v>17.600000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F11" s="1">
         <v>200</v>
       </c>
-      <c r="G11" s="3">
-        <v>-105.18745744</v>
-      </c>
-      <c r="H11" s="3">
-        <v>27.818471450000001</v>
-      </c>
-      <c r="I11" s="1" t="s">
+      <c r="G11" s="9">
+        <v>-105.1942667</v>
+      </c>
+      <c r="H11" s="9">
+        <v>27.7253583</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="J11" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="D12" s="1">
-        <v>19.96</v>
+        <v>7.61</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F12" s="1">
-        <v>300</v>
-      </c>
-      <c r="G12" s="3">
-        <v>-105.19613178</v>
-      </c>
-      <c r="H12" s="3">
-        <v>27.836371679999999</v>
-      </c>
-      <c r="I12" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="G12" s="9">
+        <v>-105.193725</v>
+      </c>
+      <c r="H12" s="9">
+        <v>27.73255</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="J12" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="D13" s="1">
-        <v>21.63</v>
+        <v>8.1639999999999997</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F13" s="1">
-        <v>300</v>
-      </c>
-      <c r="G13" s="3">
-        <v>-105.19996148</v>
-      </c>
-      <c r="H13" s="3">
-        <v>27.851017880000001</v>
-      </c>
-      <c r="I13" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="G13" s="9">
+        <v>-105.19242103000001</v>
+      </c>
+      <c r="H13" s="9">
+        <v>27.737176049999999</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="J13" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D14" s="1">
-        <v>22.21</v>
+        <v>10.53</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F14" s="1">
         <v>200</v>
       </c>
-      <c r="G14" s="3">
-        <v>-105.20323401</v>
-      </c>
-      <c r="H14" s="3">
-        <v>27.855245709999998</v>
-      </c>
-      <c r="I14" s="1" t="s">
+      <c r="G14" s="9">
+        <v>-105.18438539</v>
+      </c>
+      <c r="H14" s="9">
+        <v>27.755246669999998</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="J14" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="D15" s="1">
-        <v>23.07</v>
+        <v>11.21</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G15" s="3">
-        <v>-105.20883698999999</v>
-      </c>
-      <c r="H15" s="3">
-        <v>27.860102940000001</v>
-      </c>
-      <c r="I15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F15" s="1">
+        <v>300</v>
+      </c>
+      <c r="G15" s="9">
+        <v>-105.18461035999999</v>
+      </c>
+      <c r="H15" s="9">
+        <v>27.761106130000002</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="J15" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="D16" s="1">
-        <v>23.058</v>
+        <v>14.5</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="F16" s="1">
-        <v>6000</v>
-      </c>
-      <c r="G16" s="3">
-        <v>-105.20866902</v>
-      </c>
-      <c r="H16" s="3">
-        <v>27.859941670000001</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>16</v>
+        <v>200</v>
+      </c>
+      <c r="G16" s="9">
+        <v>-105.18494722</v>
+      </c>
+      <c r="H16" s="9">
+        <v>27.792011460000001</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>332</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>208</v>
+        <v>29</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D17" s="1">
-        <v>23.82</v>
+        <v>15.7</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F17" s="1">
         <v>150</v>
       </c>
-      <c r="G17" s="3">
-        <v>-105.20724140999999</v>
-      </c>
-      <c r="H17" s="3">
-        <v>27.866153499999999</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J17" s="1">
-        <v>3</v>
+      <c r="G17" s="9">
+        <v>-105.18779438999999</v>
+      </c>
+      <c r="H17" s="9">
+        <v>27.801911499999999</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="D18" s="1">
-        <v>24.898</v>
+        <v>16.41</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F18" s="1">
-        <v>300</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-105.20528398</v>
-      </c>
-      <c r="H18" s="3">
-        <v>27.874954580000001</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J18" s="1">
-        <v>3</v>
+        <v>150</v>
+      </c>
+      <c r="G18" s="9">
+        <v>-105.18806952</v>
+      </c>
+      <c r="H18" s="9">
+        <v>27.80784976</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>209</v>
+        <v>33</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="D19" s="1">
-        <v>26.51</v>
+        <v>17.32</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F19" s="1">
         <v>300</v>
       </c>
-      <c r="G19" s="3">
-        <v>-105.20948399</v>
-      </c>
-      <c r="H19" s="3">
-        <v>27.886966690000001</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J19" s="1">
-        <v>3</v>
+      <c r="G19" s="9">
+        <v>-105.18725971000001</v>
+      </c>
+      <c r="H19" s="9">
+        <v>27.813766860000001</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>210</v>
+        <v>35</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="D20" s="1">
-        <v>27.75</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="F20" s="1">
         <v>200</v>
       </c>
-      <c r="G20" s="3">
-        <v>-105.20854941</v>
-      </c>
-      <c r="H20" s="3">
-        <v>27.89642022</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J20" s="1">
-        <v>3</v>
+      <c r="G20" s="9">
+        <v>-105.18745744</v>
+      </c>
+      <c r="H20" s="9">
+        <v>27.818471450000001</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>211</v>
+        <v>37</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="D21" s="1">
-        <v>28.23</v>
+        <v>19.96</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F21" s="1">
-        <v>120</v>
-      </c>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J21" s="1">
-        <v>3</v>
+        <v>300</v>
+      </c>
+      <c r="G21" s="9">
+        <v>-105.19613178</v>
+      </c>
+      <c r="H21" s="9">
+        <v>27.836371679999999</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>212</v>
+        <v>39</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="D22" s="1">
-        <v>28.26</v>
+        <v>21.63</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="F22" s="1">
-        <v>200</v>
-      </c>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J22" s="1">
-        <v>3</v>
+        <v>300</v>
+      </c>
+      <c r="G22" s="9">
+        <v>-105.19996148</v>
+      </c>
+      <c r="H22" s="9">
+        <v>27.851017880000001</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>213</v>
+        <v>41</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="D23" s="1">
-        <v>31.6</v>
+        <v>22.21</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="F23" s="1">
         <v>200</v>
       </c>
-      <c r="G23" s="3">
-        <v>-105.22875037999999</v>
-      </c>
-      <c r="H23" s="3">
-        <v>27.922997729999999</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J23" s="1">
-        <v>3</v>
+      <c r="G23" s="9">
+        <v>-105.20323401</v>
+      </c>
+      <c r="H23" s="9">
+        <v>27.855245709999998</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>214</v>
+        <v>188</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="D24" s="1">
-        <v>32.51</v>
+        <v>23.82</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F24" s="1">
-        <v>200</v>
-      </c>
-      <c r="G24" s="3">
-        <v>-105.23515617</v>
-      </c>
-      <c r="H24" s="3">
-        <v>27.928090149999999</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>16</v>
+        <v>150</v>
+      </c>
+      <c r="G24" s="9">
+        <v>-105.20724140999999</v>
+      </c>
+      <c r="H24" s="9">
+        <v>27.866153499999999</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>332</v>
       </c>
       <c r="J24" s="1">
         <v>3</v>
@@ -2888,31 +3053,31 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>215</v>
+        <v>43</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="D25" s="1">
-        <v>33.340000000000003</v>
+        <v>24.898</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F25" s="1">
-        <v>150</v>
-      </c>
-      <c r="G25" s="3">
-        <v>-105.24074069</v>
-      </c>
-      <c r="H25" s="4">
-        <v>27.93214682</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>16</v>
+        <v>300</v>
+      </c>
+      <c r="G25" s="9">
+        <v>-105.20528398</v>
+      </c>
+      <c r="H25" s="9">
+        <v>27.874954580000001</v>
+      </c>
+      <c r="I25" s="8" t="s">
+        <v>332</v>
       </c>
       <c r="J25" s="1">
         <v>3</v>
@@ -2920,27 +3085,31 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>216</v>
+        <v>189</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="D26" s="1">
-        <v>33.4</v>
+        <v>26.51</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="F26" s="1">
-        <v>100</v>
-      </c>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="1" t="s">
-        <v>16</v>
+        <v>300</v>
+      </c>
+      <c r="G26" s="9">
+        <v>-105.20948399</v>
+      </c>
+      <c r="H26" s="9">
+        <v>27.886966690000001</v>
+      </c>
+      <c r="I26" s="8" t="s">
+        <v>332</v>
       </c>
       <c r="J26" s="1">
         <v>3</v>
@@ -2948,215 +3117,223 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>217</v>
+        <v>190</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="D27" s="1">
-        <v>34.020000000000003</v>
+        <v>27.75</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F27" s="1">
         <v>200</v>
       </c>
-      <c r="G27" s="3">
-        <v>-105.23723529999999</v>
-      </c>
-      <c r="H27" s="3">
-        <v>27.937600589999999</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>16</v>
+      <c r="G27" s="9">
+        <v>-105.20854941</v>
+      </c>
+      <c r="H27" s="9">
+        <v>27.89642022</v>
+      </c>
+      <c r="I27" s="8" t="s">
+        <v>332</v>
       </c>
       <c r="J27" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>218</v>
+        <v>191</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="D28" s="1">
-        <v>34.950000000000003</v>
+        <v>28.23</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F28" s="1">
-        <v>500</v>
-      </c>
-      <c r="G28" s="3">
-        <v>-105.23711435</v>
-      </c>
-      <c r="H28" s="3">
-        <v>27.947039289999999</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>16</v>
+        <v>120</v>
+      </c>
+      <c r="G28" s="9">
+        <v>-105.21288428</v>
+      </c>
+      <c r="H28" s="9">
+        <v>27.898625670000001</v>
+      </c>
+      <c r="I28" s="8" t="s">
+        <v>332</v>
       </c>
       <c r="J28" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>219</v>
+        <v>192</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="D29" s="1">
-        <v>34.96</v>
+        <v>28.26</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="F29" s="1">
-        <v>150</v>
-      </c>
-      <c r="G29" s="3">
-        <v>-105.23729136999999</v>
-      </c>
-      <c r="H29" s="3">
-        <v>27.94707365</v>
-      </c>
-      <c r="I29" s="1" t="s">
-        <v>16</v>
+        <v>200</v>
+      </c>
+      <c r="G29" s="9">
+        <v>-105.21814476</v>
+      </c>
+      <c r="H29" s="9">
+        <v>27.90179109</v>
+      </c>
+      <c r="I29" s="8" t="s">
+        <v>332</v>
       </c>
       <c r="J29" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>220</v>
+        <v>193</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="D30" s="1">
-        <v>36.6</v>
+        <v>31.6</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F30" s="1">
         <v>200</v>
       </c>
-      <c r="G30" s="3">
-        <v>-105.23754886</v>
-      </c>
-      <c r="H30" s="3">
-        <v>27.947098799999999</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>16</v>
+      <c r="G30" s="9">
+        <v>-105.22875037999999</v>
+      </c>
+      <c r="H30" s="9">
+        <v>27.922997729999999</v>
+      </c>
+      <c r="I30" s="8" t="s">
+        <v>332</v>
       </c>
       <c r="J30" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>221</v>
+        <v>194</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="D31" s="1">
-        <v>36.96</v>
+        <v>32.51</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F31" s="1">
-        <v>500</v>
-      </c>
-      <c r="G31" s="3"/>
-      <c r="H31" s="3"/>
-      <c r="I31" s="1" t="s">
-        <v>16</v>
+        <v>200</v>
+      </c>
+      <c r="G31" s="9">
+        <v>-105.23515617</v>
+      </c>
+      <c r="H31" s="9">
+        <v>27.928090149999999</v>
+      </c>
+      <c r="I31" s="8" t="s">
+        <v>332</v>
       </c>
       <c r="J31" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>222</v>
+        <v>195</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="D32" s="1">
-        <v>37.5</v>
+        <v>33.340000000000003</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="F32" s="1">
         <v>150</v>
       </c>
-      <c r="G32" s="3">
-        <v>-105.25980885</v>
-      </c>
-      <c r="H32" s="3">
-        <v>27.952508229999999</v>
-      </c>
-      <c r="I32" s="1" t="s">
-        <v>16</v>
+      <c r="G32" s="9">
+        <v>-105.24074069</v>
+      </c>
+      <c r="H32" s="9">
+        <v>27.93214682</v>
+      </c>
+      <c r="I32" s="8" t="s">
+        <v>332</v>
       </c>
       <c r="J32" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>223</v>
+        <v>196</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="D33" s="1">
-        <v>38</v>
+        <v>34.020000000000003</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>68</v>
+        <v>19</v>
       </c>
       <c r="F33" s="1">
-        <v>100</v>
-      </c>
-      <c r="G33" s="3"/>
-      <c r="H33" s="3"/>
-      <c r="I33" s="1" t="s">
-        <v>16</v>
+        <v>200</v>
+      </c>
+      <c r="G33" s="9">
+        <v>-105.23723529999999</v>
+      </c>
+      <c r="H33" s="9">
+        <v>27.937600589999999</v>
+      </c>
+      <c r="I33" s="8" t="s">
+        <v>332</v>
       </c>
       <c r="J33" s="1">
         <v>4</v>
@@ -3164,27 +3341,31 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>224</v>
+        <v>333</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>69</v>
+        <v>334</v>
       </c>
       <c r="D34" s="1">
-        <v>38.299999999999997</v>
+        <v>34.950000000000003</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>68</v>
+        <v>15</v>
       </c>
       <c r="F34" s="1">
-        <v>80</v>
-      </c>
-      <c r="G34" s="3"/>
-      <c r="H34" s="3"/>
-      <c r="I34" s="1" t="s">
-        <v>16</v>
+        <v>500</v>
+      </c>
+      <c r="G34" s="9">
+        <v>-105.23711433</v>
+      </c>
+      <c r="H34" s="9">
+        <v>27.947039270000001</v>
+      </c>
+      <c r="I34" s="8" t="s">
+        <v>332</v>
       </c>
       <c r="J34" s="1">
         <v>4</v>
@@ -3192,27 +3373,31 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>225</v>
+        <v>197</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="D35" s="1">
-        <v>38.67</v>
+        <v>34.951999999999998</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>68</v>
+        <v>15</v>
       </c>
       <c r="F35" s="1">
-        <v>40</v>
-      </c>
-      <c r="G35" s="3"/>
-      <c r="H35" s="3"/>
-      <c r="I35" s="1" t="s">
-        <v>16</v>
+        <v>500</v>
+      </c>
+      <c r="G35" s="9">
+        <v>-105.23711435</v>
+      </c>
+      <c r="H35" s="9">
+        <v>27.947039289999999</v>
+      </c>
+      <c r="I35" s="8" t="s">
+        <v>332</v>
       </c>
       <c r="J35" s="1">
         <v>4</v>
@@ -3220,31 +3405,31 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>226</v>
+        <v>198</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>71</v>
+        <v>335</v>
       </c>
       <c r="D36" s="1">
-        <v>38.799999999999997</v>
+        <v>34.979999999999997</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="F36" s="1">
-        <v>300</v>
-      </c>
-      <c r="G36" s="3">
-        <v>-105.27104099</v>
-      </c>
-      <c r="H36" s="3">
-        <v>27.956860160000002</v>
-      </c>
-      <c r="I36" s="1" t="s">
-        <v>16</v>
+        <v>150</v>
+      </c>
+      <c r="G36" s="9">
+        <v>-105.23729136999999</v>
+      </c>
+      <c r="H36" s="9">
+        <v>27.94707365</v>
+      </c>
+      <c r="I36" s="8" t="s">
+        <v>332</v>
       </c>
       <c r="J36" s="1">
         <v>4</v>
@@ -3252,27 +3437,31 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>227</v>
+        <v>199</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="D37" s="1">
-        <v>38.94</v>
+        <v>36.6</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>68</v>
+        <v>19</v>
       </c>
       <c r="F37" s="1">
-        <v>40</v>
-      </c>
-      <c r="G37" s="3"/>
-      <c r="H37" s="3"/>
-      <c r="I37" s="1" t="s">
-        <v>16</v>
+        <v>200</v>
+      </c>
+      <c r="G37" s="9">
+        <v>-105.23754886</v>
+      </c>
+      <c r="H37" s="9">
+        <v>27.947098799999999</v>
+      </c>
+      <c r="I37" s="8" t="s">
+        <v>332</v>
       </c>
       <c r="J37" s="1">
         <v>4</v>
@@ -3280,27 +3469,31 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>228</v>
+        <v>200</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="D38" s="1">
-        <v>39.04</v>
+        <v>36.96</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>68</v>
+        <v>15</v>
       </c>
       <c r="F38" s="1">
-        <v>40</v>
-      </c>
-      <c r="G38" s="3"/>
-      <c r="H38" s="3"/>
-      <c r="I38" s="1" t="s">
-        <v>16</v>
+        <v>500</v>
+      </c>
+      <c r="G38" s="9">
+        <v>-105.25444519</v>
+      </c>
+      <c r="H38" s="9">
+        <v>27.95329546</v>
+      </c>
+      <c r="I38" s="8" t="s">
+        <v>332</v>
       </c>
       <c r="J38" s="1">
         <v>4</v>
@@ -3308,383 +3501,415 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>229</v>
+        <v>201</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="D39" s="1">
-        <v>39.270000000000003</v>
+        <v>37.5</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="F39" s="1">
-        <v>40</v>
-      </c>
-      <c r="G39" s="3"/>
-      <c r="H39" s="3"/>
-      <c r="I39" s="1" t="s">
-        <v>16</v>
+        <v>150</v>
+      </c>
+      <c r="G39" s="9">
+        <v>-105.25980885</v>
+      </c>
+      <c r="H39" s="9">
+        <v>27.952508229999999</v>
+      </c>
+      <c r="I39" s="8" t="s">
+        <v>332</v>
       </c>
       <c r="J39" s="1">
         <v>4</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="B40" s="1" t="s">
+      <c r="A40" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="B40" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C40" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="D40" s="1">
-        <v>39.78</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F40" s="1">
+      <c r="C40" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D40" s="8">
+        <v>38</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F40" s="8">
         <v>100</v>
       </c>
-      <c r="G40" s="3"/>
-      <c r="H40" s="3"/>
-      <c r="I40" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J40" s="1">
+      <c r="G40" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="H40" s="9" t="s">
+        <v>337</v>
+      </c>
+      <c r="I40" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="J40" s="8">
         <v>4</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="B41" s="1" t="s">
+      <c r="A41" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="B41" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C41" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="D41" s="1">
-        <v>39.79</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="F41" s="1">
+      <c r="C41" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D41" s="8">
+        <v>38.299999999999997</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F41" s="8">
+        <v>80</v>
+      </c>
+      <c r="G41" s="9" t="s">
+        <v>338</v>
+      </c>
+      <c r="H41" s="9" t="s">
+        <v>339</v>
+      </c>
+      <c r="I41" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="J41" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="D42" s="8">
+        <v>38.67</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F42" s="8">
         <v>40</v>
       </c>
-      <c r="G41" s="3"/>
-      <c r="H41" s="3"/>
-      <c r="I41" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J41" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="D42" s="1">
-        <v>40.06</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="F42" s="1">
-        <v>60</v>
-      </c>
-      <c r="G42" s="3"/>
-      <c r="H42" s="3"/>
-      <c r="I42" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J42" s="1">
+      <c r="G42" s="9" t="s">
+        <v>340</v>
+      </c>
+      <c r="H42" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="I42" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="J42" s="8">
         <v>4</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>233</v>
+        <v>205</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="D43" s="1">
-        <v>40.26</v>
+        <v>38.799999999999997</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F43" s="1">
-        <v>400</v>
-      </c>
-      <c r="G43" s="3">
-        <v>-105.28063009</v>
-      </c>
-      <c r="H43" s="3">
-        <v>27.966191599999998</v>
-      </c>
-      <c r="I43" s="1" t="s">
-        <v>16</v>
+        <v>300</v>
+      </c>
+      <c r="G43" s="9">
+        <v>-105.27104099</v>
+      </c>
+      <c r="H43" s="9">
+        <v>27.956860160000002</v>
+      </c>
+      <c r="I43" s="8" t="s">
+        <v>332</v>
       </c>
       <c r="J43" s="1">
         <v>4</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="B44" s="1" t="s">
+      <c r="A44" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="B44" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C44" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D44" s="1">
-        <v>41.08</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F44" s="1">
-        <v>150</v>
-      </c>
-      <c r="G44" s="3"/>
-      <c r="H44" s="3"/>
-      <c r="I44" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J44" s="1">
-        <v>5</v>
+      <c r="C44" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D44" s="8">
+        <v>38.94</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F44" s="8">
+        <v>40</v>
+      </c>
+      <c r="G44" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="H44" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="I44" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="J44" s="8">
+        <v>4</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="B45" s="1" t="s">
+      <c r="A45" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="B45" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C45" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D45" s="1">
-        <v>41.91</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F45" s="1">
-        <v>400</v>
-      </c>
-      <c r="G45" s="3">
-        <v>-105.2903634</v>
-      </c>
-      <c r="H45" s="3">
-        <v>27.978049729999999</v>
-      </c>
-      <c r="I45" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J45" s="1">
-        <v>5</v>
+      <c r="C45" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="D45" s="8">
+        <v>39.04</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F45" s="8">
+        <v>40</v>
+      </c>
+      <c r="G45" s="9" t="s">
+        <v>344</v>
+      </c>
+      <c r="H45" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="I45" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="J45" s="8">
+        <v>4</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="B46" s="1" t="s">
+      <c r="A46" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="B46" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C46" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D46" s="1">
-        <v>42.26</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F46" s="1">
-        <v>200</v>
-      </c>
-      <c r="G46" s="3"/>
-      <c r="H46" s="3"/>
-      <c r="I46" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J46" s="1">
-        <v>5</v>
+      <c r="C46" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D46" s="8">
+        <v>39.270000000000003</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F46" s="8">
+        <v>40</v>
+      </c>
+      <c r="G46" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="H46" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="I46" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="J46" s="8">
+        <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>237</v>
+        <v>209</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="D47" s="1">
-        <v>42.99</v>
+        <v>39.78</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F47" s="1">
-        <v>200</v>
-      </c>
-      <c r="G47" s="3"/>
-      <c r="H47" s="3"/>
-      <c r="I47" s="1" t="s">
-        <v>16</v>
+        <v>100</v>
+      </c>
+      <c r="G47" s="9">
+        <v>-105.27726006</v>
+      </c>
+      <c r="H47" s="9">
+        <v>27.962909499999999</v>
+      </c>
+      <c r="I47" s="8" t="s">
+        <v>332</v>
       </c>
       <c r="J47" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="B48" s="1" t="s">
+      <c r="A48" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="B48" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C48" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D48" s="1">
-        <v>43.36</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F48" s="1">
-        <v>200</v>
-      </c>
-      <c r="G48" s="3">
-        <v>-105.29749196</v>
-      </c>
-      <c r="H48" s="3">
-        <v>27.988156709999998</v>
-      </c>
-      <c r="I48" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J48" s="1">
-        <v>5</v>
+      <c r="C48" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="D48" s="8">
+        <v>39.79</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F48" s="8">
+        <v>40</v>
+      </c>
+      <c r="G48" s="9" t="s">
+        <v>348</v>
+      </c>
+      <c r="H48" s="9" t="s">
+        <v>349</v>
+      </c>
+      <c r="I48" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="J48" s="8">
+        <v>4</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="B49" s="1" t="s">
+      <c r="A49" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="B49" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C49" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="D49" s="1">
-        <v>43.71</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F49" s="1">
-        <v>400</v>
-      </c>
-      <c r="G49" s="3">
-        <v>-105.30043954</v>
-      </c>
-      <c r="H49" s="3">
-        <v>27.991423139999998</v>
-      </c>
-      <c r="I49" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J49" s="1">
-        <v>5</v>
+      <c r="C49" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="D49" s="8">
+        <v>40.06</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F49" s="8">
+        <v>60</v>
+      </c>
+      <c r="G49" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="H49" s="9" t="s">
+        <v>351</v>
+      </c>
+      <c r="I49" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="J49" s="8">
+        <v>4</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>240</v>
+        <v>212</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="D50" s="1">
-        <v>43.74</v>
+        <v>40.26</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F50" s="1">
-        <v>150</v>
-      </c>
-      <c r="G50" s="3"/>
-      <c r="H50" s="3"/>
-      <c r="I50" s="1" t="s">
-        <v>16</v>
+        <v>400</v>
+      </c>
+      <c r="G50" s="9">
+        <v>-105.28063009</v>
+      </c>
+      <c r="H50" s="9">
+        <v>27.966191599999998</v>
+      </c>
+      <c r="I50" s="8" t="s">
+        <v>332</v>
       </c>
       <c r="J50" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>241</v>
+        <v>213</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="D51" s="1">
-        <v>44.54</v>
+        <v>41.08</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F51" s="1">
         <v>150</v>
       </c>
-      <c r="G51" s="3">
-        <v>-105.30767815</v>
-      </c>
-      <c r="H51" s="3">
-        <v>27.989236139999999</v>
-      </c>
-      <c r="I51" s="1" t="s">
-        <v>16</v>
+      <c r="G51" s="9">
+        <v>-105.28573684</v>
+      </c>
+      <c r="H51" s="9">
+        <v>27.97063627</v>
+      </c>
+      <c r="I51" s="8" t="s">
+        <v>332</v>
       </c>
       <c r="J51" s="1">
         <v>5</v>
@@ -3692,31 +3917,31 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>242</v>
+        <v>214</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="D52" s="1">
-        <v>44.95</v>
+        <v>41.91</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F52" s="1">
-        <v>200</v>
-      </c>
-      <c r="G52" s="3">
-        <v>-105.31295607</v>
-      </c>
-      <c r="H52" s="3">
-        <v>27.99550035</v>
-      </c>
-      <c r="I52" s="1" t="s">
-        <v>16</v>
+        <v>400</v>
+      </c>
+      <c r="G52" s="9">
+        <v>-105.2903634</v>
+      </c>
+      <c r="H52" s="9">
+        <v>27.978049729999999</v>
+      </c>
+      <c r="I52" s="8" t="s">
+        <v>332</v>
       </c>
       <c r="J52" s="1">
         <v>5</v>
@@ -3724,31 +3949,31 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>243</v>
+        <v>215</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="D53" s="1">
-        <v>46.5</v>
+        <v>42.26</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="F53" s="1">
-        <v>600</v>
-      </c>
-      <c r="G53" s="3">
-        <v>-105.31206826</v>
-      </c>
-      <c r="H53" s="3">
-        <v>28.000137890000001</v>
-      </c>
-      <c r="I53" s="1" t="s">
-        <v>16</v>
+        <v>200</v>
+      </c>
+      <c r="G53" s="9">
+        <v>-105.29259601</v>
+      </c>
+      <c r="H53" s="9">
+        <v>27.980258190000001</v>
+      </c>
+      <c r="I53" s="8" t="s">
+        <v>332</v>
       </c>
       <c r="J53" s="1">
         <v>5</v>
@@ -3756,27 +3981,31 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>244</v>
+        <v>216</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="D54" s="1">
-        <v>47.64</v>
+        <v>42.99</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F54" s="1">
         <v>200</v>
       </c>
-      <c r="G54" s="3"/>
-      <c r="H54" s="3"/>
-      <c r="I54" s="1" t="s">
-        <v>16</v>
+      <c r="G54" s="9" t="s">
+        <v>352</v>
+      </c>
+      <c r="H54" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="I54" s="8" t="s">
+        <v>332</v>
       </c>
       <c r="J54" s="1">
         <v>5</v>
@@ -3784,295 +4013,319 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>245</v>
+        <v>217</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>360</v>
+        <v>13</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="D55" s="1">
-        <v>48.42</v>
+        <v>43.36</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="F55" s="1">
-        <v>800</v>
-      </c>
-      <c r="G55" s="3">
-        <v>-105.3240962</v>
-      </c>
-      <c r="H55" s="3">
-        <v>28.012186960000001</v>
-      </c>
-      <c r="I55" s="1" t="s">
-        <v>150</v>
+        <v>200</v>
+      </c>
+      <c r="G55" s="9">
+        <v>-105.29749196</v>
+      </c>
+      <c r="H55" s="9">
+        <v>27.988156709999998</v>
+      </c>
+      <c r="I55" s="8" t="s">
+        <v>332</v>
       </c>
       <c r="J55" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>246</v>
+        <v>218</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>360</v>
+        <v>13</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="D56" s="1">
-        <v>49.87</v>
+        <v>43.71</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G56" s="3"/>
-      <c r="H56" s="3"/>
-      <c r="I56" s="1" t="s">
-        <v>150</v>
+        <v>15</v>
+      </c>
+      <c r="F56" s="1">
+        <v>400</v>
+      </c>
+      <c r="G56" s="9">
+        <v>-105.30043954</v>
+      </c>
+      <c r="H56" s="9">
+        <v>27.991423139999998</v>
+      </c>
+      <c r="I56" s="8" t="s">
+        <v>332</v>
       </c>
       <c r="J56" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>247</v>
+        <v>219</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>360</v>
+        <v>13</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="D57" s="1">
-        <v>55.37</v>
+        <v>43.74</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G57" s="3">
-        <v>-105.35649905</v>
-      </c>
-      <c r="H57" s="3">
-        <v>28.054997449999998</v>
-      </c>
-      <c r="I57" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F57" s="1">
         <v>150</v>
       </c>
+      <c r="G57" s="9">
+        <v>-105.30089099</v>
+      </c>
+      <c r="H57" s="9">
+        <v>27.991641319999999</v>
+      </c>
+      <c r="I57" s="8" t="s">
+        <v>332</v>
+      </c>
       <c r="J57" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>248</v>
+        <v>220</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>360</v>
+        <v>13</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="D58" s="1">
-        <v>57.29</v>
+        <v>44.54</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G58" s="3"/>
-      <c r="H58" s="3"/>
-      <c r="I58" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F58" s="1">
         <v>150</v>
       </c>
+      <c r="G58" s="9">
+        <v>-105.30767815</v>
+      </c>
+      <c r="H58" s="9">
+        <v>27.989236139999999</v>
+      </c>
+      <c r="I58" s="8" t="s">
+        <v>332</v>
+      </c>
       <c r="J58" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>249</v>
+        <v>354</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>360</v>
+        <v>13</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>94</v>
+        <v>355</v>
       </c>
       <c r="D59" s="1">
-        <v>62.16</v>
+        <v>44.8</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G59" s="3">
-        <v>-105.39453444999999</v>
-      </c>
-      <c r="H59" s="3">
-        <v>28.082670799999999</v>
-      </c>
-      <c r="I59" s="1" t="s">
-        <v>150</v>
+        <v>19</v>
+      </c>
+      <c r="F59" s="1">
+        <v>200</v>
+      </c>
+      <c r="G59" s="9">
+        <v>-105.31023949</v>
+      </c>
+      <c r="H59" s="9">
+        <v>27.9891431</v>
+      </c>
+      <c r="I59" s="8" t="s">
+        <v>332</v>
       </c>
       <c r="J59" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>250</v>
+        <v>221</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>360</v>
+        <v>13</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="D60" s="1">
-        <v>49.04</v>
+        <v>44.95</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="F60" s="1">
-        <v>800</v>
-      </c>
-      <c r="G60" s="3">
-        <v>-105.32486768</v>
-      </c>
-      <c r="H60" s="3">
-        <v>28.016605810000001</v>
-      </c>
-      <c r="I60" s="1" t="s">
-        <v>150</v>
+        <v>200</v>
+      </c>
+      <c r="G60" s="9">
+        <v>-105.31295607</v>
+      </c>
+      <c r="H60" s="9">
+        <v>27.99550035</v>
+      </c>
+      <c r="I60" s="8" t="s">
+        <v>332</v>
       </c>
       <c r="J60" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>251</v>
+        <v>222</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>360</v>
+        <v>13</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="D61" s="1">
-        <v>49.64</v>
+        <v>46.5</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F61" s="1">
-        <v>400</v>
-      </c>
-      <c r="G61" s="3">
-        <v>-105.32485167</v>
-      </c>
-      <c r="H61" s="3">
-        <v>28.021578210000001</v>
-      </c>
-      <c r="I61" s="1" t="s">
-        <v>150</v>
+        <v>600</v>
+      </c>
+      <c r="G61" s="9">
+        <v>-105.31206826</v>
+      </c>
+      <c r="H61" s="9">
+        <v>28.000137890000001</v>
+      </c>
+      <c r="I61" s="8" t="s">
+        <v>332</v>
       </c>
       <c r="J61" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D62" s="1">
-        <v>49.7</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F62" s="1">
-        <v>150</v>
-      </c>
-      <c r="G62" s="3">
-        <v>-105.32513062</v>
-      </c>
-      <c r="H62" s="3">
-        <v>28.022209700000001</v>
-      </c>
-      <c r="I62" s="1" t="s">
-        <v>150</v>
+      <c r="A62" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="B62" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="D62" s="8">
+        <v>47.64</v>
+      </c>
+      <c r="E62" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F62" s="8">
+        <v>200</v>
+      </c>
+      <c r="G62" s="9" t="s">
+        <v>356</v>
+      </c>
+      <c r="H62" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="I62" s="8" t="s">
+        <v>332</v>
       </c>
       <c r="J62" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>253</v>
+        <v>224</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="D63" s="1">
-        <v>49.87</v>
+        <v>48.42</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="F63" s="1">
-        <v>120</v>
-      </c>
-      <c r="G63" s="3"/>
-      <c r="H63" s="3"/>
+        <v>800</v>
+      </c>
+      <c r="G63" s="9">
+        <v>-105.3240962</v>
+      </c>
+      <c r="H63" s="9">
+        <v>28.012186960000001</v>
+      </c>
       <c r="I63" s="1" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="J63" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>254</v>
+        <v>229</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>360</v>
+        <v>331</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="D64" s="1">
-        <v>50.5</v>
+        <v>49.04</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="F64" s="1">
-        <v>100</v>
-      </c>
-      <c r="G64" s="3">
-        <v>-105.33104413</v>
-      </c>
-      <c r="H64" s="3">
-        <v>28.026579439999999</v>
+        <v>800</v>
+      </c>
+      <c r="G64" s="9">
+        <v>-105.32486768</v>
+      </c>
+      <c r="H64" s="9">
+        <v>28.016605810000001</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="J64" s="1">
         <v>6</v>
@@ -4080,31 +4333,31 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>255</v>
+        <v>230</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>360</v>
+        <v>331</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="D65" s="1">
-        <v>51.09</v>
+        <v>49.64</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="F65" s="1">
-        <v>150</v>
-      </c>
-      <c r="G65" s="3">
-        <v>-105.33677668</v>
-      </c>
-      <c r="H65" s="3">
-        <v>28.028726209999999</v>
+        <v>400</v>
+      </c>
+      <c r="G65" s="9">
+        <v>-105.32485167</v>
+      </c>
+      <c r="H65" s="9">
+        <v>28.021578210000001</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="J65" s="1">
         <v>6</v>
@@ -4112,127 +4365,127 @@
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>256</v>
+        <v>231</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>360</v>
+        <v>331</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="D66" s="1">
-        <v>52.36</v>
+        <v>49.7</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="F66" s="1">
-        <v>100</v>
-      </c>
-      <c r="G66" s="3">
-        <v>-105.33835558</v>
-      </c>
-      <c r="H66" s="3">
-        <v>28.037389829999999</v>
+        <v>150</v>
+      </c>
+      <c r="G66" s="9">
+        <v>-105.32513062</v>
+      </c>
+      <c r="H66" s="9">
+        <v>28.022209700000001</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="J66" s="1">
         <v>6</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="D67" s="1">
-        <v>50.9</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F67" s="1">
-        <v>150</v>
-      </c>
-      <c r="G67" s="3">
-        <v>-105.33761831</v>
-      </c>
-      <c r="H67" s="3">
-        <v>28.041947489999998</v>
-      </c>
-      <c r="I67" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="J67" s="1">
+      <c r="A67" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="B67" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="C67" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="D67" s="8">
+        <v>49.87</v>
+      </c>
+      <c r="E67" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F67" s="8">
+        <v>120</v>
+      </c>
+      <c r="G67" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="H67" s="9" t="s">
+        <v>365</v>
+      </c>
+      <c r="I67" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="J67" s="8">
         <v>6</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>258</v>
+        <v>225</v>
       </c>
       <c r="B68" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D68" s="1">
+        <v>49.872</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F68" s="1">
+        <v>600</v>
+      </c>
+      <c r="G68" s="9" t="s">
         <v>360</v>
       </c>
-      <c r="C68" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="D68" s="1">
-        <v>53.14</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F68" s="1">
-        <v>150</v>
-      </c>
-      <c r="G68" s="3">
-        <v>-105.33914449</v>
-      </c>
-      <c r="H68" s="3">
-        <v>28.043404020000001</v>
+      <c r="H68" s="9" t="s">
+        <v>361</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="J68" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>259</v>
+        <v>233</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>360</v>
+        <v>331</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="D69" s="1">
-        <v>53.38</v>
+        <v>50.5</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="F69" s="1">
-        <v>250</v>
-      </c>
-      <c r="G69" s="3">
-        <v>-105.34160726</v>
-      </c>
-      <c r="H69" s="3">
-        <v>28.044510509999999</v>
+        <v>100</v>
+      </c>
+      <c r="G69" s="9">
+        <v>-105.33104413</v>
+      </c>
+      <c r="H69" s="9">
+        <v>28.026579439999999</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="J69" s="1">
         <v>6</v>
@@ -4240,28 +4493,31 @@
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>260</v>
+        <v>236</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>360</v>
+        <v>331</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="D70" s="1">
-        <v>53.9</v>
+        <v>50.9</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G70" s="3">
-        <v>-105.34165914</v>
-      </c>
-      <c r="H70" s="3">
-        <v>28.044526940000001</v>
+        <v>48</v>
+      </c>
+      <c r="F70" s="1">
+        <v>150</v>
+      </c>
+      <c r="G70" s="9">
+        <v>-105.33761831</v>
+      </c>
+      <c r="H70" s="9">
+        <v>28.041947489999998</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="J70" s="1">
         <v>6</v>
@@ -4269,31 +4525,31 @@
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>261</v>
+        <v>234</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>360</v>
+        <v>331</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="D71" s="1">
-        <v>54.41</v>
+        <v>51.09</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="F71" s="1">
-        <v>100</v>
-      </c>
-      <c r="G71" s="3">
-        <v>-105.34921065</v>
-      </c>
-      <c r="H71" s="3">
-        <v>28.05042461</v>
+        <v>150</v>
+      </c>
+      <c r="G71" s="9">
+        <v>-105.33677668</v>
+      </c>
+      <c r="H71" s="9">
+        <v>28.028726209999999</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="J71" s="1">
         <v>6</v>
@@ -4301,31 +4557,31 @@
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>262</v>
+        <v>235</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>360</v>
+        <v>331</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="D72" s="1">
-        <v>55.03</v>
+        <v>52.36</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="F72" s="1">
         <v>100</v>
       </c>
-      <c r="G72" s="3">
-        <v>-105.35306607</v>
-      </c>
-      <c r="H72" s="3">
-        <v>28.054693180000001</v>
+      <c r="G72" s="9">
+        <v>-105.33835558</v>
+      </c>
+      <c r="H72" s="9">
+        <v>28.037389829999999</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="J72" s="1">
         <v>6</v>
@@ -4333,31 +4589,31 @@
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>263</v>
+        <v>237</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>360</v>
+        <v>331</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="D73" s="1">
-        <v>55.36</v>
+        <v>53.14</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="F73" s="1">
-        <v>500</v>
-      </c>
-      <c r="G73" s="3">
-        <v>-105.35636175</v>
-      </c>
-      <c r="H73" s="3">
-        <v>28.054971210000001</v>
+        <v>150</v>
+      </c>
+      <c r="G73" s="9">
+        <v>-105.33914449</v>
+      </c>
+      <c r="H73" s="9">
+        <v>28.043404020000001</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="J73" s="1">
         <v>6</v>
@@ -4365,31 +4621,31 @@
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>264</v>
+        <v>238</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>360</v>
+        <v>331</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="D74" s="1">
-        <v>55.37</v>
+        <v>53.38</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>110</v>
+        <v>15</v>
       </c>
       <c r="F74" s="1">
-        <v>400</v>
-      </c>
-      <c r="G74" s="3">
-        <v>-105.35649905</v>
-      </c>
-      <c r="H74" s="3">
-        <v>28.054997449999998</v>
+        <v>250</v>
+      </c>
+      <c r="G74" s="9">
+        <v>-105.34160726</v>
+      </c>
+      <c r="H74" s="9">
+        <v>28.044510509999999</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="J74" s="1">
         <v>6</v>
@@ -4397,184 +4653,191 @@
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>265</v>
+        <v>239</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>360</v>
+        <v>331</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="D75" s="1">
-        <v>56.36</v>
+        <v>53.9</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="F75" s="1">
-        <v>200</v>
-      </c>
-      <c r="G75" s="3">
-        <v>-105.35787544</v>
-      </c>
-      <c r="H75" s="3">
-        <v>28.062200019999999</v>
+        <v>350</v>
+      </c>
+      <c r="G75" s="9">
+        <v>-105.34165914</v>
+      </c>
+      <c r="H75" s="9">
+        <v>28.044526940000001</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="J75" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>266</v>
+        <v>240</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>360</v>
+        <v>331</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="D76" s="1">
-        <v>56.36</v>
+        <v>54.41</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="F76" s="1">
         <v>100</v>
       </c>
-      <c r="G76" s="3">
-        <v>-105.35785373</v>
-      </c>
-      <c r="H76" s="3">
-        <v>28.062313</v>
+      <c r="G76" s="9">
+        <v>-105.34921065</v>
+      </c>
+      <c r="H76" s="9">
+        <v>28.05042461</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="J76" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>267</v>
+        <v>241</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>360</v>
+        <v>331</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="D77" s="1">
-        <v>57.14</v>
+        <v>55.03</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="F77" s="1">
-        <v>700</v>
-      </c>
-      <c r="G77" s="3">
-        <v>-105.36198308</v>
-      </c>
-      <c r="H77" s="3">
-        <v>28.068257030000002</v>
+        <v>100</v>
+      </c>
+      <c r="G77" s="9">
+        <v>-105.35306607</v>
+      </c>
+      <c r="H77" s="9">
+        <v>28.054693180000001</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="J77" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>268</v>
+        <v>242</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="D78" s="1">
-        <v>57.15</v>
+        <v>55.36</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G78" s="3">
-        <v>-105.36214425999999</v>
-      </c>
-      <c r="H78" s="3">
-        <v>28.068353170000002</v>
+        <v>48</v>
+      </c>
+      <c r="F78" s="1">
+        <v>500</v>
+      </c>
+      <c r="G78" s="9">
+        <v>-105.35636175</v>
+      </c>
+      <c r="H78" s="9">
+        <v>28.054971210000001</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="J78" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>269</v>
+        <v>226</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>115</v>
+        <v>358</v>
+      </c>
+      <c r="C79" s="10" t="s">
+        <v>83</v>
       </c>
       <c r="D79" s="1">
-        <v>57.29</v>
+        <v>55.37</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="F79" s="1">
-        <v>120</v>
-      </c>
-      <c r="G79" s="3"/>
-      <c r="H79" s="3"/>
+        <v>600</v>
+      </c>
+      <c r="G79" s="9">
+        <v>-105.35649905</v>
+      </c>
+      <c r="H79" s="9">
+        <v>28.054997449999998</v>
+      </c>
       <c r="I79" s="1" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="J79" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>270</v>
+        <v>243</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>360</v>
+        <v>331</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="D80" s="1">
-        <v>58.6</v>
+        <v>56.36</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="F80" s="1">
-        <v>150</v>
-      </c>
-      <c r="G80" s="3">
-        <v>-105.37317283</v>
-      </c>
-      <c r="H80" s="3">
-        <v>28.06971858</v>
+        <v>200</v>
+      </c>
+      <c r="G80" s="9">
+        <v>-105.35787544</v>
+      </c>
+      <c r="H80" s="9">
+        <v>28.062200019999999</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="J80" s="1">
         <v>7</v>
@@ -4582,28 +4845,31 @@
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>271</v>
+        <v>244</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>360</v>
+        <v>331</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="D81" s="1">
-        <v>58.76</v>
+        <v>56.36</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-105.3748234</v>
-      </c>
-      <c r="H81" s="3">
-        <v>28.070505730000001</v>
+        <v>48</v>
+      </c>
+      <c r="F81" s="1">
+        <v>100</v>
+      </c>
+      <c r="G81" s="9">
+        <v>-105.35785373</v>
+      </c>
+      <c r="H81" s="9">
+        <v>28.062313</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="J81" s="1">
         <v>7</v>
@@ -4611,28 +4877,31 @@
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>272</v>
+        <v>245</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>360</v>
+        <v>331</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="D82" s="1">
-        <v>58.78</v>
+        <v>57.14</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="G82" s="3">
-        <v>-105.38349196</v>
-      </c>
-      <c r="H82" s="3">
-        <v>28.068821799999998</v>
+        <v>15</v>
+      </c>
+      <c r="F82" s="1">
+        <v>700</v>
+      </c>
+      <c r="G82" s="9">
+        <v>-105.36198308</v>
+      </c>
+      <c r="H82" s="9">
+        <v>28.068257030000002</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="J82" s="1">
         <v>7</v>
@@ -4640,120 +4909,127 @@
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>273</v>
+        <v>246</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>360</v>
+        <v>331</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="D83" s="1">
-        <v>60.3</v>
+        <v>57.15</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="F83" s="1">
-        <v>100</v>
-      </c>
-      <c r="G83" s="3">
-        <v>-105.38525518</v>
-      </c>
-      <c r="H83" s="3">
-        <v>28.073751619999999</v>
+        <v>500</v>
+      </c>
+      <c r="G83" s="9">
+        <v>-105.36214425999999</v>
+      </c>
+      <c r="H83" s="9">
+        <v>28.068353170000002</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="J83" s="1">
         <v>7</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A84" s="1" t="s">
-        <v>274</v>
+      <c r="A84" s="8" t="s">
+        <v>227</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="C84" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="C84" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D84" s="8">
+        <v>57.29</v>
+      </c>
+      <c r="E84" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F84" s="8">
+        <v>600</v>
+      </c>
+      <c r="G84" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="H84" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="I84" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="J84" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A85" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="B85" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="C85" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="D85" s="8">
+        <v>57.29</v>
+      </c>
+      <c r="E85" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F85" s="8">
         <v>120</v>
       </c>
-      <c r="D84" s="1">
-        <v>61.03</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F84" s="1">
-        <v>200</v>
-      </c>
-      <c r="G84" s="3">
-        <v>-105.3870215</v>
-      </c>
-      <c r="H84" s="3">
-        <v>28.080127730000001</v>
-      </c>
-      <c r="I84" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="J84" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A85" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="B85" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="D85" s="1">
-        <v>62.16</v>
-      </c>
-      <c r="E85" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="G85" s="3"/>
-      <c r="H85" s="3"/>
-      <c r="I85" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="J85" s="1">
+      <c r="G85" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="H85" s="9" t="s">
+        <v>367</v>
+      </c>
+      <c r="I85" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="J85" s="8">
         <v>7</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>276</v>
+        <v>248</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>360</v>
+        <v>331</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="D86" s="1">
-        <v>62.63</v>
+        <v>58.6</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="F86" s="1">
-        <v>100</v>
-      </c>
-      <c r="G86" s="3">
-        <v>-105.39425558000001</v>
-      </c>
-      <c r="H86" s="3">
-        <v>28.087006259999999</v>
+        <v>150</v>
+      </c>
+      <c r="G86" s="9">
+        <v>-105.37317283</v>
+      </c>
+      <c r="H86" s="9">
+        <v>28.06971858</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="J86" s="1">
         <v>7</v>
@@ -4761,24 +5037,31 @@
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>277</v>
+        <v>249</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>360</v>
+        <v>331</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="D87" s="1">
-        <v>63.71</v>
+        <v>58.76</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G87" s="3"/>
-      <c r="H87" s="3"/>
+        <v>48</v>
+      </c>
+      <c r="F87" s="1">
+        <v>500</v>
+      </c>
+      <c r="G87" s="9">
+        <v>-105.3748234</v>
+      </c>
+      <c r="H87" s="9">
+        <v>28.070505730000001</v>
+      </c>
       <c r="I87" s="1" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="J87" s="1">
         <v>7</v>
@@ -4786,31 +5069,31 @@
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>278</v>
+        <v>250</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>360</v>
+        <v>331</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="D88" s="1">
-        <v>64.25</v>
+        <v>60.3</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="F88" s="1">
-        <v>250</v>
-      </c>
-      <c r="G88" s="3">
-        <v>-105.39665105</v>
-      </c>
-      <c r="H88" s="3">
-        <v>28.098379659999999</v>
+        <v>100</v>
+      </c>
+      <c r="G88" s="9">
+        <v>-105.38525518</v>
+      </c>
+      <c r="H88" s="9">
+        <v>28.073751619999999</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="J88" s="1">
         <v>7</v>
@@ -4818,698 +5101,813 @@
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>360</v>
+        <v>331</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>125</v>
+        <v>108</v>
       </c>
       <c r="D89" s="1">
-        <v>64.34</v>
+        <v>61.03</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G89" s="3">
-        <v>-105.396456</v>
-      </c>
-      <c r="H89" s="3">
-        <v>28.098824409999999</v>
+      <c r="F89" s="1">
+        <v>200</v>
+      </c>
+      <c r="G89" s="9">
+        <v>-105.3870215</v>
+      </c>
+      <c r="H89" s="9">
+        <v>28.080127730000001</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="J89" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>280</v>
+        <v>228</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>126</v>
+        <v>85</v>
       </c>
       <c r="D90" s="1">
-        <v>64.540000000000006</v>
+        <v>62.16</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G90" s="3"/>
-      <c r="H90" s="3"/>
+        <v>48</v>
+      </c>
+      <c r="F90" s="1">
+        <v>600</v>
+      </c>
+      <c r="G90" s="9">
+        <v>-105.39453444999999</v>
+      </c>
+      <c r="H90" s="9">
+        <v>28.082670799999999</v>
+      </c>
       <c r="I90" s="1" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="J90" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>281</v>
+        <v>252</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>360</v>
+        <v>331</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="D91" s="1">
-        <v>65.849999999999994</v>
+        <v>62.63</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="F91" s="1">
-        <v>150</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-105.39881911000001</v>
-      </c>
-      <c r="H91" s="3">
-        <v>28.110534850000001</v>
+        <v>100</v>
+      </c>
+      <c r="G91" s="9">
+        <v>-105.39425558000001</v>
+      </c>
+      <c r="H91" s="9">
+        <v>28.087006259999999</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="J91" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>282</v>
+        <v>368</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>360</v>
+        <v>331</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>128</v>
+        <v>369</v>
       </c>
       <c r="D92" s="1">
-        <v>66.900000000000006</v>
+        <v>62.8</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="G92" s="3"/>
-      <c r="H92" s="3"/>
+        <v>48</v>
+      </c>
+      <c r="F92" s="1">
+        <v>500</v>
+      </c>
+      <c r="G92" s="9">
+        <v>-105.39407772</v>
+      </c>
+      <c r="H92" s="9">
+        <v>28.08851215</v>
+      </c>
       <c r="I92" s="1" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="J92" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A93" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="D93" s="1">
-        <v>67.319999999999993</v>
-      </c>
-      <c r="E93" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F93" s="1">
+      <c r="A93" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="B93" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="C93" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="D93" s="8">
+        <v>63.71</v>
+      </c>
+      <c r="E93" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F93" s="8">
         <v>500</v>
       </c>
-      <c r="G93" s="3">
-        <v>-105.39667469</v>
-      </c>
-      <c r="H93" s="3">
-        <v>28.122881469999999</v>
-      </c>
-      <c r="I93" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="J93" s="1">
-        <v>8</v>
+      <c r="G93" s="9" t="s">
+        <v>370</v>
+      </c>
+      <c r="H93" s="9" t="s">
+        <v>371</v>
+      </c>
+      <c r="I93" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="J93" s="8">
+        <v>7</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>284</v>
+        <v>254</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="C94" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="D94" s="6">
-        <v>67.61</v>
-      </c>
-      <c r="E94" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="F94" s="8"/>
-      <c r="G94" s="3">
-        <v>-105.39545235</v>
-      </c>
-      <c r="H94" s="3">
-        <v>-105.39545235</v>
+        <v>331</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D94" s="1">
+        <v>64.25</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F94" s="1">
+        <v>250</v>
+      </c>
+      <c r="G94" s="9">
+        <v>-105.39665105</v>
+      </c>
+      <c r="H94" s="9">
+        <v>28.098379659999999</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>357</v>
+        <v>136</v>
       </c>
       <c r="J94" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>285</v>
+        <v>255</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="C95" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="D95" s="6">
-        <v>67.849999999999994</v>
+        <v>331</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D95" s="1">
+        <v>64.34</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F95" s="8"/>
-      <c r="G95" s="3">
-        <v>-105.39539644</v>
-      </c>
-      <c r="H95" s="4">
-        <v>28.12746143</v>
+      <c r="F95" s="1">
+        <v>500</v>
+      </c>
+      <c r="G95" s="9">
+        <v>-105.396456</v>
+      </c>
+      <c r="H95" s="9">
+        <v>28.098824409999999</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>357</v>
+        <v>136</v>
       </c>
       <c r="J95" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A96" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="C96" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="D96" s="6">
-        <v>68.19</v>
-      </c>
-      <c r="E96" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="F96" s="8"/>
-      <c r="G96" s="3">
-        <v>-105.39714424</v>
-      </c>
-      <c r="H96" s="3">
-        <v>28.130186720000001</v>
-      </c>
-      <c r="I96" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="J96" s="1">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A96" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="B96" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="C96" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="D96" s="8">
+        <v>64.540000000000006</v>
+      </c>
+      <c r="E96" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F96" s="8">
+        <v>500</v>
+      </c>
+      <c r="G96" s="9" t="s">
+        <v>372</v>
+      </c>
+      <c r="H96" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="I96" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="J96" s="8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>287</v>
+        <v>257</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="C97" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="D97" s="6">
-        <v>68.58</v>
+        <v>331</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D97" s="1">
+        <v>65.849999999999994</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F97" s="8"/>
-      <c r="G97" s="3">
-        <v>-105.39927341000001</v>
-      </c>
-      <c r="H97" s="3">
-        <v>28.133146870000001</v>
+      <c r="F97" s="1">
+        <v>150</v>
+      </c>
+      <c r="G97" s="9">
+        <v>-105.39881911000001</v>
+      </c>
+      <c r="H97" s="9">
+        <v>28.110534850000001</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>357</v>
+        <v>136</v>
       </c>
       <c r="J97" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A98" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="B98" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="C98" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="D98" s="8">
+        <v>66.900000000000006</v>
+      </c>
+      <c r="E98" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="F98" s="8">
+        <v>300</v>
+      </c>
+      <c r="G98" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="H98" s="9" t="s">
+        <v>375</v>
+      </c>
+      <c r="I98" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="J98" s="8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A99" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="B99" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="C99" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="D99" s="10">
+        <v>67.319999999999993</v>
+      </c>
+      <c r="E99" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F99" s="10">
+        <v>500</v>
+      </c>
+      <c r="G99" s="9">
+        <v>-105.39667469</v>
+      </c>
+      <c r="H99" s="9">
+        <v>28.122881469999999</v>
+      </c>
+      <c r="I99" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="J99" s="10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A100" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="B100" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="C100" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="D100" s="12">
+        <v>67.61</v>
+      </c>
+      <c r="E100" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="F100" s="14">
+        <v>400</v>
+      </c>
+      <c r="G100" s="9">
+        <v>-105.39545235</v>
+      </c>
+      <c r="H100" s="9">
+        <v>28.125361179999999</v>
+      </c>
+      <c r="I100" s="10" t="s">
+        <v>328</v>
+      </c>
+      <c r="J100" s="10">
         <v>9</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A98" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="C98" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="D98" s="6">
-        <v>0.54</v>
-      </c>
-      <c r="E98" s="7"/>
-      <c r="F98" s="8"/>
-      <c r="G98" s="9"/>
-      <c r="H98" s="9"/>
-      <c r="I98" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="J98" s="1">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A99" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="B99" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="C99" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="D99" s="6">
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="E99" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F99" s="8"/>
-      <c r="G99" s="9"/>
-      <c r="H99" s="9"/>
-      <c r="I99" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="J99" s="1">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A100" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="C100" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="D100" s="6">
-        <v>1.36</v>
-      </c>
-      <c r="E100" s="7"/>
-      <c r="F100" s="8"/>
-      <c r="G100" s="9"/>
-      <c r="H100" s="9"/>
-      <c r="I100" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="J100" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>291</v>
+        <v>261</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="C101" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="D101" s="6">
-        <v>1.37</v>
+        <v>331</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="D101" s="5">
+        <v>67.849999999999994</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F101" s="8"/>
-      <c r="G101" s="9"/>
-      <c r="H101" s="9"/>
+      <c r="F101" s="14">
+        <v>400</v>
+      </c>
+      <c r="G101" s="9">
+        <v>-105.39539644</v>
+      </c>
+      <c r="H101" s="9">
+        <v>28.12746143</v>
+      </c>
       <c r="I101" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="J101" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="K101" s="11"/>
-    </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+        <v>328</v>
+      </c>
+      <c r="J101" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>292</v>
+        <v>262</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="C102" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="D102" s="6">
-        <v>0.53</v>
-      </c>
-      <c r="E102" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="F102" s="8"/>
-      <c r="G102" s="9"/>
-      <c r="H102" s="9"/>
+        <v>331</v>
+      </c>
+      <c r="C102" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="D102" s="5">
+        <v>68.19</v>
+      </c>
+      <c r="E102" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F102" s="14">
+        <v>400</v>
+      </c>
+      <c r="G102" s="9">
+        <v>-105.39714424</v>
+      </c>
+      <c r="H102" s="9">
+        <v>28.130186720000001</v>
+      </c>
       <c r="I102" s="1" t="s">
-        <v>357</v>
+        <v>328</v>
       </c>
       <c r="J102" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>293</v>
+        <v>263</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="C103" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="D103" s="6">
-        <v>2.2799999999999998</v>
+        <v>331</v>
+      </c>
+      <c r="C103" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="D103" s="5">
+        <v>68.58</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F103" s="8"/>
-      <c r="G103" s="9"/>
-      <c r="H103" s="9"/>
+      <c r="F103" s="14">
+        <v>400</v>
+      </c>
+      <c r="G103" s="9">
+        <v>-105.39927341000001</v>
+      </c>
+      <c r="H103" s="9">
+        <v>28.133146870000001</v>
+      </c>
       <c r="I103" s="1" t="s">
-        <v>357</v>
+        <v>328</v>
       </c>
       <c r="J103" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A104" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="C104" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="D104" s="6">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A104" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="B104" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="C104" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="D104" s="16">
         <v>68.599999999999994</v>
       </c>
-      <c r="E104" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="F104" s="8"/>
-      <c r="G104" s="9"/>
-      <c r="H104" s="9"/>
-      <c r="I104" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="J104" s="1" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A105" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="C105" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="D105" s="6">
+      <c r="E104" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="F104" s="14">
+        <v>400</v>
+      </c>
+      <c r="G104" s="9" t="s">
+        <v>380</v>
+      </c>
+      <c r="H104" s="9" t="s">
+        <v>381</v>
+      </c>
+      <c r="I104" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="J104" s="8" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A105" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="B105" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="C105" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="D105" s="16">
         <v>69.959999999999994</v>
       </c>
-      <c r="E105" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="F105" s="8"/>
-      <c r="G105" s="9"/>
-      <c r="H105" s="9"/>
-      <c r="I105" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="J105" s="1" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E105" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="F105" s="14">
+        <v>400</v>
+      </c>
+      <c r="G105" s="9" t="s">
+        <v>382</v>
+      </c>
+      <c r="H105" s="9" t="s">
+        <v>383</v>
+      </c>
+      <c r="I105" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="J105" s="8" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="B106" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="C106" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="D106" s="6">
+        <v>272</v>
+      </c>
+      <c r="B106" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="D106" s="5">
         <v>70.680000000000007</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F106" s="8"/>
-      <c r="G106" s="3">
+      <c r="F106" s="14">
+        <v>400</v>
+      </c>
+      <c r="G106" s="9">
         <v>-105.42034577</v>
       </c>
-      <c r="H106" s="3">
+      <c r="H106" s="9">
         <v>28.13127411</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>357</v>
+        <v>328</v>
       </c>
       <c r="J106" s="1">
         <v>19</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A107" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="B107" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="C107" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="D107" s="6">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A107" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="B107" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="C107" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="D107" s="16">
         <v>70.77</v>
       </c>
-      <c r="E107" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="F107" s="8"/>
-      <c r="G107" s="9"/>
-      <c r="H107" s="9"/>
-      <c r="I107" s="1" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E107" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="F107" s="14">
+        <v>400</v>
+      </c>
+      <c r="G107" s="9" t="s">
+        <v>384</v>
+      </c>
+      <c r="H107" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="I107" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="J107" s="8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="B108" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="C108" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="D108" s="6">
+        <v>274</v>
+      </c>
+      <c r="B108" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="C108" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="D108" s="5">
         <v>70.84</v>
       </c>
-      <c r="E108" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="F108" s="8"/>
-      <c r="G108" s="3">
+      <c r="E108" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F108" s="14">
+        <v>400</v>
+      </c>
+      <c r="G108" s="9">
         <v>-105.42176239</v>
       </c>
-      <c r="H108" s="3">
+      <c r="H108" s="9">
         <v>28.130590479999999</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
+        <v>328</v>
+      </c>
+      <c r="J108" s="1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="B109" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="C109" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="D109" s="6">
+        <v>275</v>
+      </c>
+      <c r="B109" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="C109" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="D109" s="5">
         <v>71.91</v>
       </c>
-      <c r="E109" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="F109" s="8"/>
-      <c r="G109" s="3">
+      <c r="E109" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F109" s="14">
+        <v>400</v>
+      </c>
+      <c r="G109" s="9">
         <v>-105.43241922999999</v>
       </c>
-      <c r="H109" s="3">
+      <c r="H109" s="9">
         <v>28.1303728</v>
       </c>
       <c r="I109" s="1" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="110" spans="1:11" ht="16.5" x14ac:dyDescent="0.35">
+        <v>328</v>
+      </c>
+      <c r="J109" s="8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A110" s="1" t="s">
-        <v>300</v>
+        <v>277</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="C110" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="D110" s="12">
-        <v>0.18</v>
+        <v>330</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D110" s="1">
+        <v>72.92</v>
       </c>
       <c r="E110" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F110" s="20">
+        <v>400</v>
+      </c>
+      <c r="G110" s="9">
+        <v>-105.43953956999999</v>
+      </c>
+      <c r="H110" s="9">
+        <v>28.12976184</v>
+      </c>
+      <c r="I110" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="J110" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A111" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D111" s="1">
+        <v>73.069999999999993</v>
+      </c>
+      <c r="E111" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F110" s="13"/>
-      <c r="G110" s="9"/>
-      <c r="H110" s="9"/>
-      <c r="I110" s="1" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A111" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="B111" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="C111" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="D111" s="1">
-        <v>72.92</v>
-      </c>
-      <c r="E111" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G111" s="3">
-        <v>-105.43953956999999</v>
-      </c>
-      <c r="H111" s="3">
-        <v>28.12976184</v>
+      <c r="F111" s="20">
+        <v>400</v>
+      </c>
+      <c r="G111" s="9">
+        <v>-105.44315854</v>
+      </c>
+      <c r="H111" s="9">
+        <v>28.1315326</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>358</v>
+        <v>329</v>
       </c>
       <c r="J111" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A112" s="1" t="s">
-        <v>302</v>
+        <v>279</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>359</v>
+        <v>330</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="D112" s="1">
-        <v>73.069999999999993</v>
+        <v>73.27</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G112" s="3">
-        <v>-105.44315854</v>
-      </c>
-      <c r="H112" s="3">
-        <v>28.1315326</v>
+        <v>48</v>
+      </c>
+      <c r="F112" s="20">
+        <v>400</v>
+      </c>
+      <c r="G112" s="9">
+        <v>-105.44465396</v>
+      </c>
+      <c r="H112" s="9">
+        <v>28.131304950000001</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>358</v>
+        <v>329</v>
       </c>
       <c r="J112" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A113" s="1" t="s">
-        <v>303</v>
+        <v>387</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>359</v>
+        <v>330</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>133</v>
+        <v>388</v>
       </c>
       <c r="D113" s="1">
-        <v>73.27</v>
+        <v>73.296000000000006</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G113" s="3">
-        <v>-105.44465396</v>
-      </c>
-      <c r="H113" s="3">
-        <v>28.131304950000001</v>
+        <v>48</v>
+      </c>
+      <c r="F113" s="20">
+        <v>400</v>
+      </c>
+      <c r="G113" s="9">
+        <v>-105.44482729000001</v>
+      </c>
+      <c r="H113" s="9">
+        <v>28.13110756</v>
       </c>
       <c r="I113" s="1" t="s">
-        <v>358</v>
+        <v>329</v>
       </c>
       <c r="J113" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A114" s="1" t="s">
-        <v>304</v>
+        <v>280</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>359</v>
+        <v>330</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="D114" s="1">
         <v>74.099999999999994</v>
@@ -5517,28 +5915,31 @@
       <c r="E114" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G114" s="3">
+      <c r="F114" s="20">
+        <v>400</v>
+      </c>
+      <c r="G114" s="9">
         <v>-105.45333761000001</v>
       </c>
-      <c r="H114" s="3">
+      <c r="H114" s="9">
         <v>28.130554180000001</v>
       </c>
       <c r="I114" s="1" t="s">
-        <v>358</v>
+        <v>329</v>
       </c>
       <c r="J114" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A115" s="1" t="s">
-        <v>305</v>
+        <v>281</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>359</v>
+        <v>330</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="D115" s="1">
         <v>74.650000000000006</v>
@@ -5546,224 +5947,273 @@
       <c r="E115" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G115" s="3">
+      <c r="F115" s="20">
+        <v>400</v>
+      </c>
+      <c r="G115" s="9">
         <v>-105.45837714</v>
       </c>
-      <c r="H115" s="3">
+      <c r="H115" s="9">
         <v>28.128932290000002</v>
       </c>
       <c r="I115" s="1" t="s">
-        <v>358</v>
+        <v>329</v>
       </c>
       <c r="J115" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A116" s="1" t="s">
-        <v>306</v>
+        <v>282</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>359</v>
+        <v>330</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="G116" s="3"/>
-      <c r="H116" s="3"/>
+        <v>123</v>
+      </c>
+      <c r="D116" s="1">
+        <v>75.58</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F116" s="20">
+        <v>400</v>
+      </c>
+      <c r="G116" s="9">
+        <v>-105.46639611000001</v>
+      </c>
+      <c r="H116" s="9">
+        <v>28.12456431</v>
+      </c>
       <c r="I116" s="1" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
+        <v>329</v>
+      </c>
+      <c r="J116" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A117" s="1" t="s">
-        <v>307</v>
+        <v>283</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>359</v>
+        <v>330</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="D117" s="1">
-        <v>75.58</v>
+        <v>75.81</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G117" s="3">
-        <v>-105.46639611000001</v>
-      </c>
-      <c r="H117" s="4">
-        <v>28.12456431</v>
+      <c r="F117" s="20">
+        <v>400</v>
+      </c>
+      <c r="G117" s="9">
+        <v>-105.46856644</v>
+      </c>
+      <c r="H117" s="9">
+        <v>28.123767610000002</v>
       </c>
       <c r="I117" s="1" t="s">
-        <v>358</v>
+        <v>329</v>
       </c>
       <c r="J117" s="1">
         <v>21</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A118" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="B118" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="C118" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D118" s="1">
-        <v>75.78</v>
-      </c>
-      <c r="E118" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="G118" s="3"/>
-      <c r="H118" s="14"/>
-      <c r="I118" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="J118" s="1">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A118" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="B118" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="C118" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="D118" s="8">
+        <v>79</v>
+      </c>
+      <c r="E118" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F118" s="20">
+        <v>400</v>
+      </c>
+      <c r="G118" s="9" t="s">
+        <v>389</v>
+      </c>
+      <c r="H118" s="9" t="s">
+        <v>390</v>
+      </c>
+      <c r="I118" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="J118" s="8">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A119" s="1" t="s">
-        <v>309</v>
+        <v>285</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>359</v>
+        <v>330</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="D119" s="1">
-        <v>75.81</v>
+        <v>79.010000000000005</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G119" s="3">
-        <v>-105.46856644</v>
-      </c>
-      <c r="H119" s="3">
-        <v>28.123767610000002</v>
+        <v>48</v>
+      </c>
+      <c r="F119" s="20">
+        <v>400</v>
+      </c>
+      <c r="G119" s="9">
+        <v>-105.48091742</v>
+      </c>
+      <c r="H119" s="9">
+        <v>28.099132019999999</v>
       </c>
       <c r="I119" s="1" t="s">
-        <v>358</v>
+        <v>329</v>
       </c>
       <c r="J119" s="1">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A120" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="B120" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="C120" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="D120" s="1">
-        <v>79</v>
-      </c>
-      <c r="E120" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G120" s="3"/>
-      <c r="H120" s="3"/>
-      <c r="I120" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="J120" s="1">
         <v>22</v>
       </c>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A121" s="1" t="s">
-        <v>311</v>
+    <row r="120" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A120" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="B120" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="C120" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="D120" s="8">
+        <v>79.010000000000005</v>
+      </c>
+      <c r="E120" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F120" s="20">
+        <v>400</v>
+      </c>
+      <c r="G120" s="9" t="s">
+        <v>391</v>
+      </c>
+      <c r="H120" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="I120" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="J120" s="8">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A121" s="8" t="s">
+        <v>393</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>359</v>
+        <v>330</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>140</v>
+        <v>394</v>
       </c>
       <c r="D121" s="1">
-        <v>79.010000000000005</v>
+        <v>79.025000000000006</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G121" s="3">
-        <v>-105.48091742</v>
-      </c>
-      <c r="H121" s="3">
-        <v>28.099132019999999</v>
+        <v>48</v>
+      </c>
+      <c r="F121" s="20">
+        <v>400</v>
+      </c>
+      <c r="G121" s="9" t="s">
+        <v>395</v>
+      </c>
+      <c r="H121" s="9" t="s">
+        <v>396</v>
       </c>
       <c r="I121" s="1" t="s">
-        <v>358</v>
+        <v>329</v>
       </c>
       <c r="J121" s="1">
         <v>22</v>
       </c>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>359</v>
+        <v>330</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="D122" s="1">
-        <v>79.010000000000005</v>
+        <v>79.73</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G122" s="3"/>
-      <c r="H122" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="F122" s="1">
+        <v>120</v>
+      </c>
+      <c r="G122" s="9">
+        <v>-105.54784365</v>
+      </c>
+      <c r="H122" s="9">
+        <v>28.109398680000002</v>
+      </c>
       <c r="I122" s="1" t="s">
-        <v>358</v>
+        <v>329</v>
       </c>
       <c r="J122" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" s="1" t="s">
-        <v>313</v>
+        <v>287</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>359</v>
+        <v>330</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="D123" s="1">
         <v>79.87</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F123" s="1">
-        <v>120</v>
-      </c>
-      <c r="G123" s="3">
+        <v>48</v>
+      </c>
+      <c r="F123" s="20">
+        <v>400</v>
+      </c>
+      <c r="G123" s="9">
         <v>-105.48108581</v>
       </c>
-      <c r="H123" s="3">
+      <c r="H123" s="9">
         <v>28.091610769999999</v>
       </c>
       <c r="I123" s="1" t="s">
-        <v>358</v>
+        <v>329</v>
       </c>
       <c r="J123" s="1">
         <v>22</v>
@@ -5771,31 +6221,31 @@
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>314</v>
+        <v>288</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>359</v>
+        <v>330</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="D124" s="1">
         <v>80.400000000000006</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="F124" s="1">
         <v>310</v>
       </c>
-      <c r="G124" s="3">
+      <c r="G124" s="9">
         <v>-105.48191688</v>
       </c>
-      <c r="H124" s="3">
+      <c r="H124" s="9">
         <v>28.08701967</v>
       </c>
       <c r="I124" s="1" t="s">
-        <v>358</v>
+        <v>329</v>
       </c>
       <c r="J124" s="1">
         <v>22</v>
@@ -5803,13 +6253,13 @@
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>315</v>
+        <v>289</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>359</v>
+        <v>330</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="D125" s="1">
         <v>80.95</v>
@@ -5820,14 +6270,14 @@
       <c r="F125" s="1">
         <v>60</v>
       </c>
-      <c r="G125" s="3">
+      <c r="G125" s="9">
         <v>-105.48321943000001</v>
       </c>
-      <c r="H125" s="3">
+      <c r="H125" s="9">
         <v>28.082236200000001</v>
       </c>
       <c r="I125" s="1" t="s">
-        <v>358</v>
+        <v>329</v>
       </c>
       <c r="J125" s="1">
         <v>22</v>
@@ -5835,31 +6285,31 @@
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>316</v>
+        <v>290</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>359</v>
+        <v>330</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="D126" s="1">
         <v>82.93</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="F126" s="1">
         <v>60</v>
       </c>
-      <c r="G126" s="3">
+      <c r="G126" s="9">
         <v>-105.49965215</v>
       </c>
-      <c r="H126" s="3">
+      <c r="H126" s="9">
         <v>28.07462937</v>
       </c>
       <c r="I126" s="1" t="s">
-        <v>358</v>
+        <v>329</v>
       </c>
       <c r="J126" s="1">
         <v>22</v>
@@ -5867,31 +6317,31 @@
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>317</v>
+        <v>291</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>359</v>
+        <v>330</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="D127" s="1">
         <v>84.05</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="F127" s="1">
         <v>60</v>
       </c>
-      <c r="G127" s="3">
+      <c r="G127" s="9">
         <v>-105.50879454</v>
       </c>
-      <c r="H127" s="3">
+      <c r="H127" s="9">
         <v>28.0790717</v>
       </c>
       <c r="I127" s="1" t="s">
-        <v>358</v>
+        <v>329</v>
       </c>
       <c r="J127" s="1">
         <v>23</v>
@@ -5899,100 +6349,109 @@
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>318</v>
+        <v>292</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>359</v>
+        <v>330</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="D128" s="1">
         <v>84.55</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="F128" s="1">
         <v>60</v>
       </c>
-      <c r="G128" s="3">
+      <c r="G128" s="9">
         <v>-105.51198017</v>
       </c>
-      <c r="H128" s="3">
+      <c r="H128" s="9">
         <v>28.08252135</v>
       </c>
       <c r="I128" s="1" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+        <v>329</v>
+      </c>
+      <c r="J128" s="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>319</v>
+        <v>293</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>359</v>
+        <v>330</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="D129" s="1">
         <v>85.04</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="F129" s="1">
         <v>40</v>
       </c>
-      <c r="G129" s="3">
+      <c r="G129" s="9">
         <v>-105.51496127999999</v>
       </c>
-      <c r="H129" s="3">
+      <c r="H129" s="9">
         <v>28.086334359999999</v>
       </c>
       <c r="I129" s="1" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+        <v>329</v>
+      </c>
+      <c r="J129" s="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>320</v>
+        <v>294</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>359</v>
+        <v>330</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="D130" s="1">
         <v>85.51</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="F130" s="1">
         <v>120</v>
       </c>
-      <c r="G130" s="3">
+      <c r="G130" s="9">
         <v>-105.51879692</v>
       </c>
-      <c r="H130" s="3">
+      <c r="H130" s="9">
         <v>28.08875523</v>
       </c>
       <c r="I130" s="1" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+        <v>329</v>
+      </c>
+      <c r="J130" s="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>321</v>
+        <v>295</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>359</v>
+        <v>330</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="D131" s="1">
         <v>86.06</v>
@@ -6003,978 +6462,1089 @@
       <c r="F131" s="1">
         <v>120</v>
       </c>
-      <c r="G131" s="3">
+      <c r="G131" s="9">
         <v>-105.52316951</v>
       </c>
-      <c r="H131" s="3">
+      <c r="H131" s="9">
         <v>28.091678999999999</v>
       </c>
       <c r="I131" s="1" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A132" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="B132" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="C132" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="D132" s="1">
+        <v>329</v>
+      </c>
+      <c r="J131" s="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A132" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="B132" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="C132" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="D132" s="8">
         <v>86.24</v>
       </c>
-      <c r="E132" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F132" s="1">
+      <c r="E132" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F132" s="8">
         <v>90</v>
       </c>
-      <c r="G132" s="3"/>
-      <c r="H132" s="3"/>
-      <c r="I132" s="1" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G132" s="9" t="s">
+        <v>397</v>
+      </c>
+      <c r="H132" s="9" t="s">
+        <v>398</v>
+      </c>
+      <c r="I132" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="J132" s="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>323</v>
+        <v>297</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>359</v>
+        <v>330</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>157</v>
+        <v>141</v>
       </c>
       <c r="D133" s="1">
         <v>86.6</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="F133" s="1">
         <v>100</v>
       </c>
-      <c r="G133" s="3">
+      <c r="G133" s="9">
         <v>-105.53100969</v>
       </c>
-      <c r="H133" s="3">
+      <c r="H133" s="9">
         <v>28.095699880000002</v>
       </c>
       <c r="I133" s="1" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+        <v>329</v>
+      </c>
+      <c r="J133" s="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>324</v>
+        <v>298</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>359</v>
+        <v>330</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c r="D134" s="1">
         <v>86.95</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="F134" s="1">
         <v>100</v>
       </c>
-      <c r="G134" s="3">
+      <c r="G134" s="9">
         <v>-105.53100969</v>
       </c>
-      <c r="H134" s="3">
+      <c r="H134" s="9">
         <v>28.095699880000002</v>
       </c>
       <c r="I134" s="1" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+        <v>329</v>
+      </c>
+      <c r="J134" s="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>325</v>
+        <v>299</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>359</v>
+        <v>330</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="D135" s="1">
         <v>87.47</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="F135" s="1">
         <v>100</v>
       </c>
-      <c r="G135" s="3">
+      <c r="G135" s="9">
         <v>-105.53535755</v>
       </c>
-      <c r="H135" s="3">
+      <c r="H135" s="9">
         <v>28.095285730000001</v>
       </c>
       <c r="I135" s="1" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+        <v>329</v>
+      </c>
+      <c r="J135" s="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>326</v>
+        <v>399</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>359</v>
+        <v>330</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>160</v>
+        <v>400</v>
       </c>
       <c r="D136" s="1">
+        <v>87.549000000000007</v>
+      </c>
+      <c r="E136" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F136" s="1">
+        <v>4000</v>
+      </c>
+      <c r="G136" s="9">
+        <v>-105.53596616</v>
+      </c>
+      <c r="H136" s="9">
+        <v>28.094830930000001</v>
+      </c>
+      <c r="I136" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="J136" s="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A137" s="10" t="s">
+        <v>300</v>
+      </c>
+      <c r="B137" s="10" t="s">
+        <v>330</v>
+      </c>
+      <c r="C137" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="D137" s="10">
         <v>88.37</v>
       </c>
-      <c r="E136" s="1" t="s">
+      <c r="E137" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="F136" s="1">
+      <c r="F137" s="10">
         <v>180</v>
       </c>
-      <c r="G136" s="3"/>
-      <c r="H136" s="3"/>
-      <c r="I136" s="1" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A137" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="B137" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="C137" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="D137" s="1">
+      <c r="G137" s="9">
+        <v>-105.53899798</v>
+      </c>
+      <c r="H137" s="9">
+        <v>28.100674290000001</v>
+      </c>
+      <c r="I137" s="10" t="s">
+        <v>329</v>
+      </c>
+      <c r="J137" s="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A138" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D138" s="1">
         <v>88.86</v>
       </c>
-      <c r="E137" s="1" t="s">
+      <c r="E138" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F137" s="1">
+      <c r="F138" s="1">
         <v>120</v>
       </c>
-      <c r="G137" s="3">
+      <c r="G138" s="9">
         <v>-105.54076077000001</v>
       </c>
-      <c r="H137" s="3">
+      <c r="H138" s="9">
         <v>28.10482786</v>
       </c>
-      <c r="I137" s="1" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A138" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="B138" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="C138" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="D138" s="1">
+      <c r="I138" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="J138" s="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A139" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D139" s="1">
         <v>89.1</v>
       </c>
-      <c r="E138" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F138" s="1">
+      <c r="E139" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F139" s="1">
         <v>60</v>
       </c>
-      <c r="G138" s="3">
+      <c r="G139" s="9">
         <v>-105.54267989</v>
       </c>
-      <c r="H138" s="3">
+      <c r="H139" s="9">
         <v>28.10604743</v>
       </c>
-      <c r="I138" s="1" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A139" s="1" t="s">
+      <c r="I139" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="B139" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="C139" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="D139" s="1">
-        <v>79.73</v>
-      </c>
-      <c r="E139" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F139" s="1">
-        <v>120</v>
-      </c>
-      <c r="G139" s="3">
-        <v>-105.54784365</v>
-      </c>
-      <c r="H139" s="3">
-        <v>28.109398680000002</v>
-      </c>
-      <c r="I139" s="1" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J139" s="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B140" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="B140" s="1" t="s">
-        <v>359</v>
-      </c>
       <c r="C140" s="1" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="D140" s="1">
         <v>90.06</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="F140" s="1">
         <v>500</v>
       </c>
-      <c r="G140" s="3">
+      <c r="G140" s="9">
         <v>-105.54986939</v>
       </c>
-      <c r="H140" s="3">
+      <c r="H140" s="9">
         <v>28.111644949999999</v>
       </c>
       <c r="I140" s="1" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+        <v>329</v>
+      </c>
+      <c r="J140" s="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>331</v>
+        <v>305</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>359</v>
+        <v>330</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>165</v>
+        <v>149</v>
       </c>
       <c r="D141" s="1">
         <v>90.13</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G141" s="3">
+        <v>48</v>
+      </c>
+      <c r="F141" s="1">
+        <v>400</v>
+      </c>
+      <c r="G141" s="9">
         <v>-105.55062418</v>
       </c>
-      <c r="H141" s="3">
+      <c r="H141" s="9">
         <v>28.11212372</v>
       </c>
       <c r="I141" s="1" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+        <v>329</v>
+      </c>
+      <c r="J141" s="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>332</v>
+        <v>306</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>359</v>
+        <v>330</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>166</v>
+        <v>150</v>
       </c>
       <c r="D142" s="1">
-        <v>90.42</v>
+        <v>90.72</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="G142" s="3">
-        <v>-105.55345131</v>
-      </c>
-      <c r="H142" s="3">
-        <v>28.112480040000001</v>
+        <v>48</v>
+      </c>
+      <c r="F142" s="1">
+        <v>120</v>
+      </c>
+      <c r="G142" s="9">
+        <v>-105.55624743</v>
+      </c>
+      <c r="H142" s="9">
+        <v>28.113247229999999</v>
       </c>
       <c r="I142" s="1" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+        <v>329</v>
+      </c>
+      <c r="J142" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>333</v>
+        <v>307</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>359</v>
+        <v>330</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="D143" s="1">
-        <v>90.72</v>
+        <v>91.75</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="F143" s="1">
+        <v>100</v>
+      </c>
+      <c r="G143" s="9">
+        <v>-105.56281473</v>
+      </c>
+      <c r="H143" s="9">
+        <v>28.11815408</v>
+      </c>
+      <c r="I143" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="J143" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A144" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D144" s="1">
+        <v>92.07</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F144" s="1">
         <v>120</v>
       </c>
-      <c r="G143" s="3">
-        <v>-105.55624743</v>
-      </c>
-      <c r="H143" s="3">
-        <v>28.113247229999999</v>
-      </c>
-      <c r="I143" s="1" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A144" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="B144" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="C144" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="D144" s="1">
-        <v>91.75</v>
-      </c>
-      <c r="E144" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F144" s="1">
+      <c r="G144" s="9">
+        <v>-105.56566558999999</v>
+      </c>
+      <c r="H144" s="9">
+        <v>28.119577580000001</v>
+      </c>
+      <c r="I144" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="J144" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A145" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D145" s="1">
+        <v>92.34</v>
+      </c>
+      <c r="E145" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F145" s="1">
         <v>100</v>
       </c>
-      <c r="G144" s="3">
-        <v>-105.56281473</v>
-      </c>
-      <c r="H144" s="3">
-        <v>28.11815408</v>
-      </c>
-      <c r="I144" s="1" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A145" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="B145" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="C145" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D145" s="1">
-        <v>92.07</v>
-      </c>
-      <c r="E145" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F145" s="1">
+      <c r="G145" s="9">
+        <v>-105.56806684</v>
+      </c>
+      <c r="H145" s="9">
+        <v>28.120772420000002</v>
+      </c>
+      <c r="I145" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="J145" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A146" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D146" s="1">
+        <v>92.67</v>
+      </c>
+      <c r="E146" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F146" s="1">
         <v>120</v>
       </c>
-      <c r="G145" s="3">
-        <v>-105.56566558999999</v>
-      </c>
-      <c r="H145" s="3">
-        <v>28.119577580000001</v>
-      </c>
-      <c r="I145" s="1" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A146" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="B146" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="C146" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="D146" s="1">
-        <v>92.34</v>
-      </c>
-      <c r="E146" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F146" s="1">
-        <v>100</v>
-      </c>
-      <c r="G146" s="3">
-        <v>-105.56806684</v>
-      </c>
-      <c r="H146" s="3">
-        <v>28.120772420000002</v>
+      <c r="G146" s="9">
+        <v>-105.56995184</v>
+      </c>
+      <c r="H146" s="9">
+        <v>28.12179459</v>
       </c>
       <c r="I146" s="1" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+        <v>329</v>
+      </c>
+      <c r="J146" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>337</v>
+        <v>311</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>359</v>
+        <v>330</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>171</v>
+        <v>155</v>
       </c>
       <c r="D147" s="1">
-        <v>92.67</v>
+        <v>93.19</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="F147" s="1">
         <v>120</v>
       </c>
-      <c r="G147" s="3">
-        <v>-105.56995184</v>
-      </c>
-      <c r="H147" s="3">
-        <v>28.12179459</v>
+      <c r="G147" s="9">
+        <v>-105.57484603</v>
+      </c>
+      <c r="H147" s="9">
+        <v>28.125313479999999</v>
       </c>
       <c r="I147" s="1" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A148" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="B148" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="C148" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="D148" s="1">
-        <v>93.19</v>
-      </c>
-      <c r="E148" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F148" s="1">
+        <v>329</v>
+      </c>
+      <c r="J147" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A148" s="10" t="s">
+        <v>312</v>
+      </c>
+      <c r="B148" s="10" t="s">
+        <v>330</v>
+      </c>
+      <c r="C148" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="D148" s="10">
+        <v>93.62</v>
+      </c>
+      <c r="E148" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="F148" s="10">
         <v>120</v>
       </c>
-      <c r="G148" s="3">
-        <v>-105.57484603</v>
-      </c>
-      <c r="H148" s="3">
-        <v>28.125313479999999</v>
-      </c>
-      <c r="I148" s="1" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G148" s="9">
+        <v>-105.57809770999999</v>
+      </c>
+      <c r="H148" s="9">
+        <v>28.12756143</v>
+      </c>
+      <c r="I148" s="10" t="s">
+        <v>329</v>
+      </c>
+      <c r="J148" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>339</v>
+        <v>313</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>359</v>
+        <v>330</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>173</v>
+        <v>157</v>
       </c>
       <c r="D149" s="1">
-        <v>93.57</v>
+        <v>93.64</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="G149" s="3">
-        <v>-105.57777031000001</v>
-      </c>
-      <c r="H149" s="3">
-        <v>28.12712397</v>
+        <v>15</v>
+      </c>
+      <c r="F149" s="1">
+        <v>180</v>
+      </c>
+      <c r="G149" s="9">
+        <v>-105.57814062999999</v>
+      </c>
+      <c r="H149" s="9">
+        <v>28.127586399999998</v>
       </c>
       <c r="I149" s="1" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+        <v>329</v>
+      </c>
+      <c r="J149" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>340</v>
+        <v>314</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>359</v>
+        <v>330</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>174</v>
+        <v>158</v>
       </c>
       <c r="D150" s="1">
-        <v>93.62</v>
+        <v>93.71</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="F150" s="1">
-        <v>120</v>
-      </c>
-      <c r="G150" s="3">
-        <v>-105.57809770999999</v>
-      </c>
-      <c r="H150" s="3">
-        <v>-105.57809770999999</v>
+        <v>1200</v>
+      </c>
+      <c r="G150" s="9">
+        <v>-105.57855226</v>
+      </c>
+      <c r="H150" s="9">
+        <v>28.12831169</v>
       </c>
       <c r="I150" s="1" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+        <v>329</v>
+      </c>
+      <c r="J150" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
-        <v>341</v>
+        <v>315</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>359</v>
+        <v>330</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>175</v>
+        <v>159</v>
       </c>
       <c r="D151" s="1">
-        <v>93.64</v>
+        <v>94.03</v>
       </c>
       <c r="E151" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F151" s="1">
-        <v>180</v>
-      </c>
-      <c r="G151" s="3">
-        <v>-105.57814062999999</v>
-      </c>
-      <c r="H151" s="3">
-        <v>28.127586399999998</v>
+        <v>360</v>
+      </c>
+      <c r="G151" s="9">
+        <v>-105.58096012999999</v>
+      </c>
+      <c r="H151" s="9">
+        <v>28.129931240000001</v>
       </c>
       <c r="I151" s="1" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+        <v>329</v>
+      </c>
+      <c r="J151" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>342</v>
+        <v>316</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>359</v>
+        <v>330</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="D152" s="1">
-        <v>93.71</v>
+        <v>94.04</v>
       </c>
       <c r="E152" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F152" s="1">
-        <v>1200</v>
-      </c>
-      <c r="G152" s="3">
-        <v>-105.57855226</v>
-      </c>
-      <c r="H152" s="3">
-        <v>28.12831169</v>
+        <v>100</v>
+      </c>
+      <c r="G152" s="9">
+        <v>-105.58110859999999</v>
+      </c>
+      <c r="H152" s="9">
+        <v>28.129979039999998</v>
       </c>
       <c r="I152" s="1" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+        <v>329</v>
+      </c>
+      <c r="J152" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>343</v>
+        <v>401</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>359</v>
+        <v>330</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>177</v>
+        <v>402</v>
       </c>
       <c r="D153" s="1">
-        <v>94.03</v>
+        <v>94.057000000000002</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="F153" s="1">
-        <v>360</v>
-      </c>
-      <c r="G153" s="3">
-        <v>-105.58096012999999</v>
-      </c>
-      <c r="H153" s="3">
-        <v>28.129931240000001</v>
+        <v>200</v>
+      </c>
+      <c r="G153" s="9">
+        <v>-105.5812744</v>
+      </c>
+      <c r="H153" s="9">
+        <v>28.12993402</v>
       </c>
       <c r="I153" s="1" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+        <v>329</v>
+      </c>
+      <c r="J153" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>344</v>
+        <v>317</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>359</v>
+        <v>330</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>178</v>
+        <v>161</v>
       </c>
       <c r="D154" s="1">
-        <v>94.04</v>
+        <v>94.96</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="F154" s="1">
         <v>100</v>
       </c>
-      <c r="G154" s="3">
-        <v>-105.58110859999999</v>
-      </c>
-      <c r="H154" s="3">
-        <v>28.129979039999998</v>
+      <c r="G154" s="9">
+        <v>-105.58607049</v>
+      </c>
+      <c r="H154" s="9">
+        <v>28.133634789999999</v>
       </c>
       <c r="I154" s="1" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+        <v>329</v>
+      </c>
+      <c r="J154" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
-        <v>345</v>
+        <v>318</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>359</v>
+        <v>330</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>179</v>
+        <v>403</v>
       </c>
       <c r="D155" s="1">
-        <v>94.96</v>
+        <v>95.61</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="F155" s="1">
         <v>100</v>
       </c>
-      <c r="G155" s="3"/>
-      <c r="H155" s="3"/>
+      <c r="G155" s="9">
+        <v>-105.59170841</v>
+      </c>
+      <c r="H155" s="9">
+        <v>28.136690489999999</v>
+      </c>
       <c r="I155" s="1" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A156" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="B156" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="C156" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="D156" s="1">
-        <v>94.61</v>
-      </c>
-      <c r="E156" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F156" s="1">
+        <v>329</v>
+      </c>
+      <c r="J155" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A156" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="B156" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="C156" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="D156" s="8">
+        <v>96.82</v>
+      </c>
+      <c r="E156" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F156" s="8">
         <v>100</v>
       </c>
-      <c r="G156" s="3"/>
-      <c r="H156" s="3"/>
-      <c r="I156" s="1" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G156" s="9" t="s">
+        <v>404</v>
+      </c>
+      <c r="H156" s="9" t="s">
+        <v>405</v>
+      </c>
+      <c r="I156" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="J156" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>347</v>
+        <v>320</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>359</v>
+        <v>330</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>181</v>
+        <v>163</v>
       </c>
       <c r="D157" s="1">
-        <v>96.82</v>
+        <v>96.96</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="F157" s="1">
+        <v>480</v>
+      </c>
+      <c r="G157" s="9">
+        <v>-105.60089364</v>
+      </c>
+      <c r="H157" s="9">
+        <v>28.145025619999998</v>
+      </c>
+      <c r="I157" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="J157" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A158" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="B158" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="C158" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="D158" s="8">
+        <v>97.2</v>
+      </c>
+      <c r="E158" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F158" s="8">
+        <v>30</v>
+      </c>
+      <c r="G158" s="9" t="s">
+        <v>406</v>
+      </c>
+      <c r="H158" s="9" t="s">
+        <v>407</v>
+      </c>
+      <c r="I158" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="J158" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A159" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D159" s="1">
+        <v>97.79</v>
+      </c>
+      <c r="E159" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F159" s="1">
         <v>100</v>
       </c>
-      <c r="G157" s="3"/>
-      <c r="H157" s="3"/>
-      <c r="I157" s="1" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A158" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="B158" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="C158" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="D158" s="1">
-        <v>96.96</v>
-      </c>
-      <c r="E158" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F158" s="1">
-        <v>480</v>
-      </c>
-      <c r="G158" s="3">
-        <v>-105.60089364</v>
-      </c>
-      <c r="H158" s="3">
-        <v>28.145025619999998</v>
-      </c>
-      <c r="I158" s="1" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A159" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="B159" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="C159" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="D159" s="1">
-        <v>97.2</v>
-      </c>
-      <c r="E159" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F159" s="1">
-        <v>30</v>
-      </c>
-      <c r="G159" s="3"/>
-      <c r="H159" s="3"/>
+      <c r="G159" s="9">
+        <v>-105.60755784</v>
+      </c>
+      <c r="H159" s="9">
+        <v>28.147992649999999</v>
+      </c>
       <c r="I159" s="1" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+        <v>329</v>
+      </c>
+      <c r="J159" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>350</v>
+        <v>323</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>359</v>
+        <v>330</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="D160" s="1">
-        <v>97.79</v>
+        <v>97.84</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="F160" s="1">
+        <v>120</v>
+      </c>
+      <c r="G160" s="9">
+        <v>-105.60788029</v>
+      </c>
+      <c r="H160" s="9">
+        <v>28.148482659999999</v>
+      </c>
+      <c r="I160" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="J160" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A161" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="B161" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="C161" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="D161" s="8">
+        <v>98.36</v>
+      </c>
+      <c r="E161" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F161" s="8">
+        <v>200</v>
+      </c>
+      <c r="G161" s="9" t="s">
+        <v>408</v>
+      </c>
+      <c r="H161" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="I161" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="J161" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A162" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="B162" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="C162" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="D162" s="8">
+        <v>98.38</v>
+      </c>
+      <c r="E162" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F162" s="8">
+        <v>120</v>
+      </c>
+      <c r="G162" s="9" t="s">
+        <v>410</v>
+      </c>
+      <c r="H162" s="9" t="s">
+        <v>411</v>
+      </c>
+      <c r="I162" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="J162" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A163" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="B163" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="C163" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="D163" s="8">
+        <v>99.62</v>
+      </c>
+      <c r="E163" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F163" s="8">
+        <v>120</v>
+      </c>
+      <c r="G163" s="9" t="s">
+        <v>412</v>
+      </c>
+      <c r="H163" s="9" t="s">
+        <v>413</v>
+      </c>
+      <c r="I163" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="J163" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A164" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="B164" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="C164" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="D164" s="8">
+        <v>99.75</v>
+      </c>
+      <c r="E164" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F164" s="8">
         <v>100</v>
       </c>
-      <c r="G160" s="3">
-        <v>-105.60755784</v>
-      </c>
-      <c r="H160" s="3">
-        <v>28.147992649999999</v>
-      </c>
-      <c r="I160" s="1" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A161" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="B161" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="C161" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="D161" s="1">
-        <v>97.81</v>
-      </c>
-      <c r="E161" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="G161" s="3">
-        <v>-105.60801308000001</v>
-      </c>
-      <c r="H161" s="3">
-        <v>28.148154989999998</v>
-      </c>
-      <c r="I161" s="1" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A162" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="B162" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="C162" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="D162" s="1">
-        <v>97.84</v>
-      </c>
-      <c r="E162" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F162" s="1">
-        <v>120</v>
-      </c>
-      <c r="G162" s="3">
-        <v>-105.60788029</v>
-      </c>
-      <c r="H162" s="3">
-        <v>28.148482659999999</v>
-      </c>
-      <c r="I162" s="1" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A163" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="B163" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="C163" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="D163" s="1">
-        <v>98.36</v>
-      </c>
-      <c r="E163" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G163" s="3"/>
-      <c r="H163" s="3"/>
-      <c r="I163" s="1" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A164" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="B164" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="C164" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="D164" s="1">
-        <v>98.38</v>
-      </c>
-      <c r="E164" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F164" s="1">
-        <v>120</v>
-      </c>
-      <c r="G164" s="3"/>
-      <c r="H164" s="3"/>
-      <c r="I164" s="1" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A165" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="B165" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="C165" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="D165" s="1">
-        <v>99.62</v>
-      </c>
-      <c r="E165" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F165" s="1">
-        <v>120</v>
-      </c>
-      <c r="G165" s="3"/>
-      <c r="H165" s="3"/>
-      <c r="I165" s="1" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A166" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="B166" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="C166" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="D166" s="1">
-        <v>99.75</v>
-      </c>
-      <c r="E166" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F166" s="1">
-        <v>100</v>
-      </c>
+      <c r="G164" s="9" t="s">
+        <v>414</v>
+      </c>
+      <c r="H164" s="9" t="s">
+        <v>415</v>
+      </c>
+      <c r="I164" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="J164" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A165" s="8"/>
+      <c r="G165" s="9"/>
+      <c r="H165" s="9"/>
+    </row>
+    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
       <c r="G166" s="3"/>
       <c r="H166" s="3"/>
-      <c r="I166" s="1" t="s">
-        <v>358</v>
-      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:L166" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L167">
+    <sortCondition ref="D2:D167"/>
+  </sortState>
   <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/public/datos/puntos_entrega_rows validado.xlsx
+++ b/public/datos/puntos_entrega_rows validado.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29911"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29918"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\peper\Downloads\Antigravity\SICA 005\conchos-digital\public\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9E5D858-6439-4C7D-9F1F-56A876F14ABE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A31FAE8-A303-4D62-A5F3-8423B9DC45A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-17290" yWindow="0" windowWidth="17380" windowHeight="13770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25690" yWindow="1650" windowWidth="12980" windowHeight="10170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="puntos_entrega_rows" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
     <author>tc={68D79ADE-2227-4F97-AF7F-FD7D8C7C0BD9}</author>
   </authors>
   <commentList>
-    <comment ref="C15" authorId="0" shapeId="0" xr:uid="{B160D996-08EB-4B64-BC68-969651B009FF}">
+    <comment ref="C6" authorId="0" shapeId="0" xr:uid="{BA9E82EB-00A5-4951-BFF5-19E86DA098EE}">
       <text>
         <r>
           <rPr>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="904" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="849" uniqueCount="358">
   <si>
     <t>id</t>
   </si>
@@ -1060,126 +1060,24 @@
     <t>Directa K-34+980</t>
   </si>
   <si>
-    <t>105°15'45.01"O</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 27°57'7.58"N</t>
-  </si>
-  <si>
-    <t>105°15'55.72"O</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 27°57'6.53"N</t>
-  </si>
-  <si>
-    <t>105°16'10.65"O</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 27°57'20.07"N</t>
-  </si>
-  <si>
-    <t>105°16'17.17"O</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 27°57'26.28"N</t>
-  </si>
-  <si>
-    <t>105°16'19.71"O</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 27°57'28.64"N</t>
-  </si>
-  <si>
-    <t>105°16'25.63"O</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 27°57'34.32"N</t>
-  </si>
-  <si>
-    <t>105°16'32.98"O</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 27°57'41.35"N</t>
-  </si>
-  <si>
-    <t>105°16'40.01"O</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 27°57'48.00"N</t>
-  </si>
-  <si>
-    <t>105°17'46.79"O</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 27°59'9.58"N</t>
-  </si>
-  <si>
     <t>PE-053</t>
   </si>
   <si>
     <t>Directa k-44+800</t>
   </si>
   <si>
-    <t>105°19'3.42"O</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 28° 0'33.25"N</t>
-  </si>
-  <si>
     <t>MOD-012</t>
   </si>
   <si>
     <t>Toma K-49+872</t>
   </si>
   <si>
-    <t>105°19'34.02"O</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 28° 1'24.54"N</t>
-  </si>
-  <si>
-    <t>105°21'39.55"O</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 28° 4'2.56"N</t>
-  </si>
-  <si>
-    <t>105°19'29.56"O</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 28° 1'17.87"N</t>
-  </si>
-  <si>
-    <t>105°21'48.34"O</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 28° 4'5.42"N</t>
-  </si>
-  <si>
     <t>PE-092</t>
   </si>
   <si>
     <t>Repr. Y Pte K-62+800</t>
   </si>
   <si>
-    <t>105°23'48.20"O</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 28° 5'39.55"N</t>
-  </si>
-  <si>
-    <t>105°23'46.94"O</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 28° 5'59.46"N</t>
-  </si>
-  <si>
-    <t>105°23'56.42"O</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 28° 7'8.20"N</t>
-  </si>
-  <si>
     <t>MOD-003</t>
   </si>
   <si>
@@ -1192,24 +1090,6 @@
     <t>SUBLATERAL K-2+286</t>
   </si>
   <si>
-    <t>105°23'56.26"O</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 28° 7'58.55"N</t>
-  </si>
-  <si>
-    <t>105°24'44.35"O</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 28° 7'53.67"N</t>
-  </si>
-  <si>
-    <t>105°25'13.84"O</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 28° 7'52.30"N</t>
-  </si>
-  <si>
     <t>SUB LAT K-0+186(M-12)</t>
   </si>
   <si>
@@ -1219,36 +1099,12 @@
     <t>Represa K-73+296</t>
   </si>
   <si>
-    <t>105°28'51.36"O</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 28° 5'56.93"N</t>
-  </si>
-  <si>
-    <t>105°28'51.33"O</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 28° 5'56.83"N</t>
-  </si>
-  <si>
     <t>PE-138</t>
   </si>
   <si>
     <t>Represa K-79+025</t>
   </si>
   <si>
-    <t>105°28'51.37"O</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 28° 5'56.51"N</t>
-  </si>
-  <si>
-    <t>105°31'31.72"O</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 28° 5'34.71"N</t>
-  </si>
-  <si>
     <t>PE-152</t>
   </si>
   <si>
@@ -1264,47 +1120,20 @@
     <t>Directa K-95+617</t>
   </si>
   <si>
-    <t>105°36'19.29"O</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 28° 8'43.42"N</t>
-  </si>
-  <si>
-    <t>105°36'27.76"O</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 28° 8'53.48"N</t>
-  </si>
-  <si>
-    <t>105°36'47.28"O</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 28° 9'23.41"N</t>
-  </si>
-  <si>
-    <t>105°36'46.86"O</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 28° 9'22.87"N</t>
-  </si>
-  <si>
-    <t>105°37'10.40"O</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 28° 9'35.09"N</t>
-  </si>
-  <si>
-    <t>105°37'10.85"O</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 28° 9'35.28"N</t>
+    <t>PE-185</t>
+  </si>
+  <si>
+    <t>Represa K-99+786</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="26" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.00000000"/>
+  </numFmts>
+  <fonts count="29" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1484,8 +1313,26 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1673,12 +1520,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -1793,6 +1646,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1838,7 +1706,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1849,25 +1717,34 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1882,22 +1759,25 @@
     <xf numFmtId="0" fontId="23" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="27" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2277,7 +2157,7 @@
     <col min="3" max="3" width="25.140625" style="1" customWidth="1"/>
     <col min="4" max="4" width="15.42578125" style="1" customWidth="1"/>
     <col min="5" max="6" width="11.42578125" style="1"/>
-    <col min="7" max="7" width="11.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" style="2" customWidth="1"/>
     <col min="8" max="8" width="14.7109375" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="11" width="11.42578125" style="1"/>
     <col min="12" max="12" width="17.7109375" style="1" customWidth="1"/>
@@ -2303,10 +2183,10 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
@@ -2322,395 +2202,403 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="8" t="s">
-        <v>276</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>358</v>
-      </c>
-      <c r="C2" s="15" t="s">
-        <v>386</v>
-      </c>
-      <c r="D2" s="19">
-        <v>0.186</v>
-      </c>
-      <c r="E2" s="8" t="s">
+    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="1">
+        <v>6.8</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="20">
-        <v>400</v>
-      </c>
-      <c r="G2" s="9">
-        <v>-105.209819</v>
-      </c>
-      <c r="H2" s="9">
-        <v>27.669433000000001</v>
-      </c>
-      <c r="I2" s="8" t="s">
-        <v>328</v>
-      </c>
-      <c r="J2" s="8">
-        <v>3</v>
+      <c r="F2" s="1">
+        <v>200</v>
+      </c>
+      <c r="G2" s="6">
+        <v>-105.1942667</v>
+      </c>
+      <c r="H2" s="6">
+        <v>27.7253583</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
-        <v>268</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>377</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>176</v>
-      </c>
-      <c r="D3" s="16">
-        <v>0.53</v>
-      </c>
-      <c r="E3" s="17" t="s">
-        <v>187</v>
-      </c>
-      <c r="F3" s="14">
-        <v>400</v>
-      </c>
-      <c r="G3" s="9">
-        <v>-105.20787199999999</v>
-      </c>
-      <c r="H3" s="9">
-        <v>27.671658000000001</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>328</v>
-      </c>
-      <c r="J3" s="8">
-        <v>14</v>
+      <c r="A3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="1">
+        <v>7.61</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="1">
+        <v>200</v>
+      </c>
+      <c r="G3" s="6">
+        <v>-105.193725</v>
+      </c>
+      <c r="H3" s="6">
+        <v>27.73255</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
-        <v>264</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>331</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>186</v>
-      </c>
-      <c r="D4" s="16">
-        <v>0.54</v>
-      </c>
-      <c r="E4" s="17" t="s">
+      <c r="A4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="1">
+        <v>8.1639999999999997</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="14">
-        <v>400</v>
-      </c>
-      <c r="G4" s="9">
-        <v>-105.207808</v>
-      </c>
-      <c r="H4" s="9">
-        <v>27.671703000000001</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>328</v>
-      </c>
-      <c r="J4" s="8">
-        <v>9</v>
+      <c r="F4" s="1">
+        <v>200</v>
+      </c>
+      <c r="G4" s="7">
+        <v>-105.19242103000001</v>
+      </c>
+      <c r="H4" s="7">
+        <v>27.737176049999999</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
-        <v>265</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>331</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>173</v>
-      </c>
-      <c r="D5" s="16">
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="E5" s="8" t="s">
+      <c r="A5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="1">
+        <v>10.53</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="1">
+        <v>200</v>
+      </c>
+      <c r="G5" s="7">
+        <v>-105.18438539</v>
+      </c>
+      <c r="H5" s="7">
+        <v>27.755246669999998</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="1">
+        <v>11.21</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="1">
+        <v>300</v>
+      </c>
+      <c r="G6" s="7">
+        <v>-105.18461035999999</v>
+      </c>
+      <c r="H6" s="7">
+        <v>27.761106130000002</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="1">
+        <v>14.5</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="14">
-        <v>400</v>
-      </c>
-      <c r="G5" s="9">
-        <v>-105.20411900000001</v>
-      </c>
-      <c r="H5" s="9">
-        <v>27.675628</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>328</v>
-      </c>
-      <c r="J5" s="8">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
-        <v>266</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>331</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>174</v>
-      </c>
-      <c r="D6" s="16">
-        <v>1.36</v>
-      </c>
-      <c r="E6" s="17" t="s">
+      <c r="F7" s="1">
+        <v>200</v>
+      </c>
+      <c r="G7" s="7">
+        <v>-105.18494722</v>
+      </c>
+      <c r="H7" s="7">
+        <v>27.792011460000001</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="1">
+        <v>15.7</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="14">
-        <v>400</v>
-      </c>
-      <c r="G6" s="9">
-        <v>-105.203367</v>
-      </c>
-      <c r="H6" s="9">
-        <v>27.677778</v>
-      </c>
-      <c r="I6" s="8" t="s">
-        <v>328</v>
-      </c>
-      <c r="J6" s="8">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
-        <v>266</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>376</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>174</v>
-      </c>
-      <c r="D7" s="16">
-        <v>1.36</v>
-      </c>
-      <c r="E7" s="17" t="s">
+      <c r="F8" s="1">
+        <v>150</v>
+      </c>
+      <c r="G8" s="7">
+        <v>-105.18779438999999</v>
+      </c>
+      <c r="H8" s="7">
+        <v>27.801911499999999</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="1">
+        <v>16.41</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F7" s="14">
-        <v>400</v>
-      </c>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="8" t="s">
-        <v>328</v>
-      </c>
-      <c r="J7" s="8">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
-        <v>267</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>376</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>175</v>
-      </c>
-      <c r="D8" s="16">
-        <v>1.37</v>
-      </c>
-      <c r="E8" s="8" t="s">
+      <c r="F9" s="1">
+        <v>150</v>
+      </c>
+      <c r="G9" s="7">
+        <v>-105.18806952</v>
+      </c>
+      <c r="H9" s="7">
+        <v>27.80784976</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="K9" s="4"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="1">
+        <v>17.32</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="14">
-        <v>400</v>
-      </c>
-      <c r="G8" s="9">
-        <v>-105.20357799999999</v>
-      </c>
-      <c r="H8" s="9">
-        <v>27.677810999999998</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>328</v>
-      </c>
-      <c r="J8" s="18" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>377</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>177</v>
-      </c>
-      <c r="D9" s="16">
-        <v>2.2799999999999998</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F9" s="14">
-        <v>400</v>
-      </c>
-      <c r="G9" s="9">
-        <v>-105.201308</v>
-      </c>
-      <c r="H9" s="9">
-        <v>27.685775</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>328</v>
-      </c>
-      <c r="J9" s="8">
-        <v>14</v>
-      </c>
-      <c r="K9" s="7"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="8" t="s">
-        <v>378</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>377</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>379</v>
-      </c>
-      <c r="D10" s="16">
-        <v>2.286</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F10" s="14">
-        <v>400</v>
-      </c>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="8" t="s">
-        <v>328</v>
-      </c>
-      <c r="J10" s="8" t="s">
-        <v>185</v>
+      <c r="F10" s="1">
+        <v>300</v>
+      </c>
+      <c r="G10" s="7">
+        <v>-105.18725971000001</v>
+      </c>
+      <c r="H10" s="7">
+        <v>27.813766860000001</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="D11" s="1">
-        <v>6.8</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F11" s="1">
         <v>200</v>
       </c>
-      <c r="G11" s="9">
-        <v>-105.1942667</v>
-      </c>
-      <c r="H11" s="9">
-        <v>27.7253583</v>
-      </c>
-      <c r="I11" s="8" t="s">
+      <c r="G11" s="7">
+        <v>-105.18745744</v>
+      </c>
+      <c r="H11" s="7">
+        <v>27.818471450000001</v>
+      </c>
+      <c r="I11" s="5" t="s">
         <v>332</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="D12" s="1">
-        <v>7.61</v>
+        <v>19.96</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F12" s="1">
-        <v>200</v>
-      </c>
-      <c r="G12" s="9">
-        <v>-105.193725</v>
-      </c>
-      <c r="H12" s="9">
-        <v>27.73255</v>
-      </c>
-      <c r="I12" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="G12" s="7">
+        <v>-105.19613178</v>
+      </c>
+      <c r="H12" s="7">
+        <v>27.836371679999999</v>
+      </c>
+      <c r="I12" s="5" t="s">
         <v>332</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="D13" s="1">
-        <v>8.1639999999999997</v>
+        <v>21.63</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F13" s="1">
-        <v>200</v>
-      </c>
-      <c r="G13" s="9">
-        <v>-105.19242103000001</v>
-      </c>
-      <c r="H13" s="9">
-        <v>27.737176049999999</v>
-      </c>
-      <c r="I13" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="G13" s="7">
+        <v>-105.19996148</v>
+      </c>
+      <c r="H13" s="7">
+        <v>27.851017880000001</v>
+      </c>
+      <c r="I13" s="5" t="s">
         <v>332</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D14" s="1">
-        <v>10.53</v>
+        <v>22.21</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>19</v>
@@ -2718,843 +2606,843 @@
       <c r="F14" s="1">
         <v>200</v>
       </c>
-      <c r="G14" s="9">
-        <v>-105.18438539</v>
-      </c>
-      <c r="H14" s="9">
-        <v>27.755246669999998</v>
-      </c>
-      <c r="I14" s="8" t="s">
+      <c r="G14" s="7">
+        <v>-105.20323401</v>
+      </c>
+      <c r="H14" s="7">
+        <v>27.855245709999998</v>
+      </c>
+      <c r="I14" s="5" t="s">
         <v>332</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B15" s="1" t="s">
+      <c r="A15" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="B15" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D15" s="1">
-        <v>11.21</v>
-      </c>
-      <c r="E15" s="1" t="s">
+      <c r="C15" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" s="8">
+        <v>23.82</v>
+      </c>
+      <c r="E15" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F15" s="1">
-        <v>300</v>
+      <c r="F15" s="8">
+        <v>150</v>
       </c>
       <c r="G15" s="9">
-        <v>-105.18461035999999</v>
+        <v>-105.20724140999999</v>
       </c>
       <c r="H15" s="9">
-        <v>27.761106130000002</v>
+        <v>27.866153499999999</v>
       </c>
       <c r="I15" s="8" t="s">
         <v>332</v>
       </c>
-      <c r="J15" s="1" t="s">
-        <v>16</v>
+      <c r="J15" s="8">
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B16" s="1" t="s">
+      <c r="A16" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D16" s="1">
-        <v>14.5</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F16" s="1">
-        <v>200</v>
+      <c r="C16" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" s="8">
+        <v>24.898</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="8">
+        <v>300</v>
       </c>
       <c r="G16" s="9">
-        <v>-105.18494722</v>
+        <v>-105.20528398</v>
       </c>
       <c r="H16" s="9">
-        <v>27.792011460000001</v>
+        <v>27.874954580000001</v>
       </c>
       <c r="I16" s="8" t="s">
         <v>332</v>
       </c>
-      <c r="J16" s="1" t="s">
-        <v>28</v>
+      <c r="J16" s="8">
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B17" s="1" t="s">
+      <c r="A17" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="B17" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D17" s="1">
-        <v>15.7</v>
-      </c>
-      <c r="E17" s="1" t="s">
+      <c r="C17" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D17" s="8">
+        <v>26.51</v>
+      </c>
+      <c r="E17" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F17" s="1">
-        <v>150</v>
+      <c r="F17" s="8">
+        <v>300</v>
       </c>
       <c r="G17" s="9">
-        <v>-105.18779438999999</v>
+        <v>-105.20948399</v>
       </c>
       <c r="H17" s="9">
-        <v>27.801911499999999</v>
+        <v>27.886966690000001</v>
       </c>
       <c r="I17" s="8" t="s">
         <v>332</v>
       </c>
-      <c r="J17" s="1" t="s">
-        <v>28</v>
+      <c r="J17" s="8">
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B18" s="1" t="s">
+      <c r="A18" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="B18" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D18" s="1">
-        <v>16.41</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F18" s="1">
-        <v>150</v>
+      <c r="C18" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D18" s="8">
+        <v>27.75</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F18" s="8">
+        <v>200</v>
       </c>
       <c r="G18" s="9">
-        <v>-105.18806952</v>
+        <v>-105.20854941</v>
       </c>
       <c r="H18" s="9">
-        <v>27.80784976</v>
+        <v>27.89642022</v>
       </c>
       <c r="I18" s="8" t="s">
         <v>332</v>
       </c>
-      <c r="J18" s="1" t="s">
-        <v>28</v>
+      <c r="J18" s="8">
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B19" s="1" t="s">
+      <c r="A19" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="B19" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D19" s="1">
-        <v>17.32</v>
-      </c>
-      <c r="E19" s="1" t="s">
+      <c r="C19" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D19" s="8">
+        <v>28.23</v>
+      </c>
+      <c r="E19" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F19" s="1">
-        <v>300</v>
+      <c r="F19" s="8">
+        <v>120</v>
       </c>
       <c r="G19" s="9">
-        <v>-105.18725971000001</v>
+        <v>-105.21288428</v>
       </c>
       <c r="H19" s="9">
-        <v>27.813766860000001</v>
+        <v>27.898625670000001</v>
       </c>
       <c r="I19" s="8" t="s">
         <v>332</v>
       </c>
-      <c r="J19" s="1" t="s">
-        <v>28</v>
+      <c r="J19" s="8">
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B20" s="1" t="s">
+      <c r="A20" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="B20" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D20" s="1">
-        <v>17.600000000000001</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F20" s="1">
+      <c r="C20" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D20" s="8">
+        <v>28.26</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F20" s="8">
         <v>200</v>
       </c>
       <c r="G20" s="9">
-        <v>-105.18745744</v>
+        <v>-105.21814476</v>
       </c>
       <c r="H20" s="9">
-        <v>27.818471450000001</v>
+        <v>27.90179109</v>
       </c>
       <c r="I20" s="8" t="s">
         <v>332</v>
       </c>
-      <c r="J20" s="1" t="s">
-        <v>28</v>
+      <c r="J20" s="8">
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B21" s="1" t="s">
+      <c r="A21" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="B21" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D21" s="1">
-        <v>19.96</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F21" s="1">
-        <v>300</v>
+      <c r="C21" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D21" s="8">
+        <v>31.6</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F21" s="8">
+        <v>200</v>
       </c>
       <c r="G21" s="9">
-        <v>-105.19613178</v>
+        <v>-105.22875037999999</v>
       </c>
       <c r="H21" s="9">
-        <v>27.836371679999999</v>
+        <v>27.922997729999999</v>
       </c>
       <c r="I21" s="8" t="s">
         <v>332</v>
       </c>
-      <c r="J21" s="1" t="s">
-        <v>28</v>
+      <c r="J21" s="8">
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B22" s="1" t="s">
+      <c r="A22" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="B22" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D22" s="1">
-        <v>21.63</v>
-      </c>
-      <c r="E22" s="1" t="s">
+      <c r="C22" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D22" s="8">
+        <v>32.51</v>
+      </c>
+      <c r="E22" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F22" s="1">
-        <v>300</v>
+      <c r="F22" s="8">
+        <v>200</v>
       </c>
       <c r="G22" s="9">
-        <v>-105.19996148</v>
+        <v>-105.23515617</v>
       </c>
       <c r="H22" s="9">
-        <v>27.851017880000001</v>
+        <v>27.928090149999999</v>
       </c>
       <c r="I22" s="8" t="s">
         <v>332</v>
       </c>
-      <c r="J22" s="1" t="s">
-        <v>28</v>
+      <c r="J22" s="8">
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B23" s="1" t="s">
+      <c r="A23" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="B23" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D23" s="1">
-        <v>22.21</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F23" s="1">
-        <v>200</v>
+      <c r="C23" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D23" s="8">
+        <v>33.340000000000003</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F23" s="8">
+        <v>150</v>
       </c>
       <c r="G23" s="9">
-        <v>-105.20323401</v>
-      </c>
-      <c r="H23" s="9">
-        <v>27.855245709999998</v>
+        <v>-105.24074069</v>
+      </c>
+      <c r="H23" s="10">
+        <v>27.93214682</v>
       </c>
       <c r="I23" s="8" t="s">
         <v>332</v>
       </c>
-      <c r="J23" s="1" t="s">
-        <v>28</v>
+      <c r="J23" s="8">
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="B24" s="1" t="s">
+      <c r="A24" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="B24" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D24" s="1">
-        <v>23.82</v>
-      </c>
-      <c r="E24" s="1" t="s">
+      <c r="C24" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D24" s="8">
+        <v>34.020000000000003</v>
+      </c>
+      <c r="E24" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F24" s="1">
-        <v>150</v>
+      <c r="F24" s="8">
+        <v>200</v>
       </c>
       <c r="G24" s="9">
-        <v>-105.20724140999999</v>
+        <v>-105.23723529999999</v>
       </c>
       <c r="H24" s="9">
-        <v>27.866153499999999</v>
+        <v>27.937600589999999</v>
       </c>
       <c r="I24" s="8" t="s">
         <v>332</v>
       </c>
-      <c r="J24" s="1">
-        <v>3</v>
+      <c r="J24" s="8">
+        <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B25" s="1" t="s">
+      <c r="A25" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="B25" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C25" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D25" s="1">
-        <v>24.898</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F25" s="1">
-        <v>300</v>
+      <c r="C25" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="D25" s="8">
+        <v>34.950000000000003</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F25" s="8">
+        <v>500</v>
       </c>
       <c r="G25" s="9">
-        <v>-105.20528398</v>
+        <v>-105.23711433</v>
       </c>
       <c r="H25" s="9">
-        <v>27.874954580000001</v>
+        <v>27.947039270000001</v>
       </c>
       <c r="I25" s="8" t="s">
         <v>332</v>
       </c>
-      <c r="J25" s="1">
-        <v>3</v>
+      <c r="J25" s="8">
+        <v>4</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="B26" s="1" t="s">
+      <c r="A26" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="B26" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C26" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D26" s="1">
-        <v>26.51</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F26" s="1">
-        <v>300</v>
+      <c r="C26" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D26" s="8">
+        <v>34.951999999999998</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F26" s="8">
+        <v>500</v>
       </c>
       <c r="G26" s="9">
-        <v>-105.20948399</v>
+        <v>-105.23711435</v>
       </c>
       <c r="H26" s="9">
-        <v>27.886966690000001</v>
+        <v>27.947039289999999</v>
       </c>
       <c r="I26" s="8" t="s">
         <v>332</v>
       </c>
-      <c r="J26" s="1">
-        <v>3</v>
+      <c r="J26" s="8">
+        <v>4</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="B27" s="1" t="s">
+      <c r="A27" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="B27" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C27" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D27" s="1">
-        <v>27.75</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F27" s="1">
-        <v>200</v>
+      <c r="C27" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="D27" s="8">
+        <v>34.979999999999997</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F27" s="8">
+        <v>150</v>
       </c>
       <c r="G27" s="9">
-        <v>-105.20854941</v>
+        <v>-105.23729136999999</v>
       </c>
       <c r="H27" s="9">
-        <v>27.89642022</v>
+        <v>27.94707365</v>
       </c>
       <c r="I27" s="8" t="s">
         <v>332</v>
       </c>
-      <c r="J27" s="1">
-        <v>3</v>
+      <c r="J27" s="8">
+        <v>4</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="B28" s="1" t="s">
+      <c r="A28" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="B28" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C28" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D28" s="1">
-        <v>28.23</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F28" s="1">
-        <v>120</v>
+      <c r="C28" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="D28" s="8">
+        <v>36.6</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F28" s="8">
+        <v>200</v>
       </c>
       <c r="G28" s="9">
-        <v>-105.21288428</v>
+        <v>-105.23754886</v>
       </c>
       <c r="H28" s="9">
-        <v>27.898625670000001</v>
+        <v>27.947098799999999</v>
       </c>
       <c r="I28" s="8" t="s">
         <v>332</v>
       </c>
-      <c r="J28" s="1">
-        <v>3</v>
+      <c r="J28" s="8">
+        <v>4</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="B29" s="1" t="s">
+      <c r="A29" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="B29" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C29" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D29" s="1">
-        <v>28.26</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F29" s="1">
-        <v>200</v>
+      <c r="C29" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D29" s="8">
+        <v>36.96</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F29" s="8">
+        <v>500</v>
       </c>
       <c r="G29" s="9">
-        <v>-105.21814476</v>
+        <v>-105.25444519</v>
       </c>
       <c r="H29" s="9">
-        <v>27.90179109</v>
+        <v>27.95329546</v>
       </c>
       <c r="I29" s="8" t="s">
         <v>332</v>
       </c>
-      <c r="J29" s="1">
-        <v>3</v>
+      <c r="J29" s="8">
+        <v>4</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="B30" s="1" t="s">
+      <c r="A30" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="B30" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D30" s="1">
-        <v>31.6</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F30" s="1">
-        <v>200</v>
+      <c r="C30" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="D30" s="8">
+        <v>37.5</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F30" s="8">
+        <v>150</v>
       </c>
       <c r="G30" s="9">
-        <v>-105.22875037999999</v>
+        <v>-105.25980885</v>
       </c>
       <c r="H30" s="9">
-        <v>27.922997729999999</v>
+        <v>27.952508229999999</v>
       </c>
       <c r="I30" s="8" t="s">
         <v>332</v>
       </c>
-      <c r="J30" s="1">
-        <v>3</v>
+      <c r="J30" s="8">
+        <v>4</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="B31" s="1" t="s">
+      <c r="A31" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="B31" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C31" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D31" s="1">
-        <v>32.51</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F31" s="1">
-        <v>200</v>
+      <c r="C31" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D31" s="8">
+        <v>38</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F31" s="8">
+        <v>100</v>
       </c>
       <c r="G31" s="9">
-        <v>-105.23515617</v>
+        <v>-105.26250278000001</v>
       </c>
       <c r="H31" s="9">
-        <v>27.928090149999999</v>
+        <v>27.95210556</v>
       </c>
       <c r="I31" s="8" t="s">
         <v>332</v>
       </c>
-      <c r="J31" s="1">
-        <v>3</v>
+      <c r="J31" s="8">
+        <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="B32" s="1" t="s">
+      <c r="A32" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="B32" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C32" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D32" s="1">
-        <v>33.340000000000003</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F32" s="1">
-        <v>150</v>
-      </c>
-      <c r="G32" s="9">
-        <v>-105.24074069</v>
+      <c r="C32" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D32" s="8">
+        <v>38.299999999999997</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F32" s="8">
+        <v>80</v>
+      </c>
+      <c r="G32" s="11">
+        <v>-105.26547778</v>
       </c>
       <c r="H32" s="9">
-        <v>27.93214682</v>
+        <v>27.95181389</v>
       </c>
       <c r="I32" s="8" t="s">
         <v>332</v>
       </c>
-      <c r="J32" s="1">
-        <v>3</v>
+      <c r="J32" s="8">
+        <v>4</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="B33" s="1" t="s">
+      <c r="A33" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="B33" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C33" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D33" s="1">
-        <v>34.020000000000003</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F33" s="1">
-        <v>200</v>
-      </c>
-      <c r="G33" s="9">
-        <v>-105.23723529999999</v>
-      </c>
-      <c r="H33" s="9">
-        <v>27.937600589999999</v>
+      <c r="C33" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="D33" s="8">
+        <v>38.67</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F33" s="8">
+        <v>40</v>
+      </c>
+      <c r="G33" s="12">
+        <v>-105.265784</v>
+      </c>
+      <c r="H33" s="12">
+        <v>27.951967</v>
       </c>
       <c r="I33" s="8" t="s">
         <v>332</v>
       </c>
-      <c r="J33" s="1">
+      <c r="J33" s="8">
         <v>4</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="B34" s="1" t="s">
+      <c r="A34" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="B34" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C34" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="D34" s="1">
-        <v>34.950000000000003</v>
-      </c>
-      <c r="E34" s="1" t="s">
+      <c r="C34" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="D34" s="8">
+        <v>38.799999999999997</v>
+      </c>
+      <c r="E34" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F34" s="1">
-        <v>500</v>
+      <c r="F34" s="8">
+        <v>300</v>
       </c>
       <c r="G34" s="9">
-        <v>-105.23711433</v>
+        <v>-105.27104099</v>
       </c>
       <c r="H34" s="9">
-        <v>27.947039270000001</v>
+        <v>27.956860160000002</v>
       </c>
       <c r="I34" s="8" t="s">
         <v>332</v>
       </c>
-      <c r="J34" s="1">
+      <c r="J34" s="8">
         <v>4</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="B35" s="1" t="s">
+      <c r="A35" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="B35" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C35" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D35" s="1">
-        <v>34.951999999999998</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F35" s="1">
-        <v>500</v>
+      <c r="C35" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D35" s="8">
+        <v>38.94</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F35" s="8">
+        <v>40</v>
       </c>
       <c r="G35" s="9">
-        <v>-105.23711435</v>
+        <v>-105.27143611</v>
       </c>
       <c r="H35" s="9">
-        <v>27.947039289999999</v>
+        <v>27.9573</v>
       </c>
       <c r="I35" s="8" t="s">
         <v>332</v>
       </c>
-      <c r="J35" s="1">
+      <c r="J35" s="8">
         <v>4</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="B36" s="1" t="s">
+      <c r="A36" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="B36" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C36" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="D36" s="1">
-        <v>34.979999999999997</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F36" s="1">
-        <v>150</v>
+      <c r="C36" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="D36" s="8">
+        <v>39.04</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F36" s="8">
+        <v>40</v>
       </c>
       <c r="G36" s="9">
-        <v>-105.23729136999999</v>
+        <v>-105.27214167</v>
       </c>
       <c r="H36" s="9">
-        <v>27.94707365</v>
+        <v>27.957955559999998</v>
       </c>
       <c r="I36" s="8" t="s">
         <v>332</v>
       </c>
-      <c r="J36" s="1">
+      <c r="J36" s="8">
         <v>4</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="B37" s="1" t="s">
+      <c r="A37" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="B37" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C37" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D37" s="1">
-        <v>36.6</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F37" s="1">
-        <v>200</v>
-      </c>
-      <c r="G37" s="9">
-        <v>-105.23754886</v>
+      <c r="C37" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D37" s="8">
+        <v>39.270000000000003</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F37" s="8">
+        <v>40</v>
+      </c>
+      <c r="G37" s="11">
+        <v>-105.27378611</v>
       </c>
       <c r="H37" s="9">
-        <v>27.947098799999999</v>
+        <v>27.959533329999999</v>
       </c>
       <c r="I37" s="8" t="s">
         <v>332</v>
       </c>
-      <c r="J37" s="1">
+      <c r="J37" s="8">
         <v>4</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="B38" s="1" t="s">
+      <c r="A38" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="B38" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C38" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D38" s="1">
-        <v>36.96</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F38" s="1">
-        <v>500</v>
+      <c r="C38" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D38" s="8">
+        <v>39.78</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F38" s="8">
+        <v>100</v>
       </c>
       <c r="G38" s="9">
-        <v>-105.25444519</v>
+        <v>-105.27726006</v>
       </c>
       <c r="H38" s="9">
-        <v>27.95329546</v>
+        <v>27.962909499999999</v>
       </c>
       <c r="I38" s="8" t="s">
         <v>332</v>
       </c>
-      <c r="J38" s="1">
+      <c r="J38" s="8">
         <v>4</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="B39" s="1" t="s">
+      <c r="A39" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="B39" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C39" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D39" s="1">
-        <v>37.5</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F39" s="1">
-        <v>150</v>
+      <c r="C39" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="D39" s="8">
+        <v>39.79</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F39" s="8">
+        <v>40</v>
       </c>
       <c r="G39" s="9">
-        <v>-105.25980885</v>
+        <v>-105.27582778</v>
       </c>
       <c r="H39" s="9">
-        <v>27.952508229999999</v>
+        <v>27.961486109999999</v>
       </c>
       <c r="I39" s="8" t="s">
         <v>332</v>
       </c>
-      <c r="J39" s="1">
+      <c r="J39" s="8">
         <v>4</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="8" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="B40" s="8" t="s">
         <v>13</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="D40" s="8">
-        <v>38</v>
+        <v>40.06</v>
       </c>
       <c r="E40" s="8" t="s">
         <v>60</v>
       </c>
       <c r="F40" s="8">
-        <v>100</v>
-      </c>
-      <c r="G40" s="9" t="s">
-        <v>336</v>
-      </c>
-      <c r="H40" s="9" t="s">
-        <v>337</v>
+        <v>60</v>
+      </c>
+      <c r="G40" s="9">
+        <v>-105.27778056</v>
+      </c>
+      <c r="H40" s="9">
+        <v>27.963333330000001</v>
       </c>
       <c r="I40" s="8" t="s">
         <v>332</v>
@@ -3565,28 +3453,28 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="B41" s="8" t="s">
         <v>13</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="D41" s="8">
-        <v>38.299999999999997</v>
+        <v>40.26</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="F41" s="8">
-        <v>80</v>
-      </c>
-      <c r="G41" s="9" t="s">
-        <v>338</v>
-      </c>
-      <c r="H41" s="9" t="s">
-        <v>339</v>
+        <v>400</v>
+      </c>
+      <c r="G41" s="9">
+        <v>-105.28063009</v>
+      </c>
+      <c r="H41" s="9">
+        <v>27.966191599999998</v>
       </c>
       <c r="I41" s="8" t="s">
         <v>332</v>
@@ -3597,828 +3485,828 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="8" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="B42" s="8" t="s">
         <v>13</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="D42" s="8">
-        <v>38.67</v>
+        <v>41.08</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="F42" s="8">
-        <v>40</v>
-      </c>
-      <c r="G42" s="9" t="s">
-        <v>340</v>
-      </c>
-      <c r="H42" s="9" t="s">
-        <v>341</v>
+        <v>150</v>
+      </c>
+      <c r="G42" s="9">
+        <v>-105.28573684</v>
+      </c>
+      <c r="H42" s="9">
+        <v>27.97063627</v>
       </c>
       <c r="I42" s="8" t="s">
         <v>332</v>
       </c>
       <c r="J42" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="B43" s="1" t="s">
+      <c r="A43" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="B43" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C43" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="D43" s="1">
-        <v>38.799999999999997</v>
-      </c>
-      <c r="E43" s="1" t="s">
+      <c r="C43" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="D43" s="8">
+        <v>41.91</v>
+      </c>
+      <c r="E43" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F43" s="1">
-        <v>300</v>
+      <c r="F43" s="8">
+        <v>400</v>
       </c>
       <c r="G43" s="9">
-        <v>-105.27104099</v>
+        <v>-105.2903634</v>
       </c>
       <c r="H43" s="9">
-        <v>27.956860160000002</v>
+        <v>27.978049729999999</v>
       </c>
       <c r="I43" s="8" t="s">
         <v>332</v>
       </c>
-      <c r="J43" s="1">
-        <v>4</v>
+      <c r="J43" s="8">
+        <v>5</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="8" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="B44" s="8" t="s">
         <v>13</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="D44" s="8">
-        <v>38.94</v>
+        <v>42.26</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="F44" s="8">
-        <v>40</v>
-      </c>
-      <c r="G44" s="9" t="s">
-        <v>342</v>
-      </c>
-      <c r="H44" s="9" t="s">
-        <v>343</v>
+        <v>200</v>
+      </c>
+      <c r="G44" s="9">
+        <v>-105.29259601</v>
+      </c>
+      <c r="H44" s="9">
+        <v>27.980258190000001</v>
       </c>
       <c r="I44" s="8" t="s">
         <v>332</v>
       </c>
       <c r="J44" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="B45" s="8" t="s">
         <v>13</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="D45" s="8">
-        <v>39.04</v>
+        <v>42.99</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="F45" s="8">
-        <v>40</v>
-      </c>
-      <c r="G45" s="9" t="s">
-        <v>344</v>
-      </c>
-      <c r="H45" s="9" t="s">
-        <v>345</v>
+        <v>200</v>
+      </c>
+      <c r="G45" s="9">
+        <v>-105.29633056</v>
+      </c>
+      <c r="H45" s="9">
+        <v>27.985994439999999</v>
       </c>
       <c r="I45" s="8" t="s">
         <v>332</v>
       </c>
       <c r="J45" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="8" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="B46" s="8" t="s">
         <v>13</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="D46" s="8">
-        <v>39.270000000000003</v>
+        <v>43.36</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="F46" s="8">
-        <v>40</v>
-      </c>
-      <c r="G46" s="9" t="s">
-        <v>346</v>
-      </c>
-      <c r="H46" s="9" t="s">
-        <v>347</v>
+        <v>200</v>
+      </c>
+      <c r="G46" s="9">
+        <v>-105.29749196</v>
+      </c>
+      <c r="H46" s="9">
+        <v>27.988156709999998</v>
       </c>
       <c r="I46" s="8" t="s">
         <v>332</v>
       </c>
       <c r="J46" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="B47" s="1" t="s">
+      <c r="A47" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="B47" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C47" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D47" s="1">
-        <v>39.78</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F47" s="1">
-        <v>100</v>
+      <c r="C47" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D47" s="8">
+        <v>43.71</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F47" s="8">
+        <v>400</v>
       </c>
       <c r="G47" s="9">
-        <v>-105.27726006</v>
+        <v>-105.30043954</v>
       </c>
       <c r="H47" s="9">
-        <v>27.962909499999999</v>
+        <v>27.991423139999998</v>
       </c>
       <c r="I47" s="8" t="s">
         <v>332</v>
       </c>
-      <c r="J47" s="1">
-        <v>4</v>
+      <c r="J47" s="8">
+        <v>5</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="8" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="B48" s="8" t="s">
         <v>13</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="D48" s="8">
-        <v>39.79</v>
+        <v>43.74</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="F48" s="8">
-        <v>40</v>
-      </c>
-      <c r="G48" s="9" t="s">
-        <v>348</v>
-      </c>
-      <c r="H48" s="9" t="s">
-        <v>349</v>
+        <v>150</v>
+      </c>
+      <c r="G48" s="9">
+        <v>-105.30089099</v>
+      </c>
+      <c r="H48" s="9">
+        <v>27.991641319999999</v>
       </c>
       <c r="I48" s="8" t="s">
         <v>332</v>
       </c>
       <c r="J48" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="B49" s="8" t="s">
         <v>13</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="D49" s="8">
-        <v>40.06</v>
+        <v>44.54</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="F49" s="8">
-        <v>60</v>
-      </c>
-      <c r="G49" s="9" t="s">
-        <v>350</v>
-      </c>
-      <c r="H49" s="9" t="s">
-        <v>351</v>
+        <v>150</v>
+      </c>
+      <c r="G49" s="9">
+        <v>-105.30767815</v>
+      </c>
+      <c r="H49" s="9">
+        <v>27.989236139999999</v>
       </c>
       <c r="I49" s="8" t="s">
         <v>332</v>
       </c>
       <c r="J49" s="8">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="B50" s="1" t="s">
+      <c r="A50" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="B50" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C50" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="D50" s="1">
-        <v>40.26</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F50" s="1">
-        <v>400</v>
+      <c r="C50" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="D50" s="8">
+        <v>44.8</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F50" s="8">
+        <v>200</v>
       </c>
       <c r="G50" s="9">
-        <v>-105.28063009</v>
+        <v>-105.31023949</v>
       </c>
       <c r="H50" s="9">
-        <v>27.966191599999998</v>
+        <v>27.9891431</v>
       </c>
       <c r="I50" s="8" t="s">
         <v>332</v>
       </c>
-      <c r="J50" s="1">
-        <v>4</v>
+      <c r="J50" s="8">
+        <v>5</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="B51" s="1" t="s">
+      <c r="A51" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="B51" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C51" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="D51" s="1">
-        <v>41.08</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F51" s="1">
-        <v>150</v>
+      <c r="C51" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="D51" s="8">
+        <v>44.95</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F51" s="8">
+        <v>200</v>
       </c>
       <c r="G51" s="9">
-        <v>-105.28573684</v>
+        <v>-105.31295607</v>
       </c>
       <c r="H51" s="9">
-        <v>27.97063627</v>
+        <v>27.99550035</v>
       </c>
       <c r="I51" s="8" t="s">
         <v>332</v>
       </c>
-      <c r="J51" s="1">
+      <c r="J51" s="8">
         <v>5</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="B52" s="1" t="s">
+      <c r="A52" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="B52" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C52" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="D52" s="1">
-        <v>41.91</v>
-      </c>
-      <c r="E52" s="1" t="s">
+      <c r="C52" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="D52" s="8">
+        <v>46.5</v>
+      </c>
+      <c r="E52" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F52" s="1">
-        <v>400</v>
+      <c r="F52" s="8">
+        <v>600</v>
       </c>
       <c r="G52" s="9">
-        <v>-105.2903634</v>
+        <v>-105.31206826</v>
       </c>
       <c r="H52" s="9">
-        <v>27.978049729999999</v>
+        <v>28.000137890000001</v>
       </c>
       <c r="I52" s="8" t="s">
         <v>332</v>
       </c>
-      <c r="J52" s="1">
+      <c r="J52" s="8">
         <v>5</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="B53" s="1" t="s">
+      <c r="A53" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="B53" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C53" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="D53" s="1">
-        <v>42.26</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F53" s="1">
+      <c r="C53" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="D53" s="8">
+        <v>47.64</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F53" s="8">
         <v>200</v>
       </c>
       <c r="G53" s="9">
-        <v>-105.29259601</v>
+        <v>-105.31761667000001</v>
       </c>
       <c r="H53" s="9">
-        <v>27.980258190000001</v>
+        <v>28.00923611</v>
       </c>
       <c r="I53" s="8" t="s">
         <v>332</v>
       </c>
-      <c r="J53" s="1">
+      <c r="J53" s="8">
         <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="D54" s="1">
-        <v>42.99</v>
-      </c>
-      <c r="E54" s="1" t="s">
+      <c r="A54" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="B54" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D54" s="8">
+        <v>48.42</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F54" s="8">
+        <v>800</v>
+      </c>
+      <c r="G54" s="9">
+        <v>-105.3240962</v>
+      </c>
+      <c r="H54" s="9">
+        <v>28.012186960000001</v>
+      </c>
+      <c r="I54" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="J54" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A55" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="C55" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="D55" s="8">
+        <v>49.872</v>
+      </c>
+      <c r="E55" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F54" s="1">
-        <v>200</v>
-      </c>
-      <c r="G54" s="9" t="s">
-        <v>352</v>
-      </c>
-      <c r="H54" s="9" t="s">
-        <v>353</v>
-      </c>
-      <c r="I54" s="8" t="s">
-        <v>332</v>
-      </c>
-      <c r="J54" s="1">
+      <c r="F55" s="8">
+        <v>600</v>
+      </c>
+      <c r="G55" s="9">
+        <v>-105.32611667</v>
+      </c>
+      <c r="H55" s="9">
+        <v>28.023483330000001</v>
+      </c>
+      <c r="I55" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="J55" s="8">
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D55" s="1">
-        <v>43.36</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F55" s="1">
-        <v>200</v>
-      </c>
-      <c r="G55" s="9">
-        <v>-105.29749196</v>
-      </c>
-      <c r="H55" s="9">
-        <v>27.988156709999998</v>
-      </c>
-      <c r="I55" s="8" t="s">
-        <v>332</v>
-      </c>
-      <c r="J55" s="1">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A56" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="B56" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="D56" s="8">
+        <v>55.37</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F56" s="8">
+        <v>600</v>
+      </c>
+      <c r="G56" s="9">
+        <v>-105.35649905</v>
+      </c>
+      <c r="H56" s="9">
+        <v>28.054997449999998</v>
+      </c>
+      <c r="I56" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="J56" s="8">
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="D56" s="1">
-        <v>43.71</v>
-      </c>
-      <c r="E56" s="1" t="s">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A57" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="B57" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="C57" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D57" s="8">
+        <v>57.29</v>
+      </c>
+      <c r="E57" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F57" s="8">
+        <v>600</v>
+      </c>
+      <c r="G57" s="9">
+        <v>-105.36098611</v>
+      </c>
+      <c r="H57" s="9">
+        <v>28.067377780000001</v>
+      </c>
+      <c r="I57" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="J57" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="B58" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="D58" s="8">
+        <v>62.16</v>
+      </c>
+      <c r="E58" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F58" s="8">
+        <v>600</v>
+      </c>
+      <c r="G58" s="9">
+        <v>-105.39453444999999</v>
+      </c>
+      <c r="H58" s="9">
+        <v>28.082670799999999</v>
+      </c>
+      <c r="I58" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="J58" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="B59" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="C59" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="D59" s="8">
+        <v>49.04</v>
+      </c>
+      <c r="E59" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F59" s="8">
+        <v>800</v>
+      </c>
+      <c r="G59" s="9">
+        <v>-105.32486768</v>
+      </c>
+      <c r="H59" s="9">
+        <v>28.016605810000001</v>
+      </c>
+      <c r="I59" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="J59" s="8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="B60" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="D60" s="8">
+        <v>49.64</v>
+      </c>
+      <c r="E60" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F56" s="1">
+      <c r="F60" s="8">
         <v>400</v>
       </c>
-      <c r="G56" s="9">
-        <v>-105.30043954</v>
-      </c>
-      <c r="H56" s="9">
-        <v>27.991423139999998</v>
-      </c>
-      <c r="I56" s="8" t="s">
-        <v>332</v>
-      </c>
-      <c r="J56" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="D57" s="1">
-        <v>43.74</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F57" s="1">
+      <c r="G60" s="9">
+        <v>-105.32485167</v>
+      </c>
+      <c r="H60" s="9">
+        <v>28.021578210000001</v>
+      </c>
+      <c r="I60" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="J60" s="8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A61" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="B61" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="C61" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="D61" s="8">
+        <v>49.7</v>
+      </c>
+      <c r="E61" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F61" s="8">
         <v>150</v>
       </c>
-      <c r="G57" s="9">
-        <v>-105.30089099</v>
-      </c>
-      <c r="H57" s="9">
-        <v>27.991641319999999</v>
-      </c>
-      <c r="I57" s="8" t="s">
-        <v>332</v>
-      </c>
-      <c r="J57" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D58" s="1">
-        <v>44.54</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F58" s="1">
-        <v>150</v>
-      </c>
-      <c r="G58" s="9">
-        <v>-105.30767815</v>
-      </c>
-      <c r="H58" s="9">
-        <v>27.989236139999999</v>
-      </c>
-      <c r="I58" s="8" t="s">
-        <v>332</v>
-      </c>
-      <c r="J58" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="D59" s="1">
-        <v>44.8</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F59" s="1">
-        <v>200</v>
-      </c>
-      <c r="G59" s="9">
-        <v>-105.31023949</v>
-      </c>
-      <c r="H59" s="9">
-        <v>27.9891431</v>
-      </c>
-      <c r="I59" s="8" t="s">
-        <v>332</v>
-      </c>
-      <c r="J59" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D60" s="1">
-        <v>44.95</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F60" s="1">
-        <v>200</v>
-      </c>
-      <c r="G60" s="9">
-        <v>-105.31295607</v>
-      </c>
-      <c r="H60" s="9">
-        <v>27.99550035</v>
-      </c>
-      <c r="I60" s="8" t="s">
-        <v>332</v>
-      </c>
-      <c r="J60" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D61" s="1">
-        <v>46.5</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F61" s="1">
-        <v>600</v>
-      </c>
       <c r="G61" s="9">
-        <v>-105.31206826</v>
+        <v>-105.32513062</v>
       </c>
       <c r="H61" s="9">
-        <v>28.000137890000001</v>
+        <v>28.022209700000001</v>
       </c>
       <c r="I61" s="8" t="s">
-        <v>332</v>
-      </c>
-      <c r="J61" s="1">
-        <v>5</v>
+        <v>136</v>
+      </c>
+      <c r="J61" s="8">
+        <v>6</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="8" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>13</v>
+        <v>331</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="D62" s="8">
-        <v>47.64</v>
+        <v>49.87</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="F62" s="8">
-        <v>200</v>
-      </c>
-      <c r="G62" s="9" t="s">
-        <v>356</v>
-      </c>
-      <c r="H62" s="9" t="s">
-        <v>357</v>
+        <v>120</v>
+      </c>
+      <c r="G62" s="9">
+        <v>-105.32487777999999</v>
+      </c>
+      <c r="H62" s="9">
+        <v>28.021630559999998</v>
       </c>
       <c r="I62" s="8" t="s">
-        <v>332</v>
-      </c>
-      <c r="J62" s="1">
-        <v>5</v>
+        <v>136</v>
+      </c>
+      <c r="J62" s="8">
+        <v>6</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D63" s="1">
-        <v>48.42</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F63" s="1">
-        <v>800</v>
+      <c r="A63" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="B63" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="C63" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D63" s="8">
+        <v>50.5</v>
+      </c>
+      <c r="E63" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F63" s="8">
+        <v>100</v>
       </c>
       <c r="G63" s="9">
-        <v>-105.3240962</v>
+        <v>-105.33104413</v>
       </c>
       <c r="H63" s="9">
-        <v>28.012186960000001</v>
-      </c>
-      <c r="I63" s="1" t="s">
+        <v>28.026579439999999</v>
+      </c>
+      <c r="I63" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="J63" s="1">
-        <v>5</v>
+      <c r="J63" s="8">
+        <v>6</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A64" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="B64" s="1" t="s">
+      <c r="A64" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="B64" s="8" t="s">
         <v>331</v>
       </c>
-      <c r="C64" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="D64" s="1">
-        <v>49.04</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F64" s="1">
-        <v>800</v>
+      <c r="C64" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D64" s="8">
+        <v>51.09</v>
+      </c>
+      <c r="E64" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F64" s="8">
+        <v>150</v>
       </c>
       <c r="G64" s="9">
-        <v>-105.32486768</v>
+        <v>-105.33677668</v>
       </c>
       <c r="H64" s="9">
-        <v>28.016605810000001</v>
-      </c>
-      <c r="I64" s="1" t="s">
+        <v>28.028726209999999</v>
+      </c>
+      <c r="I64" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="J64" s="1">
+      <c r="J64" s="8">
         <v>6</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="B65" s="1" t="s">
+      <c r="A65" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="B65" s="8" t="s">
         <v>331</v>
       </c>
-      <c r="C65" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="D65" s="1">
-        <v>49.64</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F65" s="1">
-        <v>400</v>
+      <c r="C65" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="D65" s="8">
+        <v>52.36</v>
+      </c>
+      <c r="E65" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F65" s="8">
+        <v>100</v>
       </c>
       <c r="G65" s="9">
-        <v>-105.32485167</v>
+        <v>-105.33835558</v>
       </c>
       <c r="H65" s="9">
-        <v>28.021578210000001</v>
-      </c>
-      <c r="I65" s="1" t="s">
+        <v>28.037389829999999</v>
+      </c>
+      <c r="I65" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="J65" s="1">
+      <c r="J65" s="8">
         <v>6</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="B66" s="1" t="s">
+      <c r="A66" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="B66" s="8" t="s">
         <v>331</v>
       </c>
-      <c r="C66" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="D66" s="1">
-        <v>49.7</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F66" s="1">
+      <c r="C66" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="D66" s="8">
+        <v>50.9</v>
+      </c>
+      <c r="E66" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F66" s="8">
         <v>150</v>
       </c>
       <c r="G66" s="9">
-        <v>-105.32513062</v>
+        <v>-105.33761831</v>
       </c>
       <c r="H66" s="9">
-        <v>28.022209700000001</v>
-      </c>
-      <c r="I66" s="1" t="s">
+        <v>28.041947489999998</v>
+      </c>
+      <c r="I66" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="J66" s="1">
+      <c r="J66" s="8">
         <v>6</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="B67" s="8" t="s">
         <v>331</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D67" s="8">
-        <v>49.87</v>
+        <v>53.14</v>
       </c>
       <c r="E67" s="8" t="s">
         <v>48</v>
       </c>
       <c r="F67" s="8">
-        <v>120</v>
-      </c>
-      <c r="G67" s="9" t="s">
-        <v>364</v>
-      </c>
-      <c r="H67" s="9" t="s">
-        <v>365</v>
+        <v>150</v>
+      </c>
+      <c r="G67" s="9">
+        <v>-105.33914449</v>
+      </c>
+      <c r="H67" s="9">
+        <v>28.043404020000001</v>
       </c>
       <c r="I67" s="8" t="s">
         <v>136</v>
@@ -4428,573 +4316,573 @@
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A68" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="D68" s="1">
-        <v>49.872</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F68" s="1">
-        <v>600</v>
-      </c>
-      <c r="G68" s="9" t="s">
-        <v>360</v>
-      </c>
-      <c r="H68" s="9" t="s">
-        <v>361</v>
-      </c>
-      <c r="I68" s="1" t="s">
+      <c r="A68" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="B68" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="C68" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="D68" s="8">
+        <v>53.38</v>
+      </c>
+      <c r="E68" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F68" s="8">
+        <v>250</v>
+      </c>
+      <c r="G68" s="9">
+        <v>-105.34160726</v>
+      </c>
+      <c r="H68" s="9">
+        <v>28.044510509999999</v>
+      </c>
+      <c r="I68" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="J68" s="1">
-        <v>5</v>
+      <c r="J68" s="8">
+        <v>6</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A69" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="B69" s="1" t="s">
+      <c r="A69" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="B69" s="8" t="s">
         <v>331</v>
       </c>
-      <c r="C69" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D69" s="1">
-        <v>50.5</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F69" s="1">
+      <c r="C69" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="D69" s="8">
+        <v>53.9</v>
+      </c>
+      <c r="E69" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F69" s="8">
+        <v>350</v>
+      </c>
+      <c r="G69" s="9">
+        <v>-105.34165914</v>
+      </c>
+      <c r="H69" s="9">
+        <v>28.044526940000001</v>
+      </c>
+      <c r="I69" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="J69" s="8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A70" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="B70" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="C70" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="D70" s="8">
+        <v>54.41</v>
+      </c>
+      <c r="E70" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F70" s="8">
         <v>100</v>
       </c>
-      <c r="G69" s="9">
-        <v>-105.33104413</v>
-      </c>
-      <c r="H69" s="9">
-        <v>28.026579439999999</v>
-      </c>
-      <c r="I69" s="1" t="s">
+      <c r="G70" s="9">
+        <v>-105.34921065</v>
+      </c>
+      <c r="H70" s="9">
+        <v>28.05042461</v>
+      </c>
+      <c r="I70" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="J69" s="1">
+      <c r="J70" s="8">
         <v>6</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A70" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="B70" s="1" t="s">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A71" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="B71" s="8" t="s">
         <v>331</v>
       </c>
-      <c r="C70" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="D70" s="1">
-        <v>50.9</v>
-      </c>
-      <c r="E70" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F70" s="1">
+      <c r="C71" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D71" s="8">
+        <v>55.03</v>
+      </c>
+      <c r="E71" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F71" s="8">
+        <v>100</v>
+      </c>
+      <c r="G71" s="9">
+        <v>-105.35306607</v>
+      </c>
+      <c r="H71" s="9">
+        <v>28.054693180000001</v>
+      </c>
+      <c r="I71" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="J71" s="8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A72" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="B72" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="C72" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="D72" s="8">
+        <v>55.36</v>
+      </c>
+      <c r="E72" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F72" s="8">
+        <v>500</v>
+      </c>
+      <c r="G72" s="9">
+        <v>-105.35636175</v>
+      </c>
+      <c r="H72" s="9">
+        <v>28.054971210000001</v>
+      </c>
+      <c r="I72" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="J72" s="8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A73" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="B73" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="C73" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="D73" s="8">
+        <v>56.36</v>
+      </c>
+      <c r="E73" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F73" s="8">
+        <v>200</v>
+      </c>
+      <c r="G73" s="9">
+        <v>-105.35787544</v>
+      </c>
+      <c r="H73" s="9">
+        <v>28.062200019999999</v>
+      </c>
+      <c r="I73" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="J73" s="8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A74" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="B74" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="C74" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="D74" s="8">
+        <v>56.36</v>
+      </c>
+      <c r="E74" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F74" s="8">
+        <v>100</v>
+      </c>
+      <c r="G74" s="9">
+        <v>-105.35785373</v>
+      </c>
+      <c r="H74" s="9">
+        <v>28.062313</v>
+      </c>
+      <c r="I74" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="J74" s="8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A75" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="B75" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="C75" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="D75" s="8">
+        <v>57.14</v>
+      </c>
+      <c r="E75" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F75" s="8">
+        <v>700</v>
+      </c>
+      <c r="G75" s="9">
+        <v>-105.36198308</v>
+      </c>
+      <c r="H75" s="9">
+        <v>28.068257030000002</v>
+      </c>
+      <c r="I75" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="J75" s="8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A76" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="B76" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="C76" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="D76" s="8">
+        <v>57.15</v>
+      </c>
+      <c r="E76" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F76" s="8">
+        <v>500</v>
+      </c>
+      <c r="G76" s="9">
+        <v>-105.36214425999999</v>
+      </c>
+      <c r="H76" s="9">
+        <v>28.068353170000002</v>
+      </c>
+      <c r="I76" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="J76" s="8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A77" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="B77" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="C77" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="D77" s="8">
+        <v>57.29</v>
+      </c>
+      <c r="E77" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F77" s="8">
+        <v>120</v>
+      </c>
+      <c r="G77" s="9">
+        <v>-105.36342777999999</v>
+      </c>
+      <c r="H77" s="9">
+        <v>28.068172220000001</v>
+      </c>
+      <c r="I77" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="J77" s="8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A78" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="B78" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="C78" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="D78" s="8">
+        <v>58.6</v>
+      </c>
+      <c r="E78" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F78" s="8">
         <v>150</v>
       </c>
-      <c r="G70" s="9">
-        <v>-105.33761831</v>
-      </c>
-      <c r="H70" s="9">
-        <v>28.041947489999998</v>
-      </c>
-      <c r="I70" s="1" t="s">
+      <c r="G78" s="9">
+        <v>-105.37317283</v>
+      </c>
+      <c r="H78" s="9">
+        <v>28.06971858</v>
+      </c>
+      <c r="I78" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="J70" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A71" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="B71" s="1" t="s">
+      <c r="J78" s="8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A79" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="B79" s="8" t="s">
         <v>331</v>
       </c>
-      <c r="C71" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="D71" s="1">
-        <v>51.09</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F71" s="1">
-        <v>150</v>
-      </c>
-      <c r="G71" s="9">
-        <v>-105.33677668</v>
-      </c>
-      <c r="H71" s="9">
-        <v>28.028726209999999</v>
-      </c>
-      <c r="I71" s="1" t="s">
+      <c r="C79" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="D79" s="8">
+        <v>58.76</v>
+      </c>
+      <c r="E79" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F79" s="8">
+        <v>500</v>
+      </c>
+      <c r="G79" s="9">
+        <v>-105.3748234</v>
+      </c>
+      <c r="H79" s="9">
+        <v>28.070505730000001</v>
+      </c>
+      <c r="I79" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="J71" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A72" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="B72" s="1" t="s">
+      <c r="J79" s="8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A80" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="B80" s="8" t="s">
         <v>331</v>
       </c>
-      <c r="C72" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="D72" s="1">
-        <v>52.36</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F72" s="1">
+      <c r="C80" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D80" s="8">
+        <v>60.3</v>
+      </c>
+      <c r="E80" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F80" s="8">
         <v>100</v>
       </c>
-      <c r="G72" s="9">
-        <v>-105.33835558</v>
-      </c>
-      <c r="H72" s="9">
-        <v>28.037389829999999</v>
-      </c>
-      <c r="I72" s="1" t="s">
+      <c r="G80" s="9">
+        <v>-105.38525518</v>
+      </c>
+      <c r="H80" s="9">
+        <v>28.073751619999999</v>
+      </c>
+      <c r="I80" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="J72" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A73" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="B73" s="1" t="s">
+      <c r="J80" s="8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A81" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="B81" s="8" t="s">
         <v>331</v>
       </c>
-      <c r="C73" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="D73" s="1">
-        <v>53.14</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F73" s="1">
-        <v>150</v>
-      </c>
-      <c r="G73" s="9">
-        <v>-105.33914449</v>
-      </c>
-      <c r="H73" s="9">
-        <v>28.043404020000001</v>
-      </c>
-      <c r="I73" s="1" t="s">
+      <c r="C81" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="D81" s="8">
+        <v>61.03</v>
+      </c>
+      <c r="E81" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F81" s="8">
+        <v>200</v>
+      </c>
+      <c r="G81" s="9">
+        <v>-105.3870215</v>
+      </c>
+      <c r="H81" s="9">
+        <v>28.080127730000001</v>
+      </c>
+      <c r="I81" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="J73" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A74" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="B74" s="1" t="s">
+      <c r="J81" s="8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A82" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="B82" s="8" t="s">
         <v>331</v>
       </c>
-      <c r="C74" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="D74" s="1">
-        <v>53.38</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F74" s="1">
-        <v>250</v>
-      </c>
-      <c r="G74" s="9">
-        <v>-105.34160726</v>
-      </c>
-      <c r="H74" s="9">
-        <v>28.044510509999999</v>
-      </c>
-      <c r="I74" s="1" t="s">
+      <c r="C82" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D82" s="8">
+        <v>62.63</v>
+      </c>
+      <c r="E82" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F82" s="8">
+        <v>100</v>
+      </c>
+      <c r="G82" s="9">
+        <v>-105.39425558000001</v>
+      </c>
+      <c r="H82" s="9">
+        <v>28.087006259999999</v>
+      </c>
+      <c r="I82" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="J74" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A75" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="B75" s="1" t="s">
+      <c r="J82" s="8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A83" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="B83" s="8" t="s">
         <v>331</v>
       </c>
-      <c r="C75" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="D75" s="1">
-        <v>53.9</v>
-      </c>
-      <c r="E75" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F75" s="1">
-        <v>350</v>
-      </c>
-      <c r="G75" s="9">
-        <v>-105.34165914</v>
-      </c>
-      <c r="H75" s="9">
-        <v>28.044526940000001</v>
-      </c>
-      <c r="I75" s="1" t="s">
+      <c r="C83" s="13" t="s">
+        <v>341</v>
+      </c>
+      <c r="D83" s="8">
+        <v>62.8</v>
+      </c>
+      <c r="E83" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F83" s="8">
+        <v>500</v>
+      </c>
+      <c r="G83" s="9">
+        <v>-105.39407772</v>
+      </c>
+      <c r="H83" s="9">
+        <v>28.08851215</v>
+      </c>
+      <c r="I83" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="J75" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A76" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D76" s="1">
-        <v>54.41</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F76" s="1">
-        <v>100</v>
-      </c>
-      <c r="G76" s="9">
-        <v>-105.34921065</v>
-      </c>
-      <c r="H76" s="9">
-        <v>28.05042461</v>
-      </c>
-      <c r="I76" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="J76" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A77" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="D77" s="1">
-        <v>55.03</v>
-      </c>
-      <c r="E77" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F77" s="1">
-        <v>100</v>
-      </c>
-      <c r="G77" s="9">
-        <v>-105.35306607</v>
-      </c>
-      <c r="H77" s="9">
-        <v>28.054693180000001</v>
-      </c>
-      <c r="I77" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="J77" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A78" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="D78" s="1">
-        <v>55.36</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F78" s="1">
-        <v>500</v>
-      </c>
-      <c r="G78" s="9">
-        <v>-105.35636175</v>
-      </c>
-      <c r="H78" s="9">
-        <v>28.054971210000001</v>
-      </c>
-      <c r="I78" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="J78" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A79" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="C79" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="D79" s="1">
-        <v>55.37</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F79" s="1">
-        <v>600</v>
-      </c>
-      <c r="G79" s="9">
-        <v>-105.35649905</v>
-      </c>
-      <c r="H79" s="9">
-        <v>28.054997449999998</v>
-      </c>
-      <c r="I79" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="J79" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A80" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D80" s="1">
-        <v>56.36</v>
-      </c>
-      <c r="E80" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F80" s="1">
-        <v>200</v>
-      </c>
-      <c r="G80" s="9">
-        <v>-105.35787544</v>
-      </c>
-      <c r="H80" s="9">
-        <v>28.062200019999999</v>
-      </c>
-      <c r="I80" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="J80" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A81" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="D81" s="1">
-        <v>56.36</v>
-      </c>
-      <c r="E81" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F81" s="1">
-        <v>100</v>
-      </c>
-      <c r="G81" s="9">
-        <v>-105.35785373</v>
-      </c>
-      <c r="H81" s="9">
-        <v>28.062313</v>
-      </c>
-      <c r="I81" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="J81" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A82" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="D82" s="1">
-        <v>57.14</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F82" s="1">
-        <v>700</v>
-      </c>
-      <c r="G82" s="9">
-        <v>-105.36198308</v>
-      </c>
-      <c r="H82" s="9">
-        <v>28.068257030000002</v>
-      </c>
-      <c r="I82" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="J82" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A83" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="D83" s="1">
-        <v>57.15</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F83" s="1">
-        <v>500</v>
-      </c>
-      <c r="G83" s="9">
-        <v>-105.36214425999999</v>
-      </c>
-      <c r="H83" s="9">
-        <v>28.068353170000002</v>
-      </c>
-      <c r="I83" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="J83" s="1">
+      <c r="J83" s="8">
         <v>7</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" s="8" t="s">
-        <v>227</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>358</v>
+        <v>253</v>
+      </c>
+      <c r="B84" s="8" t="s">
+        <v>331</v>
       </c>
       <c r="C84" s="8" t="s">
-        <v>84</v>
+        <v>110</v>
       </c>
       <c r="D84" s="8">
-        <v>57.29</v>
+        <v>63.71</v>
       </c>
       <c r="E84" s="8" t="s">
         <v>48</v>
       </c>
       <c r="F84" s="8">
-        <v>600</v>
-      </c>
-      <c r="G84" s="9" t="s">
-        <v>362</v>
-      </c>
-      <c r="H84" s="9" t="s">
-        <v>363</v>
-      </c>
-      <c r="I84" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="G84" s="9">
+        <v>-105.39672222</v>
+      </c>
+      <c r="H84" s="9">
+        <v>28.09431944</v>
+      </c>
+      <c r="I84" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="J84" s="1">
-        <v>5</v>
+      <c r="J84" s="8">
+        <v>7</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="B85" s="8" t="s">
         <v>331</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="D85" s="8">
-        <v>57.29</v>
+        <v>64.25</v>
       </c>
       <c r="E85" s="8" t="s">
         <v>48</v>
       </c>
       <c r="F85" s="8">
-        <v>120</v>
-      </c>
-      <c r="G85" s="9" t="s">
-        <v>366</v>
-      </c>
-      <c r="H85" s="9" t="s">
-        <v>367</v>
+        <v>250</v>
+      </c>
+      <c r="G85" s="9">
+        <v>-105.39665105</v>
+      </c>
+      <c r="H85" s="9">
+        <v>28.098379659999999</v>
       </c>
       <c r="I85" s="8" t="s">
         <v>136</v>
@@ -5004,605 +4892,605 @@
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A86" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="B86" s="1" t="s">
+      <c r="A86" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="B86" s="8" t="s">
         <v>331</v>
       </c>
-      <c r="C86" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D86" s="1">
-        <v>58.6</v>
-      </c>
-      <c r="E86" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F86" s="1">
+      <c r="C86" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D86" s="8">
+        <v>64.34</v>
+      </c>
+      <c r="E86" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F86" s="8">
+        <v>500</v>
+      </c>
+      <c r="G86" s="9">
+        <v>-105.396456</v>
+      </c>
+      <c r="H86" s="9">
+        <v>28.098824409999999</v>
+      </c>
+      <c r="I86" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="J86" s="8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A87" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="B87" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="C87" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="D87" s="8">
+        <v>64.540000000000006</v>
+      </c>
+      <c r="E87" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F87" s="8">
+        <v>500</v>
+      </c>
+      <c r="G87" s="9">
+        <v>-105.39637222</v>
+      </c>
+      <c r="H87" s="9">
+        <v>28.09985</v>
+      </c>
+      <c r="I87" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="J87" s="8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A88" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="B88" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="C88" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D88" s="8">
+        <v>65.849999999999994</v>
+      </c>
+      <c r="E88" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F88" s="8">
         <v>150</v>
       </c>
-      <c r="G86" s="9">
-        <v>-105.37317283</v>
-      </c>
-      <c r="H86" s="9">
-        <v>28.06971858</v>
-      </c>
-      <c r="I86" s="1" t="s">
+      <c r="G88" s="9">
+        <v>-105.39881911000001</v>
+      </c>
+      <c r="H88" s="9">
+        <v>28.110534850000001</v>
+      </c>
+      <c r="I88" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="J86" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A87" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="B87" s="1" t="s">
+      <c r="J88" s="8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A89" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="B89" s="8" t="s">
         <v>331</v>
       </c>
-      <c r="C87" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="D87" s="1">
-        <v>58.76</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F87" s="1">
+      <c r="C89" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="D89" s="8">
+        <v>66.900000000000006</v>
+      </c>
+      <c r="E89" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="F89" s="8">
+        <v>300</v>
+      </c>
+      <c r="G89" s="9">
+        <v>-105.399006</v>
+      </c>
+      <c r="H89" s="9">
+        <v>28.11894444</v>
+      </c>
+      <c r="I89" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="J89" s="8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A90" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="B90" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="C90" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="D90" s="8">
+        <v>67.319999999999993</v>
+      </c>
+      <c r="E90" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F90" s="8">
         <v>500</v>
       </c>
-      <c r="G87" s="9">
-        <v>-105.3748234</v>
-      </c>
-      <c r="H87" s="9">
-        <v>28.070505730000001</v>
-      </c>
-      <c r="I87" s="1" t="s">
+      <c r="G90" s="9">
+        <v>-105.39667469</v>
+      </c>
+      <c r="H90" s="9">
+        <v>28.122881469999999</v>
+      </c>
+      <c r="I90" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="J87" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A88" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="B88" s="1" t="s">
+      <c r="J90" s="8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A91" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="B91" s="8" t="s">
         <v>331</v>
       </c>
-      <c r="C88" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="D88" s="1">
-        <v>60.3</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F88" s="1">
-        <v>100</v>
-      </c>
-      <c r="G88" s="9">
-        <v>-105.38525518</v>
-      </c>
-      <c r="H88" s="9">
-        <v>28.073751619999999</v>
-      </c>
-      <c r="I88" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="J88" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A89" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="B89" s="1" t="s">
+      <c r="C91" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="D91" s="15">
+        <v>67.61</v>
+      </c>
+      <c r="E91" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="F91" s="17">
+        <v>400</v>
+      </c>
+      <c r="G91" s="9">
+        <v>-105.39545235</v>
+      </c>
+      <c r="H91" s="9">
+        <v>28.125361179999999</v>
+      </c>
+      <c r="I91" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="J91" s="8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A92" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="B92" s="8" t="s">
         <v>331</v>
       </c>
-      <c r="C89" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="D89" s="1">
-        <v>61.03</v>
-      </c>
-      <c r="E89" s="1" t="s">
+      <c r="C92" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="D92" s="15">
+        <v>67.849999999999994</v>
+      </c>
+      <c r="E92" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F89" s="1">
-        <v>200</v>
-      </c>
-      <c r="G89" s="9">
-        <v>-105.3870215</v>
-      </c>
-      <c r="H89" s="9">
-        <v>28.080127730000001</v>
-      </c>
-      <c r="I89" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="J89" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A90" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D90" s="1">
-        <v>62.16</v>
-      </c>
-      <c r="E90" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F90" s="1">
-        <v>600</v>
-      </c>
-      <c r="G90" s="9">
-        <v>-105.39453444999999</v>
-      </c>
-      <c r="H90" s="9">
-        <v>28.082670799999999</v>
-      </c>
-      <c r="I90" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="J90" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A91" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="D91" s="1">
-        <v>62.63</v>
-      </c>
-      <c r="E91" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F91" s="1">
-        <v>100</v>
-      </c>
-      <c r="G91" s="9">
-        <v>-105.39425558000001</v>
-      </c>
-      <c r="H91" s="9">
-        <v>28.087006259999999</v>
-      </c>
-      <c r="I91" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="J91" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A92" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="C92" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="D92" s="1">
-        <v>62.8</v>
-      </c>
-      <c r="E92" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F92" s="1">
-        <v>500</v>
+      <c r="F92" s="17">
+        <v>400</v>
       </c>
       <c r="G92" s="9">
-        <v>-105.39407772</v>
-      </c>
-      <c r="H92" s="9">
-        <v>28.08851215</v>
-      </c>
-      <c r="I92" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="J92" s="1">
-        <v>7</v>
+        <v>-105.39539644</v>
+      </c>
+      <c r="H92" s="10">
+        <v>28.12746143</v>
+      </c>
+      <c r="I92" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="J92" s="8">
+        <v>9</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="B93" s="8" t="s">
         <v>331</v>
       </c>
-      <c r="C93" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D93" s="8">
-        <v>63.71</v>
-      </c>
-      <c r="E93" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="F93" s="8">
-        <v>500</v>
-      </c>
-      <c r="G93" s="9" t="s">
-        <v>370</v>
-      </c>
-      <c r="H93" s="9" t="s">
-        <v>371</v>
+      <c r="C93" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="D93" s="15">
+        <v>68.19</v>
+      </c>
+      <c r="E93" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="F93" s="17">
+        <v>400</v>
+      </c>
+      <c r="G93" s="9">
+        <v>-105.39714424</v>
+      </c>
+      <c r="H93" s="9">
+        <v>28.130186720000001</v>
       </c>
       <c r="I93" s="8" t="s">
-        <v>136</v>
+        <v>328</v>
       </c>
       <c r="J93" s="8">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A94" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="B94" s="1" t="s">
+      <c r="A94" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="B94" s="8" t="s">
         <v>331</v>
       </c>
-      <c r="C94" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="D94" s="1">
-        <v>64.25</v>
-      </c>
-      <c r="E94" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F94" s="1">
-        <v>250</v>
+      <c r="C94" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="D94" s="15">
+        <v>68.58</v>
+      </c>
+      <c r="E94" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F94" s="17">
+        <v>400</v>
       </c>
       <c r="G94" s="9">
-        <v>-105.39665105</v>
+        <v>-105.39927341000001</v>
       </c>
       <c r="H94" s="9">
-        <v>28.098379659999999</v>
-      </c>
-      <c r="I94" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="J94" s="1">
-        <v>7</v>
+        <v>28.133146870000001</v>
+      </c>
+      <c r="I94" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="J94" s="8">
+        <v>9</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A95" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="B95" s="1" t="s">
+      <c r="A95" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="B95" s="8" t="s">
         <v>331</v>
       </c>
-      <c r="C95" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="D95" s="1">
-        <v>64.34</v>
-      </c>
-      <c r="E95" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F95" s="1">
-        <v>500</v>
-      </c>
-      <c r="G95" s="9">
-        <v>-105.396456</v>
-      </c>
-      <c r="H95" s="9">
-        <v>28.098824409999999</v>
-      </c>
-      <c r="I95" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="J95" s="1">
-        <v>8</v>
+      <c r="C95" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="D95" s="15">
+        <v>0.54</v>
+      </c>
+      <c r="E95" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="F95" s="17">
+        <v>400</v>
+      </c>
+      <c r="G95" s="18">
+        <v>-105.20780833000001</v>
+      </c>
+      <c r="H95" s="18">
+        <v>27.67170278</v>
+      </c>
+      <c r="I95" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="J95" s="8">
+        <v>9</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" s="8" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="B96" s="8" t="s">
         <v>331</v>
       </c>
-      <c r="C96" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="D96" s="8">
-        <v>64.540000000000006</v>
+      <c r="C96" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="D96" s="15">
+        <v>1.1200000000000001</v>
       </c>
       <c r="E96" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="F96" s="8">
-        <v>500</v>
-      </c>
-      <c r="G96" s="9" t="s">
-        <v>372</v>
-      </c>
-      <c r="H96" s="9" t="s">
-        <v>373</v>
+        <v>15</v>
+      </c>
+      <c r="F96" s="17">
+        <v>400</v>
+      </c>
+      <c r="G96" s="11">
+        <v>-105.20411944</v>
+      </c>
+      <c r="H96" s="18">
+        <v>27.675627779999999</v>
       </c>
       <c r="I96" s="8" t="s">
-        <v>136</v>
+        <v>328</v>
       </c>
       <c r="J96" s="8">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A97" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="B97" s="1" t="s">
+      <c r="A97" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="B97" s="8" t="s">
         <v>331</v>
       </c>
-      <c r="C97" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="D97" s="1">
-        <v>65.849999999999994</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F97" s="1">
-        <v>150</v>
-      </c>
-      <c r="G97" s="9">
-        <v>-105.39881911000001</v>
-      </c>
-      <c r="H97" s="9">
-        <v>28.110534850000001</v>
-      </c>
-      <c r="I97" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="J97" s="1">
-        <v>8</v>
+      <c r="C97" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="D97" s="15">
+        <v>1.36</v>
+      </c>
+      <c r="E97" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="F97" s="17">
+        <v>400</v>
+      </c>
+      <c r="G97" s="18">
+        <v>-105.20336666999999</v>
+      </c>
+      <c r="H97" s="18">
+        <v>27.67777778</v>
+      </c>
+      <c r="I97" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="J97" s="8">
+        <v>10</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" s="8" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="B98" s="8" t="s">
-        <v>331</v>
-      </c>
-      <c r="C98" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="D98" s="8">
-        <v>66.900000000000006</v>
-      </c>
-      <c r="E98" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="C98" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="D98" s="15">
+        <v>1.36</v>
+      </c>
+      <c r="E98" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="F98" s="17">
+        <v>400</v>
+      </c>
+      <c r="G98" s="18">
+        <v>-105.20336666999999</v>
+      </c>
+      <c r="H98" s="18">
+        <v>27.67777778</v>
+      </c>
+      <c r="I98" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="J98" s="8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A99" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="B99" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="C99" s="16" t="s">
+        <v>175</v>
+      </c>
+      <c r="D99" s="15">
+        <v>1.37</v>
+      </c>
+      <c r="E99" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F99" s="17">
+        <v>400</v>
+      </c>
+      <c r="G99" s="18">
+        <v>-105.20357778</v>
+      </c>
+      <c r="H99" s="18">
+        <v>27.67781111</v>
+      </c>
+      <c r="I99" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="J99" s="19" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A100" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="B100" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="C100" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="D100" s="15">
+        <v>0.53</v>
+      </c>
+      <c r="E100" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="F100" s="17">
+        <v>400</v>
+      </c>
+      <c r="G100" s="18">
+        <v>-105.20787222</v>
+      </c>
+      <c r="H100" s="18">
+        <v>27.67165833</v>
+      </c>
+      <c r="I100" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="J100" s="8">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A101" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="B101" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="C101" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="D101" s="15">
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="E101" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F101" s="17">
+        <v>400</v>
+      </c>
+      <c r="G101" s="18">
+        <v>-105.20130833</v>
+      </c>
+      <c r="H101" s="18">
+        <v>27.685775</v>
+      </c>
+      <c r="I101" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="J101" s="8">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A102" s="8" t="s">
+        <v>344</v>
+      </c>
+      <c r="B102" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="C102" s="20" t="s">
+        <v>345</v>
+      </c>
+      <c r="D102" s="21">
+        <v>2.286</v>
+      </c>
+      <c r="E102" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F102" s="22">
+        <v>400</v>
+      </c>
+      <c r="G102" s="18">
+        <v>-105.201292</v>
+      </c>
+      <c r="H102" s="18">
+        <v>27.685827</v>
+      </c>
+      <c r="I102" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="J102" s="8" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A103" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="B103" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="C103" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="D103" s="15">
+        <v>68.599999999999994</v>
+      </c>
+      <c r="E103" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="F98" s="8">
-        <v>300</v>
-      </c>
-      <c r="G98" s="9" t="s">
-        <v>374</v>
-      </c>
-      <c r="H98" s="9" t="s">
-        <v>375</v>
-      </c>
-      <c r="I98" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="J98" s="8">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A99" s="10" t="s">
-        <v>259</v>
-      </c>
-      <c r="B99" s="10" t="s">
-        <v>331</v>
-      </c>
-      <c r="C99" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="D99" s="10">
-        <v>67.319999999999993</v>
-      </c>
-      <c r="E99" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="F99" s="10">
-        <v>500</v>
-      </c>
-      <c r="G99" s="9">
-        <v>-105.39667469</v>
-      </c>
-      <c r="H99" s="9">
-        <v>28.122881469999999</v>
-      </c>
-      <c r="I99" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="J99" s="10">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A100" s="10" t="s">
-        <v>260</v>
-      </c>
-      <c r="B100" s="10" t="s">
-        <v>331</v>
-      </c>
-      <c r="C100" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="D100" s="12">
-        <v>67.61</v>
-      </c>
-      <c r="E100" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="F100" s="14">
+      <c r="F103" s="17">
         <v>400</v>
       </c>
-      <c r="G100" s="9">
-        <v>-105.39545235</v>
-      </c>
-      <c r="H100" s="9">
-        <v>28.125361179999999</v>
-      </c>
-      <c r="I100" s="10" t="s">
+      <c r="G103" s="18">
+        <v>-105.39896111</v>
+      </c>
+      <c r="H103" s="18">
+        <v>28.132930559999998</v>
+      </c>
+      <c r="I103" s="8" t="s">
         <v>328</v>
       </c>
-      <c r="J100" s="10">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A101" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="C101" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="D101" s="5">
-        <v>67.849999999999994</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F101" s="14">
-        <v>400</v>
-      </c>
-      <c r="G101" s="9">
-        <v>-105.39539644</v>
-      </c>
-      <c r="H101" s="9">
-        <v>28.12746143</v>
-      </c>
-      <c r="I101" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="J101" s="1">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A102" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="C102" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="D102" s="5">
-        <v>68.19</v>
-      </c>
-      <c r="E102" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="F102" s="14">
-        <v>400</v>
-      </c>
-      <c r="G102" s="9">
-        <v>-105.39714424</v>
-      </c>
-      <c r="H102" s="9">
-        <v>28.130186720000001</v>
-      </c>
-      <c r="I102" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="J102" s="1">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A103" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="C103" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="D103" s="5">
-        <v>68.58</v>
-      </c>
-      <c r="E103" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F103" s="14">
-        <v>400</v>
-      </c>
-      <c r="G103" s="9">
-        <v>-105.39927341000001</v>
-      </c>
-      <c r="H103" s="9">
-        <v>28.133146870000001</v>
-      </c>
-      <c r="I103" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="J103" s="1">
-        <v>9</v>
+      <c r="J103" s="8" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" s="8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B104" s="8" t="s">
-        <v>377</v>
-      </c>
-      <c r="C104" s="15" t="s">
-        <v>178</v>
-      </c>
-      <c r="D104" s="16">
-        <v>68.599999999999994</v>
-      </c>
-      <c r="E104" s="17" t="s">
+        <v>343</v>
+      </c>
+      <c r="C104" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="D104" s="15">
+        <v>69.959999999999994</v>
+      </c>
+      <c r="E104" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="F104" s="14">
+      <c r="F104" s="17">
         <v>400</v>
       </c>
-      <c r="G104" s="9" t="s">
-        <v>380</v>
-      </c>
-      <c r="H104" s="9" t="s">
-        <v>381</v>
+      <c r="G104" s="18">
+        <v>-105.41231944</v>
+      </c>
+      <c r="H104" s="18">
+        <v>28.131575000000002</v>
       </c>
       <c r="I104" s="8" t="s">
         <v>328</v>
@@ -5613,92 +5501,92 @@
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B105" s="8" t="s">
-        <v>377</v>
-      </c>
-      <c r="C105" s="15" t="s">
-        <v>179</v>
-      </c>
-      <c r="D105" s="16">
-        <v>69.959999999999994</v>
-      </c>
-      <c r="E105" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="F105" s="14">
+        <v>343</v>
+      </c>
+      <c r="C105" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="D105" s="15">
+        <v>70.680000000000007</v>
+      </c>
+      <c r="E105" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F105" s="17">
         <v>400</v>
       </c>
-      <c r="G105" s="9" t="s">
-        <v>382</v>
-      </c>
-      <c r="H105" s="9" t="s">
-        <v>383</v>
+      <c r="G105" s="9">
+        <v>-105.42034577</v>
+      </c>
+      <c r="H105" s="9">
+        <v>28.13127411</v>
       </c>
       <c r="I105" s="8" t="s">
         <v>328</v>
       </c>
-      <c r="J105" s="8" t="s">
-        <v>185</v>
+      <c r="J105" s="8">
+        <v>19</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A106" s="1" t="s">
-        <v>272</v>
+      <c r="A106" s="8" t="s">
+        <v>273</v>
       </c>
       <c r="B106" s="8" t="s">
-        <v>377</v>
-      </c>
-      <c r="C106" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="D106" s="5">
-        <v>70.680000000000007</v>
-      </c>
-      <c r="E106" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F106" s="14">
+        <v>343</v>
+      </c>
+      <c r="C106" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="D106" s="15">
+        <v>70.77</v>
+      </c>
+      <c r="E106" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="F106" s="17">
         <v>400</v>
       </c>
-      <c r="G106" s="9">
-        <v>-105.42034577</v>
-      </c>
-      <c r="H106" s="9">
-        <v>28.13127411</v>
-      </c>
-      <c r="I106" s="1" t="s">
+      <c r="G106" s="18">
+        <v>-105.42051111000001</v>
+      </c>
+      <c r="H106" s="18">
+        <v>28.131194440000002</v>
+      </c>
+      <c r="I106" s="8" t="s">
         <v>328</v>
       </c>
-      <c r="J106" s="1">
+      <c r="J106" s="8">
         <v>19</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B107" s="8" t="s">
-        <v>377</v>
-      </c>
-      <c r="C107" s="15" t="s">
-        <v>181</v>
-      </c>
-      <c r="D107" s="16">
-        <v>70.77</v>
-      </c>
-      <c r="E107" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="F107" s="14">
+        <v>343</v>
+      </c>
+      <c r="C107" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="D107" s="15">
+        <v>70.84</v>
+      </c>
+      <c r="E107" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="F107" s="17">
         <v>400</v>
       </c>
-      <c r="G107" s="9" t="s">
-        <v>384</v>
-      </c>
-      <c r="H107" s="9" t="s">
-        <v>385</v>
+      <c r="G107" s="9">
+        <v>-105.42176239</v>
+      </c>
+      <c r="H107" s="9">
+        <v>28.130590479999999</v>
       </c>
       <c r="I107" s="8" t="s">
         <v>328</v>
@@ -5708,86 +5596,86 @@
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A108" s="1" t="s">
-        <v>274</v>
+      <c r="A108" s="8" t="s">
+        <v>275</v>
       </c>
       <c r="B108" s="8" t="s">
-        <v>377</v>
-      </c>
-      <c r="C108" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="D108" s="5">
-        <v>70.84</v>
-      </c>
-      <c r="E108" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="F108" s="14">
+        <v>343</v>
+      </c>
+      <c r="C108" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="D108" s="15">
+        <v>71.91</v>
+      </c>
+      <c r="E108" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="F108" s="17">
         <v>400</v>
       </c>
       <c r="G108" s="9">
-        <v>-105.42176239</v>
+        <v>-105.43241922999999</v>
       </c>
       <c r="H108" s="9">
-        <v>28.130590479999999</v>
-      </c>
-      <c r="I108" s="1" t="s">
+        <v>28.1303728</v>
+      </c>
+      <c r="I108" s="8" t="s">
         <v>328</v>
       </c>
-      <c r="J108" s="1">
+      <c r="J108" s="8">
         <v>19</v>
       </c>
     </row>
-    <row r="109" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="1" t="s">
-        <v>275</v>
+    <row r="109" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A109" s="8" t="s">
+        <v>276</v>
       </c>
       <c r="B109" s="8" t="s">
-        <v>377</v>
-      </c>
-      <c r="C109" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="D109" s="5">
-        <v>71.91</v>
-      </c>
-      <c r="E109" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="F109" s="14">
+        <v>338</v>
+      </c>
+      <c r="C109" s="14" t="s">
+        <v>346</v>
+      </c>
+      <c r="D109" s="23">
+        <v>0.186</v>
+      </c>
+      <c r="E109" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F109" s="24">
         <v>400</v>
       </c>
-      <c r="G109" s="9">
-        <v>-105.43241922999999</v>
-      </c>
-      <c r="H109" s="9">
-        <v>28.1303728</v>
-      </c>
-      <c r="I109" s="1" t="s">
+      <c r="G109" s="18">
+        <v>-105.20981944</v>
+      </c>
+      <c r="H109" s="18">
+        <v>27.66943333</v>
+      </c>
+      <c r="I109" s="8" t="s">
         <v>328</v>
       </c>
       <c r="J109" s="8">
-        <v>19</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A110" s="1" t="s">
+      <c r="A110" s="8" t="s">
         <v>277</v>
       </c>
-      <c r="B110" s="1" t="s">
+      <c r="B110" s="8" t="s">
         <v>330</v>
       </c>
-      <c r="C110" s="1" t="s">
+      <c r="C110" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="D110" s="1">
+      <c r="D110" s="8">
         <v>72.92</v>
       </c>
-      <c r="E110" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F110" s="20">
+      <c r="E110" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F110" s="24">
         <v>400</v>
       </c>
       <c r="G110" s="9">
@@ -5796,30 +5684,30 @@
       <c r="H110" s="9">
         <v>28.12976184</v>
       </c>
-      <c r="I110" s="1" t="s">
+      <c r="I110" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="J110" s="1">
+      <c r="J110" s="8">
         <v>20</v>
       </c>
     </row>
     <row r="111" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A111" s="1" t="s">
+      <c r="A111" s="8" t="s">
         <v>278</v>
       </c>
-      <c r="B111" s="1" t="s">
+      <c r="B111" s="8" t="s">
         <v>330</v>
       </c>
-      <c r="C111" s="1" t="s">
+      <c r="C111" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="D111" s="1">
+      <c r="D111" s="8">
         <v>73.069999999999993</v>
       </c>
-      <c r="E111" s="1" t="s">
+      <c r="E111" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F111" s="20">
+      <c r="F111" s="24">
         <v>400</v>
       </c>
       <c r="G111" s="9">
@@ -5828,62 +5716,62 @@
       <c r="H111" s="9">
         <v>28.1315326</v>
       </c>
-      <c r="I111" s="1" t="s">
+      <c r="I111" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="J111" s="1">
+      <c r="J111" s="8">
         <v>20</v>
       </c>
     </row>
     <row r="112" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A112" s="1" t="s">
+      <c r="A112" s="8" t="s">
         <v>279</v>
       </c>
-      <c r="B112" s="1" t="s">
+      <c r="B112" s="8" t="s">
         <v>330</v>
       </c>
-      <c r="C112" s="1" t="s">
+      <c r="C112" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="D112" s="1">
+      <c r="D112" s="8">
         <v>73.27</v>
       </c>
-      <c r="E112" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F112" s="20">
+      <c r="E112" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F112" s="24">
         <v>400</v>
       </c>
-      <c r="G112" s="9">
+      <c r="G112" s="12">
         <v>-105.44465396</v>
       </c>
-      <c r="H112" s="9">
+      <c r="H112" s="12">
         <v>28.131304950000001</v>
       </c>
-      <c r="I112" s="1" t="s">
+      <c r="I112" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="J112" s="1">
+      <c r="J112" s="8">
         <v>20</v>
       </c>
     </row>
     <row r="113" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A113" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="B113" s="1" t="s">
+      <c r="A113" s="8" t="s">
+        <v>347</v>
+      </c>
+      <c r="B113" s="8" t="s">
         <v>330</v>
       </c>
-      <c r="C113" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="D113" s="1">
+      <c r="C113" s="13" t="s">
+        <v>348</v>
+      </c>
+      <c r="D113" s="8">
         <v>73.296000000000006</v>
       </c>
-      <c r="E113" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F113" s="20">
+      <c r="E113" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F113" s="24">
         <v>400</v>
       </c>
       <c r="G113" s="9">
@@ -5892,30 +5780,30 @@
       <c r="H113" s="9">
         <v>28.13110756</v>
       </c>
-      <c r="I113" s="1" t="s">
+      <c r="I113" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="J113" s="1">
+      <c r="J113" s="8">
         <v>20</v>
       </c>
     </row>
     <row r="114" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A114" s="1" t="s">
+      <c r="A114" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="B114" s="1" t="s">
+      <c r="B114" s="8" t="s">
         <v>330</v>
       </c>
-      <c r="C114" s="1" t="s">
+      <c r="C114" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="D114" s="1">
+      <c r="D114" s="8">
         <v>74.099999999999994</v>
       </c>
-      <c r="E114" s="1" t="s">
+      <c r="E114" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F114" s="20">
+      <c r="F114" s="24">
         <v>400</v>
       </c>
       <c r="G114" s="9">
@@ -5924,30 +5812,30 @@
       <c r="H114" s="9">
         <v>28.130554180000001</v>
       </c>
-      <c r="I114" s="1" t="s">
+      <c r="I114" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="J114" s="1">
+      <c r="J114" s="8">
         <v>20</v>
       </c>
     </row>
     <row r="115" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A115" s="1" t="s">
+      <c r="A115" s="8" t="s">
         <v>281</v>
       </c>
-      <c r="B115" s="1" t="s">
+      <c r="B115" s="8" t="s">
         <v>330</v>
       </c>
-      <c r="C115" s="1" t="s">
+      <c r="C115" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="D115" s="1">
+      <c r="D115" s="8">
         <v>74.650000000000006</v>
       </c>
-      <c r="E115" s="1" t="s">
+      <c r="E115" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F115" s="20">
+      <c r="F115" s="24">
         <v>400</v>
       </c>
       <c r="G115" s="9">
@@ -5956,62 +5844,62 @@
       <c r="H115" s="9">
         <v>28.128932290000002</v>
       </c>
-      <c r="I115" s="1" t="s">
+      <c r="I115" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="J115" s="1">
+      <c r="J115" s="8">
         <v>20</v>
       </c>
     </row>
     <row r="116" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A116" s="1" t="s">
+      <c r="A116" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="B116" s="1" t="s">
+      <c r="B116" s="8" t="s">
         <v>330</v>
       </c>
-      <c r="C116" s="1" t="s">
+      <c r="C116" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="D116" s="1">
+      <c r="D116" s="8">
         <v>75.58</v>
       </c>
-      <c r="E116" s="1" t="s">
+      <c r="E116" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F116" s="20">
+      <c r="F116" s="24">
         <v>400</v>
       </c>
       <c r="G116" s="9">
         <v>-105.46639611000001</v>
       </c>
-      <c r="H116" s="9">
+      <c r="H116" s="10">
         <v>28.12456431</v>
       </c>
-      <c r="I116" s="1" t="s">
+      <c r="I116" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="J116" s="1">
+      <c r="J116" s="8">
         <v>21</v>
       </c>
     </row>
     <row r="117" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A117" s="1" t="s">
+      <c r="A117" s="8" t="s">
         <v>283</v>
       </c>
-      <c r="B117" s="1" t="s">
+      <c r="B117" s="8" t="s">
         <v>330</v>
       </c>
-      <c r="C117" s="1" t="s">
+      <c r="C117" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="D117" s="1">
+      <c r="D117" s="8">
         <v>75.81</v>
       </c>
-      <c r="E117" s="1" t="s">
+      <c r="E117" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F117" s="20">
+      <c r="F117" s="24">
         <v>400</v>
       </c>
       <c r="G117" s="9">
@@ -6020,10 +5908,10 @@
       <c r="H117" s="9">
         <v>28.123767610000002</v>
       </c>
-      <c r="I117" s="1" t="s">
+      <c r="I117" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="J117" s="1">
+      <c r="J117" s="8">
         <v>21</v>
       </c>
     </row>
@@ -6043,14 +5931,14 @@
       <c r="E118" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="F118" s="20">
+      <c r="F118" s="24">
         <v>400</v>
       </c>
-      <c r="G118" s="9" t="s">
-        <v>389</v>
-      </c>
-      <c r="H118" s="9" t="s">
-        <v>390</v>
+      <c r="G118" s="9">
+        <v>-105.48093333</v>
+      </c>
+      <c r="H118" s="9">
+        <v>28.099147219999999</v>
       </c>
       <c r="I118" s="8" t="s">
         <v>329</v>
@@ -6060,22 +5948,22 @@
       </c>
     </row>
     <row r="119" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A119" s="1" t="s">
+      <c r="A119" s="8" t="s">
         <v>285</v>
       </c>
-      <c r="B119" s="1" t="s">
+      <c r="B119" s="8" t="s">
         <v>330</v>
       </c>
-      <c r="C119" s="1" t="s">
+      <c r="C119" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="D119" s="1">
+      <c r="D119" s="8">
         <v>79.010000000000005</v>
       </c>
-      <c r="E119" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F119" s="20">
+      <c r="E119" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F119" s="24">
         <v>400</v>
       </c>
       <c r="G119" s="9">
@@ -6084,10 +5972,10 @@
       <c r="H119" s="9">
         <v>28.099132019999999</v>
       </c>
-      <c r="I119" s="1" t="s">
+      <c r="I119" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="J119" s="1">
+      <c r="J119" s="8">
         <v>22</v>
       </c>
     </row>
@@ -6102,19 +5990,19 @@
         <v>127</v>
       </c>
       <c r="D120" s="8">
-        <v>79.010000000000005</v>
+        <v>79.013999999999996</v>
       </c>
       <c r="E120" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="F120" s="20">
+      <c r="F120" s="24">
         <v>400</v>
       </c>
-      <c r="G120" s="9" t="s">
-        <v>391</v>
-      </c>
-      <c r="H120" s="9" t="s">
-        <v>392</v>
+      <c r="G120" s="9">
+        <v>-105.480925</v>
+      </c>
+      <c r="H120" s="9">
+        <v>28.099119439999999</v>
       </c>
       <c r="I120" s="8" t="s">
         <v>329</v>
@@ -6125,629 +6013,629 @@
     </row>
     <row r="121" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A121" s="8" t="s">
-        <v>393</v>
-      </c>
-      <c r="B121" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="B121" s="8" t="s">
         <v>330</v>
       </c>
-      <c r="C121" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="D121" s="1">
+      <c r="C121" s="13" t="s">
+        <v>350</v>
+      </c>
+      <c r="D121" s="8">
         <v>79.025000000000006</v>
       </c>
-      <c r="E121" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F121" s="20">
+      <c r="E121" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F121" s="24">
         <v>400</v>
       </c>
-      <c r="G121" s="9" t="s">
-        <v>395</v>
-      </c>
-      <c r="H121" s="9" t="s">
-        <v>396</v>
-      </c>
-      <c r="I121" s="1" t="s">
+      <c r="G121" s="9">
+        <v>-105.48093611</v>
+      </c>
+      <c r="H121" s="9">
+        <v>28.099030559999999</v>
+      </c>
+      <c r="I121" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="J121" s="1">
+      <c r="J121" s="8">
         <v>22</v>
       </c>
     </row>
-    <row r="122" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="B122" s="1" t="s">
+    <row r="122" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A122" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="B122" s="8" t="s">
         <v>330</v>
       </c>
-      <c r="C122" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="D122" s="1">
-        <v>79.73</v>
-      </c>
-      <c r="E122" s="1" t="s">
+      <c r="C122" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="D122" s="8">
+        <v>79.87</v>
+      </c>
+      <c r="E122" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F122" s="24">
+        <v>400</v>
+      </c>
+      <c r="G122" s="9">
+        <v>-105.48108581</v>
+      </c>
+      <c r="H122" s="9">
+        <v>28.091610769999999</v>
+      </c>
+      <c r="I122" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="J122" s="8">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="B123" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="C123" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="D123" s="8">
+        <v>80.400000000000006</v>
+      </c>
+      <c r="E123" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F123" s="8">
+        <v>310</v>
+      </c>
+      <c r="G123" s="9">
+        <v>-105.48191688</v>
+      </c>
+      <c r="H123" s="9">
+        <v>28.08701967</v>
+      </c>
+      <c r="I123" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="J123" s="8">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A124" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="B124" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="C124" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="D124" s="8">
+        <v>80.95</v>
+      </c>
+      <c r="E124" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F122" s="1">
+      <c r="F124" s="8">
+        <v>60</v>
+      </c>
+      <c r="G124" s="9">
+        <v>-105.48321943000001</v>
+      </c>
+      <c r="H124" s="9">
+        <v>28.082236200000001</v>
+      </c>
+      <c r="I124" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="J124" s="8">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A125" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="B125" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="C125" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="D125" s="8">
+        <v>82.93</v>
+      </c>
+      <c r="E125" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F125" s="8">
+        <v>60</v>
+      </c>
+      <c r="G125" s="9">
+        <v>-105.49965215</v>
+      </c>
+      <c r="H125" s="9">
+        <v>28.07462937</v>
+      </c>
+      <c r="I125" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="J125" s="8">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A126" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="B126" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="C126" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="D126" s="8">
+        <v>84.05</v>
+      </c>
+      <c r="E126" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F126" s="8">
+        <v>60</v>
+      </c>
+      <c r="G126" s="9">
+        <v>-105.50879454</v>
+      </c>
+      <c r="H126" s="9">
+        <v>28.0790717</v>
+      </c>
+      <c r="I126" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="J126" s="8">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A127" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="B127" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="C127" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="D127" s="8">
+        <v>84.55</v>
+      </c>
+      <c r="E127" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F127" s="8">
+        <v>60</v>
+      </c>
+      <c r="G127" s="9">
+        <v>-105.51198017</v>
+      </c>
+      <c r="H127" s="9">
+        <v>28.08252135</v>
+      </c>
+      <c r="I127" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="J127" s="8">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A128" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="B128" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="C128" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="D128" s="8">
+        <v>85.04</v>
+      </c>
+      <c r="E128" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F128" s="8">
+        <v>40</v>
+      </c>
+      <c r="G128" s="9">
+        <v>-105.51496127999999</v>
+      </c>
+      <c r="H128" s="9">
+        <v>28.086334359999999</v>
+      </c>
+      <c r="I128" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="J128" s="8">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A129" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="B129" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="C129" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="D129" s="8">
+        <v>85.51</v>
+      </c>
+      <c r="E129" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F129" s="8">
         <v>120</v>
       </c>
-      <c r="G122" s="9">
-        <v>-105.54784365</v>
-      </c>
-      <c r="H122" s="9">
-        <v>28.109398680000002</v>
-      </c>
-      <c r="I122" s="1" t="s">
+      <c r="G129" s="9">
+        <v>-105.51879692</v>
+      </c>
+      <c r="H129" s="9">
+        <v>28.08875523</v>
+      </c>
+      <c r="I129" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="J122" s="1">
+      <c r="J129" s="8">
         <v>23</v>
       </c>
     </row>
-    <row r="123" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A123" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="B123" s="1" t="s">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A130" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="B130" s="8" t="s">
         <v>330</v>
       </c>
-      <c r="C123" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="D123" s="1">
-        <v>79.87</v>
-      </c>
-      <c r="E123" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F123" s="20">
-        <v>400</v>
-      </c>
-      <c r="G123" s="9">
-        <v>-105.48108581</v>
-      </c>
-      <c r="H123" s="9">
-        <v>28.091610769999999</v>
-      </c>
-      <c r="I123" s="1" t="s">
+      <c r="C130" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="D130" s="8">
+        <v>86.06</v>
+      </c>
+      <c r="E130" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F130" s="8">
+        <v>120</v>
+      </c>
+      <c r="G130" s="9">
+        <v>-105.52316951</v>
+      </c>
+      <c r="H130" s="9">
+        <v>28.091678999999999</v>
+      </c>
+      <c r="I130" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="J123" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A124" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="B124" s="1" t="s">
+      <c r="J130" s="8">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A131" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="B131" s="8" t="s">
         <v>330</v>
       </c>
-      <c r="C124" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="D124" s="1">
-        <v>80.400000000000006</v>
-      </c>
-      <c r="E124" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F124" s="1">
-        <v>310</v>
-      </c>
-      <c r="G124" s="9">
-        <v>-105.48191688</v>
-      </c>
-      <c r="H124" s="9">
-        <v>28.08701967</v>
-      </c>
-      <c r="I124" s="1" t="s">
+      <c r="C131" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="D131" s="8">
+        <v>86.24</v>
+      </c>
+      <c r="E131" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F131" s="8">
+        <v>90</v>
+      </c>
+      <c r="G131" s="9">
+        <v>-105.52547778</v>
+      </c>
+      <c r="H131" s="9">
+        <v>28.092974999999999</v>
+      </c>
+      <c r="I131" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="J124" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A125" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="B125" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="C125" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="D125" s="1">
-        <v>80.95</v>
-      </c>
-      <c r="E125" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F125" s="1">
-        <v>60</v>
-      </c>
-      <c r="G125" s="9">
-        <v>-105.48321943000001</v>
-      </c>
-      <c r="H125" s="9">
-        <v>28.082236200000001</v>
-      </c>
-      <c r="I125" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="J125" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A126" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="B126" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="D126" s="1">
-        <v>82.93</v>
-      </c>
-      <c r="E126" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F126" s="1">
-        <v>60</v>
-      </c>
-      <c r="G126" s="9">
-        <v>-105.49965215</v>
-      </c>
-      <c r="H126" s="9">
-        <v>28.07462937</v>
-      </c>
-      <c r="I126" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="J126" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A127" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="B127" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="D127" s="1">
-        <v>84.05</v>
-      </c>
-      <c r="E127" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F127" s="1">
-        <v>60</v>
-      </c>
-      <c r="G127" s="9">
-        <v>-105.50879454</v>
-      </c>
-      <c r="H127" s="9">
-        <v>28.0790717</v>
-      </c>
-      <c r="I127" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="J127" s="1">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A128" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="B128" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="C128" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="D128" s="1">
-        <v>84.55</v>
-      </c>
-      <c r="E128" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F128" s="1">
-        <v>60</v>
-      </c>
-      <c r="G128" s="9">
-        <v>-105.51198017</v>
-      </c>
-      <c r="H128" s="9">
-        <v>28.08252135</v>
-      </c>
-      <c r="I128" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="J128" s="1">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A129" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="B129" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="D129" s="1">
-        <v>85.04</v>
-      </c>
-      <c r="E129" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F129" s="1">
-        <v>40</v>
-      </c>
-      <c r="G129" s="9">
-        <v>-105.51496127999999</v>
-      </c>
-      <c r="H129" s="9">
-        <v>28.086334359999999</v>
-      </c>
-      <c r="I129" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="J129" s="1">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A130" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="B130" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="C130" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="D130" s="1">
-        <v>85.51</v>
-      </c>
-      <c r="E130" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F130" s="1">
-        <v>120</v>
-      </c>
-      <c r="G130" s="9">
-        <v>-105.51879692</v>
-      </c>
-      <c r="H130" s="9">
-        <v>28.08875523</v>
-      </c>
-      <c r="I130" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="J130" s="1">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A131" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="B131" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="C131" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="D131" s="1">
-        <v>86.06</v>
-      </c>
-      <c r="E131" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F131" s="1">
-        <v>120</v>
-      </c>
-      <c r="G131" s="9">
-        <v>-105.52316951</v>
-      </c>
-      <c r="H131" s="9">
-        <v>28.091678999999999</v>
-      </c>
-      <c r="I131" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="J131" s="1">
+      <c r="J131" s="8">
         <v>23</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132" s="8" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B132" s="8" t="s">
         <v>330</v>
       </c>
       <c r="C132" s="8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D132" s="8">
-        <v>86.24</v>
+        <v>86.6</v>
       </c>
       <c r="E132" s="8" t="s">
         <v>48</v>
       </c>
       <c r="F132" s="8">
-        <v>90</v>
-      </c>
-      <c r="G132" s="9" t="s">
-        <v>397</v>
-      </c>
-      <c r="H132" s="9" t="s">
-        <v>398</v>
+        <v>100</v>
+      </c>
+      <c r="G132" s="9">
+        <v>-105.5285734</v>
+      </c>
+      <c r="H132" s="9">
+        <v>28.09478584</v>
       </c>
       <c r="I132" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="J132" s="1">
+      <c r="J132" s="8">
         <v>23</v>
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A133" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="B133" s="1" t="s">
+      <c r="A133" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="B133" s="8" t="s">
         <v>330</v>
       </c>
-      <c r="C133" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="D133" s="1">
-        <v>86.6</v>
-      </c>
-      <c r="E133" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F133" s="1">
+      <c r="C133" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="D133" s="8">
+        <v>86.95</v>
+      </c>
+      <c r="E133" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F133" s="8">
         <v>100</v>
       </c>
       <c r="G133" s="9">
-        <v>-105.53100969</v>
+        <v>-105.531858</v>
       </c>
       <c r="H133" s="9">
-        <v>28.095699880000002</v>
-      </c>
-      <c r="I133" s="1" t="s">
+        <v>28.096021</v>
+      </c>
+      <c r="I133" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="J133" s="1">
+      <c r="J133" s="8">
         <v>23</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A134" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="B134" s="1" t="s">
+      <c r="A134" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="B134" s="8" t="s">
         <v>330</v>
       </c>
-      <c r="C134" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="D134" s="1">
-        <v>86.95</v>
-      </c>
-      <c r="E134" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F134" s="1">
+      <c r="C134" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="D134" s="8">
+        <v>87.47</v>
+      </c>
+      <c r="E134" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F134" s="8">
         <v>100</v>
       </c>
       <c r="G134" s="9">
-        <v>-105.53100969</v>
+        <v>-105.53535755</v>
       </c>
       <c r="H134" s="9">
-        <v>28.095699880000002</v>
-      </c>
-      <c r="I134" s="1" t="s">
+        <v>28.095285730000001</v>
+      </c>
+      <c r="I134" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="J134" s="1">
+      <c r="J134" s="8">
         <v>23</v>
       </c>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A135" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="B135" s="1" t="s">
+      <c r="A135" s="8" t="s">
+        <v>351</v>
+      </c>
+      <c r="B135" s="8" t="s">
         <v>330</v>
       </c>
-      <c r="C135" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="D135" s="1">
-        <v>87.47</v>
-      </c>
-      <c r="E135" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F135" s="1">
-        <v>100</v>
+      <c r="C135" s="13" t="s">
+        <v>352</v>
+      </c>
+      <c r="D135" s="8">
+        <v>87.549000000000007</v>
+      </c>
+      <c r="E135" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F135" s="8">
+        <v>4000</v>
       </c>
       <c r="G135" s="9">
-        <v>-105.53535755</v>
+        <v>-105.53596616</v>
       </c>
       <c r="H135" s="9">
-        <v>28.095285730000001</v>
-      </c>
-      <c r="I135" s="1" t="s">
+        <v>28.094830930000001</v>
+      </c>
+      <c r="I135" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="J135" s="1">
+      <c r="J135" s="8">
         <v>23</v>
       </c>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A136" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="B136" s="1" t="s">
+      <c r="A136" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="B136" s="8" t="s">
         <v>330</v>
       </c>
-      <c r="C136" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="D136" s="1">
-        <v>87.549000000000007</v>
-      </c>
-      <c r="E136" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F136" s="1">
-        <v>4000</v>
+      <c r="C136" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="D136" s="8">
+        <v>88.37</v>
+      </c>
+      <c r="E136" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F136" s="8">
+        <v>180</v>
       </c>
       <c r="G136" s="9">
-        <v>-105.53596616</v>
+        <v>-105.53899798</v>
       </c>
       <c r="H136" s="9">
-        <v>28.094830930000001</v>
-      </c>
-      <c r="I136" s="1" t="s">
+        <v>28.100674290000001</v>
+      </c>
+      <c r="I136" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="J136" s="1">
+      <c r="J136" s="8">
         <v>23</v>
       </c>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A137" s="10" t="s">
-        <v>300</v>
-      </c>
-      <c r="B137" s="10" t="s">
+      <c r="A137" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="B137" s="8" t="s">
         <v>330</v>
       </c>
-      <c r="C137" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="D137" s="10">
-        <v>88.37</v>
-      </c>
-      <c r="E137" s="10" t="s">
+      <c r="C137" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="D137" s="8">
+        <v>88.86</v>
+      </c>
+      <c r="E137" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F137" s="10">
-        <v>180</v>
+      <c r="F137" s="8">
+        <v>120</v>
       </c>
       <c r="G137" s="9">
-        <v>-105.53899798</v>
+        <v>-105.54076077000001</v>
       </c>
       <c r="H137" s="9">
-        <v>28.100674290000001</v>
-      </c>
-      <c r="I137" s="10" t="s">
+        <v>28.10482786</v>
+      </c>
+      <c r="I137" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="J137" s="1">
+      <c r="J137" s="8">
         <v>23</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A138" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="B138" s="1" t="s">
+      <c r="A138" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="B138" s="8" t="s">
         <v>330</v>
       </c>
-      <c r="C138" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="D138" s="1">
-        <v>88.86</v>
-      </c>
-      <c r="E138" s="1" t="s">
+      <c r="C138" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="D138" s="8">
+        <v>89.1</v>
+      </c>
+      <c r="E138" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F138" s="8">
+        <v>60</v>
+      </c>
+      <c r="G138" s="9">
+        <v>-105.54267989</v>
+      </c>
+      <c r="H138" s="9">
+        <v>28.10604743</v>
+      </c>
+      <c r="I138" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="J138" s="8">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A139" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="B139" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="C139" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="D139" s="8">
+        <v>89.733000000000004</v>
+      </c>
+      <c r="E139" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F138" s="1">
+      <c r="F139" s="8">
         <v>120</v>
       </c>
-      <c r="G138" s="9">
-        <v>-105.54076077000001</v>
-      </c>
-      <c r="H138" s="9">
-        <v>28.10482786</v>
-      </c>
-      <c r="I138" s="1" t="s">
+      <c r="G139" s="9">
+        <v>-105.54784365</v>
+      </c>
+      <c r="H139" s="9">
+        <v>28.109398680000002</v>
+      </c>
+      <c r="I139" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="J138" s="1">
+      <c r="J139" s="8">
         <v>23</v>
       </c>
     </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A139" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="B139" s="1" t="s">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A140" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="B140" s="8" t="s">
         <v>330</v>
       </c>
-      <c r="C139" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="D139" s="1">
-        <v>89.1</v>
-      </c>
-      <c r="E139" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F139" s="1">
-        <v>60</v>
-      </c>
-      <c r="G139" s="9">
-        <v>-105.54267989</v>
-      </c>
-      <c r="H139" s="9">
-        <v>28.10604743</v>
-      </c>
-      <c r="I139" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="J139" s="1">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A140" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="B140" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="C140" s="1" t="s">
+      <c r="C140" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="D140" s="1">
-        <v>90.06</v>
-      </c>
-      <c r="E140" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F140" s="1">
+      <c r="D140" s="8">
+        <v>90.066000000000003</v>
+      </c>
+      <c r="E140" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F140" s="8">
         <v>500</v>
       </c>
       <c r="G140" s="9">
@@ -6756,30 +6644,30 @@
       <c r="H140" s="9">
         <v>28.111644949999999</v>
       </c>
-      <c r="I140" s="1" t="s">
+      <c r="I140" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="J140" s="1">
+      <c r="J140" s="8">
         <v>23</v>
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A141" s="1" t="s">
+      <c r="A141" s="8" t="s">
         <v>305</v>
       </c>
-      <c r="B141" s="1" t="s">
+      <c r="B141" s="8" t="s">
         <v>330</v>
       </c>
-      <c r="C141" s="1" t="s">
+      <c r="C141" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="D141" s="1">
+      <c r="D141" s="8">
         <v>90.13</v>
       </c>
-      <c r="E141" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F141" s="1">
+      <c r="E141" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F141" s="8">
         <v>400</v>
       </c>
       <c r="G141" s="9">
@@ -6788,30 +6676,30 @@
       <c r="H141" s="9">
         <v>28.11212372</v>
       </c>
-      <c r="I141" s="1" t="s">
+      <c r="I141" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="J141" s="1">
+      <c r="J141" s="8">
         <v>23</v>
       </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A142" s="1" t="s">
+      <c r="A142" s="8" t="s">
         <v>306</v>
       </c>
-      <c r="B142" s="1" t="s">
+      <c r="B142" s="8" t="s">
         <v>330</v>
       </c>
-      <c r="C142" s="1" t="s">
+      <c r="C142" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="D142" s="1">
-        <v>90.72</v>
-      </c>
-      <c r="E142" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F142" s="1">
+      <c r="D142" s="8">
+        <v>90.728999999999999</v>
+      </c>
+      <c r="E142" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F142" s="8">
         <v>120</v>
       </c>
       <c r="G142" s="9">
@@ -6820,30 +6708,30 @@
       <c r="H142" s="9">
         <v>28.113247229999999</v>
       </c>
-      <c r="I142" s="1" t="s">
+      <c r="I142" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="J142" s="1">
+      <c r="J142" s="8">
         <v>24</v>
       </c>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A143" s="1" t="s">
+      <c r="A143" s="8" t="s">
         <v>307</v>
       </c>
-      <c r="B143" s="1" t="s">
+      <c r="B143" s="8" t="s">
         <v>330</v>
       </c>
-      <c r="C143" s="1" t="s">
+      <c r="C143" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="D143" s="1">
+      <c r="D143" s="8">
         <v>91.75</v>
       </c>
-      <c r="E143" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F143" s="1">
+      <c r="E143" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F143" s="8">
         <v>100</v>
       </c>
       <c r="G143" s="9">
@@ -6852,30 +6740,30 @@
       <c r="H143" s="9">
         <v>28.11815408</v>
       </c>
-      <c r="I143" s="1" t="s">
+      <c r="I143" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="J143" s="1">
+      <c r="J143" s="8">
         <v>24</v>
       </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A144" s="1" t="s">
+      <c r="A144" s="8" t="s">
         <v>308</v>
       </c>
-      <c r="B144" s="1" t="s">
+      <c r="B144" s="8" t="s">
         <v>330</v>
       </c>
-      <c r="C144" s="1" t="s">
+      <c r="C144" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="D144" s="1">
+      <c r="D144" s="8">
         <v>92.07</v>
       </c>
-      <c r="E144" s="1" t="s">
+      <c r="E144" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F144" s="1">
+      <c r="F144" s="8">
         <v>120</v>
       </c>
       <c r="G144" s="9">
@@ -6884,30 +6772,30 @@
       <c r="H144" s="9">
         <v>28.119577580000001</v>
       </c>
-      <c r="I144" s="1" t="s">
+      <c r="I144" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="J144" s="1">
+      <c r="J144" s="8">
         <v>24</v>
       </c>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A145" s="1" t="s">
+      <c r="A145" s="8" t="s">
         <v>309</v>
       </c>
-      <c r="B145" s="1" t="s">
+      <c r="B145" s="8" t="s">
         <v>330</v>
       </c>
-      <c r="C145" s="1" t="s">
+      <c r="C145" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="D145" s="1">
+      <c r="D145" s="8">
         <v>92.34</v>
       </c>
-      <c r="E145" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F145" s="1">
+      <c r="E145" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F145" s="8">
         <v>100</v>
       </c>
       <c r="G145" s="9">
@@ -6916,30 +6804,30 @@
       <c r="H145" s="9">
         <v>28.120772420000002</v>
       </c>
-      <c r="I145" s="1" t="s">
+      <c r="I145" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="J145" s="1">
+      <c r="J145" s="8">
         <v>24</v>
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A146" s="1" t="s">
+      <c r="A146" s="8" t="s">
         <v>310</v>
       </c>
-      <c r="B146" s="1" t="s">
+      <c r="B146" s="8" t="s">
         <v>330</v>
       </c>
-      <c r="C146" s="1" t="s">
+      <c r="C146" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="D146" s="1">
+      <c r="D146" s="8">
         <v>92.67</v>
       </c>
-      <c r="E146" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F146" s="1">
+      <c r="E146" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F146" s="8">
         <v>120</v>
       </c>
       <c r="G146" s="9">
@@ -6948,30 +6836,30 @@
       <c r="H146" s="9">
         <v>28.12179459</v>
       </c>
-      <c r="I146" s="1" t="s">
+      <c r="I146" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="J146" s="1">
+      <c r="J146" s="8">
         <v>24</v>
       </c>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A147" s="1" t="s">
+      <c r="A147" s="8" t="s">
         <v>311</v>
       </c>
-      <c r="B147" s="1" t="s">
+      <c r="B147" s="8" t="s">
         <v>330</v>
       </c>
-      <c r="C147" s="1" t="s">
+      <c r="C147" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="D147" s="1">
+      <c r="D147" s="8">
         <v>93.19</v>
       </c>
-      <c r="E147" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F147" s="1">
+      <c r="E147" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F147" s="8">
         <v>120</v>
       </c>
       <c r="G147" s="9">
@@ -6980,30 +6868,30 @@
       <c r="H147" s="9">
         <v>28.125313479999999</v>
       </c>
-      <c r="I147" s="1" t="s">
+      <c r="I147" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="J147" s="1">
+      <c r="J147" s="8">
         <v>24</v>
       </c>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A148" s="10" t="s">
+      <c r="A148" s="8" t="s">
         <v>312</v>
       </c>
-      <c r="B148" s="10" t="s">
+      <c r="B148" s="8" t="s">
         <v>330</v>
       </c>
-      <c r="C148" s="10" t="s">
+      <c r="C148" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="D148" s="10">
+      <c r="D148" s="8">
         <v>93.62</v>
       </c>
-      <c r="E148" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="F148" s="10">
+      <c r="E148" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F148" s="8">
         <v>120</v>
       </c>
       <c r="G148" s="9">
@@ -7012,30 +6900,30 @@
       <c r="H148" s="9">
         <v>28.12756143</v>
       </c>
-      <c r="I148" s="10" t="s">
+      <c r="I148" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="J148" s="1">
+      <c r="J148" s="8">
         <v>24</v>
       </c>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A149" s="1" t="s">
+      <c r="A149" s="8" t="s">
         <v>313</v>
       </c>
-      <c r="B149" s="1" t="s">
+      <c r="B149" s="8" t="s">
         <v>330</v>
       </c>
-      <c r="C149" s="1" t="s">
+      <c r="C149" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="D149" s="1">
+      <c r="D149" s="8">
         <v>93.64</v>
       </c>
-      <c r="E149" s="1" t="s">
+      <c r="E149" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F149" s="1">
+      <c r="F149" s="8">
         <v>180</v>
       </c>
       <c r="G149" s="9">
@@ -7044,30 +6932,30 @@
       <c r="H149" s="9">
         <v>28.127586399999998</v>
       </c>
-      <c r="I149" s="1" t="s">
+      <c r="I149" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="J149" s="1">
+      <c r="J149" s="8">
         <v>24</v>
       </c>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A150" s="1" t="s">
+      <c r="A150" s="8" t="s">
         <v>314</v>
       </c>
-      <c r="B150" s="1" t="s">
+      <c r="B150" s="8" t="s">
         <v>330</v>
       </c>
-      <c r="C150" s="1" t="s">
+      <c r="C150" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="D150" s="1">
+      <c r="D150" s="8">
         <v>93.71</v>
       </c>
-      <c r="E150" s="1" t="s">
+      <c r="E150" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F150" s="1">
+      <c r="F150" s="8">
         <v>1200</v>
       </c>
       <c r="G150" s="9">
@@ -7076,30 +6964,30 @@
       <c r="H150" s="9">
         <v>28.12831169</v>
       </c>
-      <c r="I150" s="1" t="s">
+      <c r="I150" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="J150" s="1">
+      <c r="J150" s="8">
         <v>24</v>
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A151" s="1" t="s">
+      <c r="A151" s="8" t="s">
         <v>315</v>
       </c>
-      <c r="B151" s="1" t="s">
+      <c r="B151" s="8" t="s">
         <v>330</v>
       </c>
-      <c r="C151" s="1" t="s">
+      <c r="C151" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="D151" s="1">
+      <c r="D151" s="8">
         <v>94.03</v>
       </c>
-      <c r="E151" s="1" t="s">
+      <c r="E151" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F151" s="1">
+      <c r="F151" s="8">
         <v>360</v>
       </c>
       <c r="G151" s="9">
@@ -7108,30 +6996,30 @@
       <c r="H151" s="9">
         <v>28.129931240000001</v>
       </c>
-      <c r="I151" s="1" t="s">
+      <c r="I151" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="J151" s="1">
+      <c r="J151" s="8">
         <v>24</v>
       </c>
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A152" s="1" t="s">
+      <c r="A152" s="8" t="s">
         <v>316</v>
       </c>
-      <c r="B152" s="1" t="s">
+      <c r="B152" s="8" t="s">
         <v>330</v>
       </c>
-      <c r="C152" s="1" t="s">
+      <c r="C152" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="D152" s="1">
+      <c r="D152" s="8">
         <v>94.04</v>
       </c>
-      <c r="E152" s="1" t="s">
+      <c r="E152" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F152" s="1">
+      <c r="F152" s="8">
         <v>100</v>
       </c>
       <c r="G152" s="9">
@@ -7140,30 +7028,30 @@
       <c r="H152" s="9">
         <v>28.129979039999998</v>
       </c>
-      <c r="I152" s="1" t="s">
+      <c r="I152" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="J152" s="1">
+      <c r="J152" s="8">
         <v>24</v>
       </c>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A153" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="B153" s="1" t="s">
+      <c r="A153" s="8" t="s">
+        <v>353</v>
+      </c>
+      <c r="B153" s="8" t="s">
         <v>330</v>
       </c>
-      <c r="C153" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="D153" s="1">
+      <c r="C153" s="13" t="s">
+        <v>354</v>
+      </c>
+      <c r="D153" s="8">
         <v>94.057000000000002</v>
       </c>
-      <c r="E153" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F153" s="1">
+      <c r="E153" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F153" s="8">
         <v>200</v>
       </c>
       <c r="G153" s="9">
@@ -7172,30 +7060,30 @@
       <c r="H153" s="9">
         <v>28.12993402</v>
       </c>
-      <c r="I153" s="1" t="s">
+      <c r="I153" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="J153" s="1">
+      <c r="J153" s="8">
         <v>24</v>
       </c>
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A154" s="1" t="s">
+      <c r="A154" s="8" t="s">
         <v>317</v>
       </c>
-      <c r="B154" s="1" t="s">
+      <c r="B154" s="8" t="s">
         <v>330</v>
       </c>
-      <c r="C154" s="1" t="s">
+      <c r="C154" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="D154" s="1">
+      <c r="D154" s="8">
         <v>94.96</v>
       </c>
-      <c r="E154" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F154" s="1">
+      <c r="E154" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F154" s="8">
         <v>100</v>
       </c>
       <c r="G154" s="9">
@@ -7204,30 +7092,30 @@
       <c r="H154" s="9">
         <v>28.133634789999999</v>
       </c>
-      <c r="I154" s="1" t="s">
+      <c r="I154" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="J154" s="1">
+      <c r="J154" s="8">
         <v>24</v>
       </c>
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A155" s="1" t="s">
+      <c r="A155" s="8" t="s">
         <v>318</v>
       </c>
-      <c r="B155" s="1" t="s">
+      <c r="B155" s="8" t="s">
         <v>330</v>
       </c>
-      <c r="C155" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="D155" s="1">
+      <c r="C155" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="D155" s="8">
         <v>95.61</v>
       </c>
-      <c r="E155" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F155" s="1">
+      <c r="E155" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F155" s="8">
         <v>100</v>
       </c>
       <c r="G155" s="9">
@@ -7236,10 +7124,10 @@
       <c r="H155" s="9">
         <v>28.136690489999999</v>
       </c>
-      <c r="I155" s="1" t="s">
+      <c r="I155" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="J155" s="1">
+      <c r="J155" s="8">
         <v>24</v>
       </c>
     </row>
@@ -7262,48 +7150,48 @@
       <c r="F156" s="8">
         <v>100</v>
       </c>
-      <c r="G156" s="9" t="s">
-        <v>404</v>
-      </c>
-      <c r="H156" s="9" t="s">
-        <v>405</v>
+      <c r="G156" s="9">
+        <v>-105.599986</v>
+      </c>
+      <c r="H156" s="9">
+        <v>28.143982000000001</v>
       </c>
       <c r="I156" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="J156" s="1">
+      <c r="J156" s="8">
         <v>24</v>
       </c>
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A157" s="1" t="s">
+      <c r="A157" s="8" t="s">
         <v>320</v>
       </c>
-      <c r="B157" s="1" t="s">
+      <c r="B157" s="8" t="s">
         <v>330</v>
       </c>
-      <c r="C157" s="1" t="s">
+      <c r="C157" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="D157" s="1">
+      <c r="D157" s="8">
         <v>96.96</v>
       </c>
-      <c r="E157" s="1" t="s">
+      <c r="E157" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F157" s="1">
+      <c r="F157" s="8">
         <v>480</v>
       </c>
       <c r="G157" s="9">
-        <v>-105.60089364</v>
+        <v>-105.600874</v>
       </c>
       <c r="H157" s="9">
-        <v>28.145025619999998</v>
-      </c>
-      <c r="I157" s="1" t="s">
+        <v>28.144977999999998</v>
+      </c>
+      <c r="I157" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="J157" s="1">
+      <c r="J157" s="8">
         <v>24</v>
       </c>
     </row>
@@ -7326,36 +7214,36 @@
       <c r="F158" s="8">
         <v>30</v>
       </c>
-      <c r="G158" s="9" t="s">
-        <v>406</v>
-      </c>
-      <c r="H158" s="9" t="s">
-        <v>407</v>
+      <c r="G158" s="9">
+        <v>-105.60320400000001</v>
+      </c>
+      <c r="H158" s="9">
+        <v>28.145493999999999</v>
       </c>
       <c r="I158" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="J158" s="1">
+      <c r="J158" s="8">
         <v>24</v>
       </c>
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A159" s="1" t="s">
+      <c r="A159" s="8" t="s">
         <v>322</v>
       </c>
-      <c r="B159" s="1" t="s">
+      <c r="B159" s="8" t="s">
         <v>330</v>
       </c>
-      <c r="C159" s="1" t="s">
+      <c r="C159" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="D159" s="1">
+      <c r="D159" s="8">
         <v>97.79</v>
       </c>
-      <c r="E159" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F159" s="1">
+      <c r="E159" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F159" s="8">
         <v>100</v>
       </c>
       <c r="G159" s="9">
@@ -7364,30 +7252,30 @@
       <c r="H159" s="9">
         <v>28.147992649999999</v>
       </c>
-      <c r="I159" s="1" t="s">
+      <c r="I159" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="J159" s="1">
+      <c r="J159" s="8">
         <v>24</v>
       </c>
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A160" s="1" t="s">
+      <c r="A160" s="8" t="s">
         <v>323</v>
       </c>
-      <c r="B160" s="1" t="s">
+      <c r="B160" s="8" t="s">
         <v>330</v>
       </c>
-      <c r="C160" s="1" t="s">
+      <c r="C160" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="D160" s="1">
+      <c r="D160" s="8">
         <v>97.84</v>
       </c>
-      <c r="E160" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F160" s="1">
+      <c r="E160" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F160" s="8">
         <v>120</v>
       </c>
       <c r="G160" s="9">
@@ -7396,10 +7284,10 @@
       <c r="H160" s="9">
         <v>28.148482659999999</v>
       </c>
-      <c r="I160" s="1" t="s">
+      <c r="I160" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="J160" s="1">
+      <c r="J160" s="8">
         <v>24</v>
       </c>
     </row>
@@ -7422,16 +7310,16 @@
       <c r="F161" s="8">
         <v>200</v>
       </c>
-      <c r="G161" s="9" t="s">
-        <v>408</v>
-      </c>
-      <c r="H161" s="9" t="s">
-        <v>409</v>
+      <c r="G161" s="9">
+        <v>-105.61313333</v>
+      </c>
+      <c r="H161" s="9">
+        <v>28.15650278</v>
       </c>
       <c r="I161" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="J161" s="1">
+      <c r="J161" s="8">
         <v>24</v>
       </c>
     </row>
@@ -7454,16 +7342,16 @@
       <c r="F162" s="8">
         <v>120</v>
       </c>
-      <c r="G162" s="9" t="s">
-        <v>410</v>
-      </c>
-      <c r="H162" s="9" t="s">
-        <v>411</v>
+      <c r="G162" s="9">
+        <v>-105.61296111</v>
+      </c>
+      <c r="H162" s="9">
+        <v>28.156352779999999</v>
       </c>
       <c r="I162" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="J162" s="1">
+      <c r="J162" s="8">
         <v>24</v>
       </c>
     </row>
@@ -7486,16 +7374,16 @@
       <c r="F163" s="8">
         <v>120</v>
       </c>
-      <c r="G163" s="9" t="s">
-        <v>412</v>
-      </c>
-      <c r="H163" s="9" t="s">
-        <v>413</v>
+      <c r="G163" s="11">
+        <v>-105.61955555999999</v>
+      </c>
+      <c r="H163" s="9">
+        <v>28.15974722</v>
       </c>
       <c r="I163" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="J163" s="1">
+      <c r="J163" s="8">
         <v>24</v>
       </c>
     </row>
@@ -7518,23 +7406,50 @@
       <c r="F164" s="8">
         <v>100</v>
       </c>
-      <c r="G164" s="9" t="s">
-        <v>414</v>
-      </c>
-      <c r="H164" s="9" t="s">
-        <v>415</v>
+      <c r="G164" s="9">
+        <v>-105.61968056000001</v>
+      </c>
+      <c r="H164" s="9">
+        <v>28.159800000000001</v>
       </c>
       <c r="I164" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="J164" s="1">
+      <c r="J164" s="8">
         <v>24</v>
       </c>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A165" s="8"/>
-      <c r="G165" s="9"/>
-      <c r="H165" s="9"/>
+      <c r="A165" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="B165" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="C165" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="D165" s="8">
+        <v>99.786000000000001</v>
+      </c>
+      <c r="E165" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F165" s="8">
+        <v>200</v>
+      </c>
+      <c r="G165" s="12">
+        <v>-105.61969534000001</v>
+      </c>
+      <c r="H165" s="9">
+        <v>28.160025539999999</v>
+      </c>
+      <c r="I165" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="J165" s="8">
+        <v>24</v>
+      </c>
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.25">
       <c r="G166" s="3"/>
